--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 19851-2025</t>
+          <t>A 52381-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45771</v>
+        <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,13 +1636,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1675,267 +1670,272 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 43626-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45184</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 19851-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52381-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45609</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 43626-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45184</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45075</v>
+        <v>45818</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2233,50 +2233,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2290,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46127</v>
+        <v>46045</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,14 +2303,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -2351,42 +2347,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2400,10 +2396,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45566</v>
+        <v>46127</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2415,17 +2411,22 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2440,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2452,39 +2453,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
@@ -2508,7 +2509,7 @@
         <v>45824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2596,7 +2597,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2610,10 +2611,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46045</v>
+        <v>45713</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2631,13 +2632,13 @@
         </is>
       </c>
       <c r="I20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2667,46 +2668,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45713</v>
+        <v>45566</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2735,23 +2740,18 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2781,46 +2781,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44494</v>
+        <v>46202</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2855,13 +2851,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2870,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2879,58 +2875,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2944,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45714</v>
+        <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2959,11 +2955,16 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2975,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2984,58 +2985,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3049,10 +3050,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45222</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3064,13 +3065,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>11.2</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3082,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3094,58 +3090,62 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45161</v>
+        <v>45714</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3175,23 +3175,23 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -3199,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3215,42 +3215,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45231</v>
+        <v>44494</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3279,24 +3279,29 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -3304,58 +3309,58 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46202</v>
+        <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3384,19 +3389,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3430,42 +3430,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46230</v>
+        <v>45231</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3519,62 +3519,58 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3588,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45818</v>
+        <v>45075</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,13 +3600,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3640,39 +3636,43 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44494</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44476</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45090</v>
+        <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45394</v>
+        <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4838,13 +4838,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4887,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45243</v>
+        <v>45002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4916,13 +4911,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4965,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4979,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45090</v>
+        <v>45524</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4994,8 +4984,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5038,7 +5033,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5052,10 +5047,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45231</v>
+        <v>45524</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5067,8 +5062,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>9.5</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44974</v>
+        <v>44538</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5140,8 +5140,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5184,7 +5189,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5198,10 +5203,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44974</v>
+        <v>45160</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5214,7 +5219,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5257,7 +5262,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5271,10 +5276,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45251</v>
+        <v>45566</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5287,7 +5292,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5330,7 +5335,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5340,14 +5345,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45470</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5359,13 +5364,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5418,14 +5418,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45483</v>
+        <v>45243</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45265</v>
+        <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5515,8 +5515,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5559,7 +5564,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5573,10 +5578,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44515</v>
+        <v>45527</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5589,7 +5594,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5632,7 +5637,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5646,10 +5651,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45176</v>
+        <v>45680</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5662,7 +5667,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5705,7 +5710,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45548</v>
+        <v>46006</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,8 +5739,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5778,7 +5788,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5788,14 +5798,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45632</v>
+        <v>46006</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5813,7 +5823,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5856,7 +5866,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5870,10 +5880,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44908</v>
+        <v>45166</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5886,7 +5896,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5929,7 +5939,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5943,10 +5953,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45589</v>
+        <v>45166</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5959,7 +5969,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6002,7 +6012,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6016,10 +6026,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45742</v>
+        <v>45804</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6031,8 +6041,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6075,7 +6090,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6089,10 +6104,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44595</v>
+        <v>45707</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6105,7 +6120,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6148,7 +6163,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6162,10 +6177,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45566</v>
+        <v>46021</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6178,7 +6193,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6221,7 +6236,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6235,10 +6250,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45565</v>
+        <v>46021</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6251,7 +6266,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.9</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6294,7 +6309,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6308,10 +6323,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45002</v>
+        <v>46021</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6324,7 +6339,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6367,7 +6382,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6381,10 +6396,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6396,8 +6411,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6440,7 +6460,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6454,10 +6474,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45566</v>
+        <v>45394</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6469,8 +6489,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6513,7 +6538,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6527,10 +6552,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45575</v>
+        <v>45103</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6543,7 +6568,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6586,7 +6611,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6600,10 +6625,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46069</v>
+        <v>45824</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6615,8 +6640,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6659,7 +6689,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6673,10 +6703,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45834</v>
+        <v>45019</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6689,7 +6719,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6732,7 +6762,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6742,14 +6772,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45834</v>
+        <v>45089</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6805,7 +6835,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6819,10 +6849,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44906</v>
+        <v>45899</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6835,7 +6865,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6878,7 +6908,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6888,14 +6918,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45835</v>
+        <v>45478</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6907,13 +6937,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6956,7 +6981,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6970,10 +6995,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45209</v>
+        <v>45183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6986,7 +7011,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7029,7 +7054,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7043,10 +7068,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45824</v>
+        <v>46045</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7064,7 +7089,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7107,7 +7132,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7121,10 +7146,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45103</v>
+        <v>46045</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7136,8 +7161,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>14.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7180,7 +7210,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7194,10 +7224,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45589</v>
+        <v>46045</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7209,8 +7239,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7253,7 +7288,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7267,10 +7302,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45524</v>
+        <v>45908</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7284,11 +7319,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7331,7 +7366,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7345,10 +7380,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45899</v>
+        <v>45090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7361,7 +7396,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7404,7 +7439,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7418,10 +7453,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45716</v>
+        <v>45603</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7434,7 +7469,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7477,7 +7512,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7491,10 +7526,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45908</v>
+        <v>45834</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7506,13 +7541,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7555,7 +7585,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7565,14 +7595,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45265</v>
+        <v>45835</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,8 +7614,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7628,7 +7663,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7638,14 +7673,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45862</v>
+        <v>45834</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7658,7 +7693,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7701,7 +7736,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7711,14 +7746,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44929</v>
+        <v>45916</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,8 +7765,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7770,35 +7810,11 @@
         <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr"/>
-      <c r="X84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD84">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7812,10 +7828,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45916</v>
+        <v>45919</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7827,13 +7843,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7876,7 +7887,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7890,10 +7901,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45369</v>
+        <v>45919</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7906,7 +7917,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7949,7 +7960,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7963,10 +7974,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45919</v>
+        <v>46052</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7979,7 +7990,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8022,7 +8033,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8036,10 +8047,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45919</v>
+        <v>46055</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8052,7 +8063,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8095,7 +8106,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8105,14 +8116,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45614</v>
+        <v>45632</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8124,8 +8135,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8168,7 +8184,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8182,10 +8198,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45930</v>
+        <v>44494</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8197,8 +8213,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8241,7 +8262,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8255,10 +8276,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45930</v>
+        <v>45548</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8271,7 +8292,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8314,7 +8335,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8328,10 +8349,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46079</v>
+        <v>45002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8344,7 +8365,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8387,7 +8408,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8401,10 +8422,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45933</v>
+        <v>46010</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8416,8 +8437,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8460,7 +8486,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8474,10 +8500,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45257</v>
+        <v>46010</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8489,8 +8515,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8533,7 +8564,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8547,10 +8578,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45883</v>
+        <v>45930</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8563,7 +8594,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8606,7 +8637,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8620,10 +8651,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45002</v>
+        <v>46010</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8635,8 +8666,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8679,7 +8715,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8693,10 +8729,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45940</v>
+        <v>45257</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8709,7 +8745,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8752,7 +8788,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8766,10 +8802,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44900</v>
+        <v>46010</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8781,8 +8817,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8825,7 +8866,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8839,10 +8880,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44755</v>
+        <v>46062</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8855,7 +8896,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8898,7 +8939,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8912,10 +8953,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45942</v>
+        <v>45716</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8928,7 +8969,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8971,7 +9012,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8985,10 +9026,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44727</v>
+        <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9001,7 +9042,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9044,7 +9085,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9058,10 +9099,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45169</v>
+        <v>45742</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9073,13 +9114,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9122,7 +9158,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9136,10 +9172,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45453</v>
+        <v>46069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9152,7 +9188,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9195,7 +9231,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9209,10 +9245,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45229</v>
+        <v>45265</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9225,7 +9261,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9268,7 +9304,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9282,10 +9318,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45973</v>
+        <v>45862</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9298,7 +9334,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9341,7 +9377,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9355,10 +9391,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45980</v>
+        <v>45933</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9371,7 +9407,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9414,7 +9450,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9428,10 +9464,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45251</v>
+        <v>44537</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9444,7 +9480,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9487,7 +9523,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9501,10 +9537,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46127</v>
+        <v>45575</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9516,13 +9552,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9565,7 +9596,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9579,10 +9610,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44538</v>
+        <v>44895</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9594,13 +9625,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9643,7 +9669,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9657,10 +9683,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45988</v>
+        <v>45942</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9673,7 +9699,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9716,7 +9742,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9730,10 +9756,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45566</v>
+        <v>45940</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9746,7 +9772,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9789,7 +9815,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9803,10 +9829,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45992</v>
+        <v>46079</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9862,7 +9888,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9876,10 +9902,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45089</v>
+        <v>44974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9892,7 +9918,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9935,7 +9961,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9949,10 +9975,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46006</v>
+        <v>44974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9964,13 +9990,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10013,7 +10034,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10027,10 +10048,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46006</v>
+        <v>44944</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10044,11 +10065,11 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10091,7 +10112,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10105,10 +10126,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44944</v>
+        <v>45883</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10120,13 +10141,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10169,7 +10185,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10183,10 +10199,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45098</v>
+        <v>45169</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10198,8 +10214,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10242,7 +10263,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10256,10 +10277,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45169</v>
+        <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10271,13 +10292,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10320,7 +10336,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10334,10 +10350,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45933</v>
+        <v>45394</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10355,7 +10371,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>9.4</v>
+        <v>0.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10398,7 +10414,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10412,10 +10428,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45394</v>
+        <v>44906</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10427,13 +10443,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10476,7 +10487,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10490,10 +10501,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45078</v>
+        <v>44687</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10517,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10549,7 +10560,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10563,10 +10574,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44537</v>
+        <v>44944</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10578,8 +10589,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10622,7 +10638,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10636,10 +10652,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46021</v>
+        <v>44937</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10652,7 +10668,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10695,7 +10711,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10709,10 +10725,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46021</v>
+        <v>45566</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10725,7 +10741,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10768,7 +10784,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10782,10 +10798,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46021</v>
+        <v>45614</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10798,7 +10814,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10841,7 +10857,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10855,10 +10871,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44944</v>
+        <v>45524</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10876,7 +10892,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10919,7 +10935,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10933,10 +10949,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45755</v>
+        <v>45176</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10949,7 +10965,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10992,7 +11008,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11006,10 +11022,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45575</v>
+        <v>46127</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11021,8 +11037,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11065,7 +11086,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11079,10 +11100,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44785</v>
+        <v>45973</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11094,13 +11115,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11143,7 +11159,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11157,10 +11173,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46045</v>
+        <v>45980</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11170,11 +11186,6 @@
       <c r="G130" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -11221,7 +11232,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11235,10 +11246,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46045</v>
+        <v>44944</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11256,7 +11267,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11299,7 +11310,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11313,10 +11324,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46045</v>
+        <v>45369</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11328,13 +11339,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>14.3</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11377,7 +11383,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11391,10 +11397,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46052</v>
+        <v>45988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11407,7 +11413,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11450,7 +11456,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11464,10 +11470,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46055</v>
+        <v>45470</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11479,8 +11485,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11523,7 +11534,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11537,10 +11548,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45524</v>
+        <v>45992</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11552,13 +11563,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11601,7 +11607,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11615,10 +11621,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45524</v>
+        <v>45755</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11630,13 +11636,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11679,7 +11680,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11693,10 +11694,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45524</v>
+        <v>44795</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11710,11 +11711,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11757,7 +11758,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11771,10 +11772,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46010</v>
+        <v>45933</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11788,11 +11789,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11835,7 +11836,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11849,10 +11850,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46010</v>
+        <v>45090</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11864,13 +11865,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11913,7 +11909,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11927,10 +11923,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46062</v>
+        <v>44785</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11942,8 +11938,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11986,7 +11987,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11996,14 +11997,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46010</v>
+        <v>45531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12017,11 +12018,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12064,7 +12065,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12078,10 +12079,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46010</v>
+        <v>45561</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12093,13 +12094,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12142,7 +12138,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12156,10 +12152,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44494</v>
+        <v>44727</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12171,13 +12167,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12220,7 +12211,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12234,10 +12225,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44494</v>
+        <v>45233</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12249,13 +12240,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12298,7 +12284,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12308,14 +12294,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45531</v>
+        <v>45489</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12327,13 +12313,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>9.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12376,7 +12357,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12390,10 +12371,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45719</v>
+        <v>45742</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12406,7 +12387,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12449,7 +12430,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12463,10 +12444,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12478,13 +12459,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>14.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12527,7 +12503,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12541,10 +12517,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12556,8 +12532,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>14.6</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12600,7 +12581,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12614,10 +12595,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44531</v>
+        <v>44515</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12630,7 +12611,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12673,7 +12654,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12687,10 +12668,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46153</v>
+        <v>45090</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12703,7 +12684,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12746,7 +12727,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12756,14 +12737,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45631</v>
+        <v>45218</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12781,7 +12762,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12824,7 +12805,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12838,10 +12819,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45742</v>
+        <v>45720</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12854,7 +12835,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12897,7 +12878,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12907,14 +12888,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45076</v>
+        <v>46153</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12927,7 +12908,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12987,7 +12968,7 @@
         <v>45890</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13043,7 +13024,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13057,10 +13038,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45561</v>
+        <v>46170</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13073,7 +13054,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13116,7 +13097,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 24724-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13130,10 +13111,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45233</v>
+        <v>46171</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13145,8 +13126,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13189,7 +13175,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13203,10 +13189,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45218</v>
+        <v>46171</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13224,7 +13210,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13267,7 +13253,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13277,14 +13263,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46170</v>
+        <v>45631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13296,8 +13282,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13340,7 +13331,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13354,10 +13345,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45243</v>
+        <v>46181</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13367,11 +13358,6 @@
       <c r="G159" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -13418,7 +13404,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24724-2026</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13432,10 +13418,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46171</v>
+        <v>46188</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13453,7 +13439,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.5</v>
+        <v>12.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13496,7 +13482,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13510,10 +13496,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46171</v>
+        <v>46188</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13531,7 +13517,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13574,7 +13560,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13588,10 +13574,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45183</v>
+        <v>46188</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13603,8 +13589,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13647,7 +13638,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13661,10 +13652,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45720</v>
+        <v>45561</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13720,7 +13711,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13734,10 +13725,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45252</v>
+        <v>45386</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13749,13 +13740,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13798,7 +13784,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13812,10 +13798,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46181</v>
+        <v>45252</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13827,8 +13813,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13871,7 +13862,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13885,10 +13876,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44809</v>
+        <v>46206</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13900,13 +13891,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13949,7 +13935,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13963,10 +13949,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46188</v>
+        <v>46160</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13984,7 +13970,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14027,7 +14013,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14041,10 +14027,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46188</v>
+        <v>46210</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14062,7 +14048,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>12.6</v>
+        <v>3.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14105,7 +14091,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14119,10 +14105,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46188</v>
+        <v>46210</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14140,7 +14126,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14183,7 +14169,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14197,10 +14183,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45566</v>
+        <v>44906</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14213,7 +14199,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14256,7 +14242,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14270,10 +14256,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45252</v>
+        <v>45209</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14285,13 +14271,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14334,7 +14315,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14348,10 +14329,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44895</v>
+        <v>46260</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14364,7 +14345,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14407,7 +14388,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14421,10 +14402,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44906</v>
+        <v>45589</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14437,7 +14418,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14480,7 +14461,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14494,10 +14475,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44503</v>
+        <v>44972</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14509,13 +14490,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14558,7 +14534,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14568,14 +14544,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44664</v>
+        <v>45076</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14587,13 +14563,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14636,7 +14607,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14646,14 +14617,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45401</v>
+        <v>45265</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14666,7 +14637,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14709,7 +14680,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14723,10 +14694,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45489</v>
+        <v>46230</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14739,7 +14710,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14782,7 +14753,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14796,10 +14767,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44494</v>
+        <v>46191</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14811,13 +14782,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14860,7 +14826,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14874,10 +14840,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45436</v>
+        <v>45251</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14890,7 +14856,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14933,7 +14899,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14947,10 +14913,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44939</v>
+        <v>44900</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14963,7 +14929,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15006,7 +14972,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15020,10 +14986,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45089</v>
+        <v>46276</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15036,7 +15002,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15079,7 +15045,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15093,10 +15059,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45090</v>
+        <v>44809</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15108,8 +15074,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15152,7 +15123,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15162,14 +15133,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44687</v>
+        <v>45483</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15181,8 +15152,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15225,7 +15201,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15239,10 +15215,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44906</v>
+        <v>45719</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15255,7 +15231,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15298,7 +15274,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15312,10 +15288,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46206</v>
+        <v>45229</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15328,7 +15304,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15371,7 +15347,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15381,14 +15357,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44809</v>
+        <v>44929</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15400,13 +15376,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15445,11 +15416,35 @@
         <v>0</v>
       </c>
       <c r="V186" s="2" t="inlineStr"/>
+      <c r="X186">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y186">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA186">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB186">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC186">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD186">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15463,10 +15458,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44972</v>
+        <v>44755</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15479,7 +15474,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15522,7 +15517,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15536,10 +15531,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46160</v>
+        <v>45243</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15557,7 +15552,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15600,7 +15595,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46210</v>
+        <v>44908</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15629,13 +15624,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15678,7 +15668,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15688,14 +15678,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46210</v>
+        <v>45631</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15713,7 +15703,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15756,7 +15746,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15770,10 +15760,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45166</v>
+        <v>45707</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15786,7 +15776,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15829,7 +15819,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15843,10 +15833,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45166</v>
+        <v>45252</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15858,8 +15848,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15902,7 +15897,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15912,14 +15907,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45394</v>
+        <v>45632</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15937,7 +15932,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15980,7 +15975,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15994,10 +15989,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44795</v>
+        <v>45394</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16015,7 +16010,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16058,7 +16053,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16068,14 +16063,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45632</v>
+        <v>45209</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16087,13 +16082,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16136,7 +16126,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16150,10 +16140,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45019</v>
+        <v>44494</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16165,8 +16155,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16209,7 +16204,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16223,10 +16218,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46260</v>
+        <v>44906</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16239,7 +16234,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16282,7 +16277,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16296,10 +16291,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44944</v>
+        <v>44531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16311,13 +16306,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16360,7 +16350,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16370,14 +16360,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45630</v>
+        <v>45089</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16390,7 +16380,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16433,7 +16423,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16447,10 +16437,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45209</v>
+        <v>45524</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16462,8 +16452,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16506,7 +16501,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16516,14 +16511,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45243</v>
+        <v>45401</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16536,7 +16531,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16579,7 +16574,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16593,10 +16588,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45603</v>
+        <v>44494</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16608,8 +16603,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16652,7 +16652,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16666,10 +16666,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45160</v>
+        <v>45098</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16739,10 +16739,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46230</v>
+        <v>45231</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46191</v>
+        <v>45575</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45478</v>
+        <v>45078</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16944,7 +16944,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45386</v>
+        <v>45566</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45561</v>
+        <v>45251</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17104,10 +17104,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45707</v>
+        <v>44809</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17119,8 +17119,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17163,7 +17168,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17177,10 +17182,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46276</v>
+        <v>45243</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17193,7 +17198,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17236,7 +17241,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17246,14 +17251,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45631</v>
+        <v>44939</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17265,13 +17270,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17387,7 +17387,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17401,10 +17401,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45617</v>
+        <v>45169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17416,8 +17416,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17460,7 +17465,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17474,10 +17479,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45786</v>
+        <v>45566</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17489,13 +17494,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17538,7 +17538,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17552,10 +17552,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45789</v>
+        <v>44664</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17567,8 +17567,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17611,7 +17616,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17625,10 +17630,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45721</v>
+        <v>45436</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17641,7 +17646,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17684,7 +17689,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17698,10 +17703,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45680</v>
+        <v>44469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17714,7 +17719,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17757,7 +17762,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17771,10 +17776,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45527</v>
+        <v>45617</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17787,7 +17792,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17830,7 +17835,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17844,10 +17849,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45630</v>
+        <v>45786</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17861,11 +17866,11 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17908,7 +17913,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17922,10 +17927,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45804</v>
+        <v>45789</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17937,13 +17942,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17986,7 +17986,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45707</v>
+        <v>45721</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 38204-2024</t>
+          <t>A 43626-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45545</v>
+        <v>45184</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1521,25 +1521,20 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1551,476 +1546,481 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
       </c>
       <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 38204-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38204-2024 artfynd.xlsx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38204-2024 karta.png", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38204-2024 georefererad karta.tif", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 38204-2024 karta knärot.png", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38204-2024 FSC-klagomål.docx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38204-2024 FSC-klagomål mail.docx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38204-2024 tillsynsbegäran.docx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38204-2024 tillsynsbegäran mail.docx", "A 38204-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 19851-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 52381-2024</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45609</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1.4</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 43626-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45184</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S 1323-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 19851-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45771</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S 1323-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45771</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/S 1323-2025 artfynd.xlsx", "S 1323-2025")</f>
         <v/>
@@ -2057,7 +2057,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23268-2022</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44720</v>
+        <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,11 +2088,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>11.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2125,49 +2125,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45818</v>
+        <v>45161</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2237,42 +2237,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46045</v>
+        <v>45231</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2301,19 +2301,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2343,46 +2338,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 23268-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46127</v>
+        <v>44720</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2417,13 +2412,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2453,46 +2448,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2506,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45824</v>
+        <v>46127</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2521,14 +2516,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2555,49 +2555,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45713</v>
+        <v>45824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,13 +2626,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2665,53 +2660,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2725,10 +2716,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45566</v>
+        <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2740,17 +2731,22 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2765,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2781,42 +2777,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46202</v>
+        <v>45075</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,19 +2845,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2887,46 +2882,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2939,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45222</v>
+        <v>45566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,23 +2954,18 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2985,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2994,49 +2988,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3050,10 +3044,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46230</v>
+        <v>46045</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3065,20 +3059,25 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3090,62 +3089,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3159,10 +3154,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45714</v>
+        <v>46202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3174,14 +3169,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3199,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3215,35 +3215,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
         <v>44494</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45161</v>
+        <v>45714</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3390,23 +3390,23 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3430,42 +3430,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45231</v>
+        <v>46230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3519,58 +3519,62 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3584,10 +3588,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45075</v>
+        <v>45818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,13 +3604,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3636,50 +3640,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 66556-2021</t>
+          <t>A 3290-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44519</v>
+        <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3752,7 +3752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3290-2022</t>
+          <t>A 66556-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44584</v>
+        <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 70949-2021</t>
+          <t>A 59883-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44538</v>
+        <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4309,11 +4309,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6068-2022</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44599</v>
+        <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34676-2022</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44795</v>
+        <v>45090</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4536,13 +4536,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4585,7 +4580,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59883-2021</t>
+          <t>A 70949-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4599,10 +4594,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44494</v>
+        <v>44538</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4616,11 +4611,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4663,7 +4658,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4677,10 +4672,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44476</v>
+        <v>45090</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4693,7 +4688,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4736,7 +4731,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 6068-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4745,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45453</v>
+        <v>44599</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4761,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4804,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4818,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44595</v>
+        <v>45183</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4839,7 +4834,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4877,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 34676-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4891,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45002</v>
+        <v>44795</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4911,8 +4906,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45524</v>
+        <v>45243</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45524</v>
+        <v>45720</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5062,13 +5062,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5106,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44538</v>
+        <v>45394</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5142,11 +5137,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5189,7 +5184,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5203,10 +5198,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45160</v>
+        <v>45252</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5218,8 +5213,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>7.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45566</v>
+        <v>44809</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5291,8 +5291,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5335,7 +5340,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5345,14 +5350,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5365,7 +5370,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5408,7 +5413,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5422,10 +5427,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45243</v>
+        <v>45231</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5437,13 +5442,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>9.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45630</v>
+        <v>44974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5515,13 +5515,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5564,7 +5559,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5578,10 +5573,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45527</v>
+        <v>44974</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5594,7 +5589,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5637,7 +5632,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5651,10 +5646,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45680</v>
+        <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5710,7 +5705,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5739,13 +5734,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5788,7 +5778,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5802,10 +5792,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46006</v>
+        <v>45470</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5819,11 +5809,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5866,7 +5856,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5876,14 +5866,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45166</v>
+        <v>45483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5895,8 +5885,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5939,7 +5934,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5953,10 +5948,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45166</v>
+        <v>45265</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5969,7 +5964,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6012,7 +6007,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6026,10 +6021,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45804</v>
+        <v>45824</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6047,7 +6042,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6090,7 +6085,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6104,10 +6099,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45707</v>
+        <v>45103</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6163,7 +6158,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46021</v>
+        <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6193,7 +6188,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6236,7 +6231,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6250,10 +6245,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46021</v>
+        <v>45176</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6266,7 +6261,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6309,7 +6304,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6323,10 +6318,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46021</v>
+        <v>45566</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6339,7 +6334,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6382,7 +6377,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6396,10 +6391,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44503</v>
+        <v>45548</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6411,13 +6406,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6460,7 +6450,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6474,10 +6464,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45394</v>
+        <v>45899</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,13 +6479,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6538,7 +6523,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6548,14 +6533,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45103</v>
+        <v>45632</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6567,8 +6552,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6611,7 +6601,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6625,10 +6615,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45824</v>
+        <v>45252</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6646,7 +6636,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6689,7 +6679,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6703,10 +6693,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45019</v>
+        <v>44908</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6719,7 +6709,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6762,7 +6752,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6776,10 +6766,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45089</v>
+        <v>45908</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6791,8 +6781,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6835,7 +6830,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6849,10 +6844,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45899</v>
+        <v>45589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6865,7 +6860,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6908,7 +6903,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6922,10 +6917,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45478</v>
+        <v>45916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6937,8 +6932,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45183</v>
+        <v>45742</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46045</v>
+        <v>44895</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7083,13 +7083,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7132,7 +7127,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7146,10 +7141,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46045</v>
+        <v>44595</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7161,13 +7156,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>14.3</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7210,7 +7200,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7224,10 +7214,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46045</v>
+        <v>45919</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7239,13 +7229,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7288,7 +7273,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7302,10 +7287,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45908</v>
+        <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7317,13 +7302,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7366,7 +7346,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7380,10 +7360,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45090</v>
+        <v>45566</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7396,7 +7376,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7439,7 +7419,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7453,10 +7433,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45603</v>
+        <v>45565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7469,7 +7449,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7512,7 +7492,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7526,10 +7506,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45834</v>
+        <v>45002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7542,7 +7522,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7585,7 +7565,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7595,14 +7575,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45835</v>
+        <v>44937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7614,13 +7594,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7663,7 +7638,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7673,14 +7648,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45834</v>
+        <v>45930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7693,7 +7668,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7736,7 +7711,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7750,10 +7725,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45916</v>
+        <v>45566</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7765,13 +7740,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7814,7 +7784,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7828,10 +7798,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45919</v>
+        <v>45930</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7844,7 +7814,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7887,7 +7857,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7901,10 +7871,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45919</v>
+        <v>46127</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7916,8 +7886,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7960,7 +7935,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7974,10 +7949,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46052</v>
+        <v>45575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7990,7 +7965,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8033,7 +8008,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8047,10 +8022,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46055</v>
+        <v>44906</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8063,7 +8038,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8106,7 +8081,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8116,14 +8091,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45632</v>
+        <v>44503</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8141,7 +8116,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8184,7 +8159,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8198,10 +8173,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44494</v>
+        <v>45933</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8213,13 +8188,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8262,7 +8232,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8276,10 +8246,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45548</v>
+        <v>44664</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8291,8 +8261,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8335,7 +8310,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8349,10 +8324,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45002</v>
+        <v>45940</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8365,7 +8340,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8408,7 +8383,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8422,10 +8397,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46010</v>
+        <v>45942</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8437,13 +8412,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8486,7 +8456,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8500,10 +8470,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46010</v>
+        <v>44906</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,13 +8485,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8564,7 +8529,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8578,10 +8543,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45930</v>
+        <v>45209</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8594,7 +8559,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8637,7 +8602,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8651,10 +8616,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46010</v>
+        <v>45933</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8668,11 +8633,11 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8715,7 +8680,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8729,10 +8694,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45257</v>
+        <v>45589</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8745,7 +8710,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8788,7 +8753,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8802,10 +8767,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46010</v>
+        <v>45524</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8819,11 +8784,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8866,7 +8831,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8876,14 +8841,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46062</v>
+        <v>44929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8896,7 +8861,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8935,11 +8900,35 @@
         <v>0</v>
       </c>
       <c r="V99" s="2" t="inlineStr"/>
+      <c r="X99">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y99">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA99">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB99">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC99">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD99">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8953,10 +8942,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45716</v>
+        <v>45755</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8969,7 +8958,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9012,7 +9001,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9026,10 +9015,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45930</v>
+        <v>45369</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9042,7 +9031,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9085,7 +9074,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9099,10 +9088,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45742</v>
+        <v>44785</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9114,8 +9103,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9158,7 +9152,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9172,10 +9166,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46069</v>
+        <v>45614</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9188,7 +9182,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9231,7 +9225,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9241,14 +9235,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45265</v>
+        <v>45401</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9261,7 +9255,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9304,7 +9298,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9318,10 +9312,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45862</v>
+        <v>45489</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9334,7 +9328,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9377,7 +9371,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9391,10 +9385,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45933</v>
+        <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9407,7 +9401,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9450,7 +9444,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9464,10 +9458,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44537</v>
+        <v>44494</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9479,8 +9473,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9523,7 +9522,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9537,10 +9536,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45575</v>
+        <v>45436</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9553,7 +9552,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9596,7 +9595,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9610,10 +9609,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44895</v>
+        <v>45980</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9626,7 +9625,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9669,7 +9668,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9679,14 +9678,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45942</v>
+        <v>45531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9698,8 +9697,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9742,7 +9746,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9756,10 +9760,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45940</v>
+        <v>44939</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9815,7 +9819,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9829,10 +9833,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46079</v>
+        <v>45257</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9845,7 +9849,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9888,7 +9892,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9902,10 +9906,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44974</v>
+        <v>45002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9918,7 +9922,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9961,7 +9965,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9975,10 +9979,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44974</v>
+        <v>46142</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9990,8 +9994,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10034,7 +10043,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10048,10 +10057,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44944</v>
+        <v>44900</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,13 +10072,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10112,7 +10116,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10126,10 +10130,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45883</v>
+        <v>45988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10142,7 +10146,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10185,7 +10189,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10199,10 +10203,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45169</v>
+        <v>44755</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10214,13 +10218,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10263,7 +10262,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10277,10 +10276,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45589</v>
+        <v>45992</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10293,7 +10292,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10336,7 +10335,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10350,10 +10349,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45394</v>
+        <v>44727</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,13 +10364,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10414,7 +10408,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10428,10 +10422,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44906</v>
+        <v>45089</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10444,7 +10438,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10487,7 +10481,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10501,10 +10495,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44687</v>
+        <v>46143</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10517,7 +10511,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>14.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10560,7 +10554,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10574,10 +10568,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44944</v>
+        <v>45169</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10595,7 +10589,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10638,7 +10632,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10652,10 +10646,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44937</v>
+        <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10668,7 +10662,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10711,7 +10705,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10725,10 +10719,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45566</v>
+        <v>45453</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10741,7 +10735,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10784,7 +10778,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10798,10 +10792,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45614</v>
+        <v>46153</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10814,7 +10808,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10857,7 +10851,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10871,10 +10865,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45524</v>
+        <v>46006</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10888,11 +10882,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10935,7 +10929,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10949,10 +10943,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45176</v>
+        <v>46006</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10964,8 +10958,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11008,7 +11007,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11022,10 +11021,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46127</v>
+        <v>45229</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11037,13 +11036,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11086,7 +11080,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11100,10 +11094,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45973</v>
+        <v>45890</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11116,7 +11110,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11159,7 +11153,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11173,10 +11167,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45980</v>
+        <v>44687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11189,7 +11183,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11232,7 +11226,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11246,10 +11240,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44944</v>
+        <v>46021</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11261,13 +11255,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11310,7 +11299,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11324,10 +11313,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45369</v>
+        <v>46021</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11340,7 +11329,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11383,7 +11372,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11397,10 +11386,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45988</v>
+        <v>46021</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11413,7 +11402,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11456,7 +11445,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11470,10 +11459,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45470</v>
+        <v>44906</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11485,13 +11474,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11534,7 +11518,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11548,10 +11532,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45992</v>
+        <v>45251</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11564,7 +11548,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11607,7 +11591,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11621,10 +11605,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45755</v>
+        <v>44538</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11636,8 +11620,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11680,7 +11669,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11694,10 +11683,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44795</v>
+        <v>45566</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11709,13 +11698,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11758,7 +11742,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11772,10 +11756,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45933</v>
+        <v>45089</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11787,13 +11771,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11836,7 +11815,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11850,10 +11829,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45090</v>
+        <v>46170</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11866,7 +11845,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11909,7 +11888,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 24724-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11923,10 +11902,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44785</v>
+        <v>46171</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11944,7 +11923,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11987,7 +11966,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11997,14 +11976,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45531</v>
+        <v>46171</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12022,7 +12001,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>9.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12065,7 +12044,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12079,10 +12058,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45561</v>
+        <v>46045</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12094,8 +12073,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12138,7 +12122,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12152,10 +12136,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44727</v>
+        <v>46045</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12167,8 +12151,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12211,7 +12200,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12225,10 +12214,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45233</v>
+        <v>46045</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12240,8 +12229,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>14.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12284,7 +12278,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12298,10 +12292,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45489</v>
+        <v>44809</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12313,8 +12307,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12357,7 +12356,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12371,10 +12370,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45742</v>
+        <v>46052</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12387,7 +12386,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12430,7 +12429,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12444,10 +12443,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46143</v>
+        <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12460,7 +12459,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>14.6</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12503,7 +12502,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12517,10 +12516,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46142</v>
+        <v>46055</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12532,13 +12531,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12581,7 +12575,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12595,10 +12589,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44515</v>
+        <v>44944</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12610,8 +12604,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12654,7 +12653,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12668,10 +12667,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45090</v>
+        <v>45098</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12684,7 +12683,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12727,7 +12726,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12741,10 +12740,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45218</v>
+        <v>45169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12758,11 +12757,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12805,7 +12804,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12819,10 +12818,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45720</v>
+        <v>46181</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12835,7 +12834,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12878,7 +12877,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12892,10 +12891,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46153</v>
+        <v>45394</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12907,8 +12906,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12951,7 +12955,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12965,10 +12969,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45890</v>
+        <v>46010</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12978,6 +12982,11 @@
       <c r="G154" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -13024,7 +13033,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13038,10 +13047,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46170</v>
+        <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,8 +13062,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13097,7 +13111,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24724-2026</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13111,10 +13125,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46171</v>
+        <v>46062</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,13 +13140,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13175,7 +13184,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13189,10 +13198,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46171</v>
+        <v>45078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13204,13 +13213,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13253,7 +13257,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13263,14 +13267,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45631</v>
+        <v>44537</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13282,13 +13286,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13331,7 +13330,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13345,10 +13344,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46181</v>
+        <v>46010</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13360,8 +13359,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13404,7 +13408,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13418,10 +13422,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46188</v>
+        <v>46010</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13435,11 +13439,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13482,7 +13486,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13496,10 +13500,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46188</v>
+        <v>44944</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13513,11 +13517,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13560,7 +13564,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13574,10 +13578,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46188</v>
+        <v>46069</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13589,13 +13593,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13638,7 +13637,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13652,10 +13651,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45561</v>
+        <v>46188</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13667,8 +13666,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13711,7 +13715,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13725,10 +13729,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45386</v>
+        <v>45575</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13741,7 +13745,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13784,7 +13788,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13798,10 +13802,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45252</v>
+        <v>45166</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13813,13 +13817,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13862,7 +13861,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13876,10 +13875,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46206</v>
+        <v>45166</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13892,7 +13891,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13935,7 +13934,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13949,10 +13948,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46160</v>
+        <v>46188</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13970,7 +13969,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>12.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14013,7 +14012,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14027,10 +14026,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46210</v>
+        <v>46188</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14048,7 +14047,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14091,7 +14090,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14105,10 +14104,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46210</v>
+        <v>45394</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14126,7 +14125,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14169,7 +14168,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14183,10 +14182,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44906</v>
+        <v>44795</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14198,8 +14197,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14242,7 +14246,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14252,14 +14256,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45209</v>
+        <v>45632</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14271,8 +14275,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14315,7 +14324,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14329,10 +14338,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46260</v>
+        <v>45524</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14344,8 +14353,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14388,7 +14402,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14402,10 +14416,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45589</v>
+        <v>45524</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14417,8 +14431,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14461,7 +14480,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14475,10 +14494,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44972</v>
+        <v>45524</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14490,8 +14509,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14534,7 +14558,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14544,14 +14568,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45076</v>
+        <v>45019</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14564,7 +14588,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14607,7 +14631,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14621,10 +14645,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45265</v>
+        <v>44494</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14636,8 +14660,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14680,7 +14709,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14694,10 +14723,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46230</v>
+        <v>44494</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14709,8 +14738,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14753,7 +14787,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14767,10 +14801,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46191</v>
+        <v>44944</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14782,8 +14816,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14826,7 +14865,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14840,10 +14879,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45251</v>
+        <v>45719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14856,7 +14895,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14899,7 +14938,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14913,10 +14952,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44900</v>
+        <v>44531</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14929,7 +14968,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14972,7 +15011,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14982,14 +15021,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46276</v>
+        <v>45631</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15001,8 +15040,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15045,7 +15089,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15059,10 +15103,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44809</v>
+        <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15074,13 +15118,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15123,7 +15162,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15133,14 +15172,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45483</v>
+        <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15152,13 +15191,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15201,7 +15235,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15215,10 +15249,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45719</v>
+        <v>46160</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15230,8 +15264,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15274,7 +15313,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15284,14 +15323,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45229</v>
+        <v>45076</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15304,7 +15343,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15347,7 +15386,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15357,14 +15396,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44929</v>
+        <v>46210</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15376,8 +15415,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15416,35 +15460,11 @@
         <v>0</v>
       </c>
       <c r="V186" s="2" t="inlineStr"/>
-      <c r="X186">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y186">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA186">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB186">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC186">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD186">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15458,10 +15478,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44755</v>
+        <v>46210</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15473,8 +15493,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15517,7 +15542,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15527,14 +15552,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45243</v>
+        <v>45630</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15546,13 +15571,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15595,7 +15615,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15609,10 +15629,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44908</v>
+        <v>45561</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15625,7 +15645,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15668,7 +15688,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15678,14 +15698,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45631</v>
+        <v>45233</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15697,13 +15717,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15746,7 +15761,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15760,10 +15775,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45707</v>
+        <v>45218</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15775,8 +15790,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15819,7 +15839,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15833,10 +15853,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45252</v>
+        <v>46260</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15848,13 +15868,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15897,7 +15912,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15907,14 +15922,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45632</v>
+        <v>45209</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15926,13 +15941,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15975,7 +15985,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15989,10 +15999,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45394</v>
+        <v>45243</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16010,7 +16020,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16053,7 +16063,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16067,10 +16077,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45209</v>
+        <v>45243</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16083,7 +16093,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16126,7 +16136,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16140,10 +16150,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44494</v>
+        <v>45603</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16155,13 +16165,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16204,7 +16209,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16218,10 +16223,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44906</v>
+        <v>45160</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16234,7 +16239,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16277,7 +16282,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16291,10 +16296,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44531</v>
+        <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16307,7 +16312,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16350,7 +16355,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16364,10 +16369,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45089</v>
+        <v>46230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16380,7 +16385,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16423,7 +16428,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16437,10 +16442,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45524</v>
+        <v>45386</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16452,13 +16457,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16501,7 +16501,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16511,14 +16511,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45401</v>
+        <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16588,10 +16588,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44494</v>
+        <v>45561</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16603,13 +16603,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16652,7 +16647,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16666,10 +16661,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45098</v>
+        <v>45707</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16682,7 +16677,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16725,7 +16720,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16739,10 +16734,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45231</v>
+        <v>46276</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16755,7 +16750,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>9.5</v>
+        <v>2.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16798,7 +16793,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16808,14 +16803,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45575</v>
+        <v>45631</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16827,8 +16822,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45078</v>
+        <v>44469</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16944,7 +16944,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45566</v>
+        <v>45617</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45251</v>
+        <v>45786</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17046,8 +17046,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17090,7 +17095,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17104,10 +17109,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44809</v>
+        <v>45789</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17119,13 +17124,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17168,7 +17168,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17182,10 +17182,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45243</v>
+        <v>45721</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17241,7 +17241,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44939</v>
+        <v>45680</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45565</v>
+        <v>45527</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>8.9</v>
+        <v>3.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17387,7 +17387,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17401,10 +17401,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45169</v>
+        <v>45630</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17465,7 +17465,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45566</v>
+        <v>45804</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17494,8 +17494,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17538,7 +17543,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17552,10 +17557,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44664</v>
+        <v>45707</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17567,13 +17572,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17616,7 +17616,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17630,10 +17630,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45436</v>
+        <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17689,7 +17689,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17699,14 +17699,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44469</v>
+        <v>45834</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17762,7 +17762,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17772,14 +17772,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45617</v>
+        <v>45835</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17791,8 +17791,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17835,7 +17840,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17849,10 +17854,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45786</v>
+        <v>45716</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17864,13 +17869,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17913,7 +17913,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17927,10 +17927,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45789</v>
+        <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17986,7 +17986,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45721</v>
+        <v>45862</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 43626-2023</t>
+          <t>A 38204-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45184</v>
+        <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1521,20 +1521,25 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1546,481 +1551,476 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
       </c>
       <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38204-2024 artfynd.xlsx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38204-2024 karta.png", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38204-2024 georefererad karta.tif", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 38204-2024 karta knärot.png", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38204-2024 FSC-klagomål.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38204-2024 FSC-klagomål mail.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38204-2024 tillsynsbegäran.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38204-2024 tillsynsbegäran mail.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 52381-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45609</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 43626-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45184</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallfingersvamp</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 38204-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 19851-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="D13" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="I13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38204-2024 artfynd.xlsx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38204-2024 karta.png", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38204-2024 georefererad karta.tif", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 38204-2024 karta knärot.png", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38204-2024 FSC-klagomål.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38204-2024 FSC-klagomål mail.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38204-2024 tillsynsbegäran.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38204-2024 tillsynsbegäran mail.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 19851-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S 1323-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45771</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>4.9</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 52381-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45609</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S 1323-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45771</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/S 1323-2025 artfynd.xlsx", "S 1323-2025")</f>
         <v/>
@@ -2057,7 +2057,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 23268-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45222</v>
+        <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,11 +2088,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11.2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2125,49 +2125,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45161</v>
+        <v>45818</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2237,42 +2237,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45231</v>
+        <v>46045</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2301,14 +2301,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2338,46 +2343,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23268-2022</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2396,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44720</v>
+        <v>45566</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,23 +2411,18 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2452,35 +2452,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         <v>46127</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45075</v>
+        <v>45222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,8 +2845,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2879,53 +2884,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2939,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45566</v>
+        <v>45714</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2964,13 +2965,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2982,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2991,46 +2992,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3044,10 +3045,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46045</v>
+        <v>44494</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3061,86 +3062,86 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3154,10 +3155,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46202</v>
+        <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3169,19 +3170,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3215,42 +3211,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3264,10 +3260,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44494</v>
+        <v>46202</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,13 +3281,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3300,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3309,58 +3305,58 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3374,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45714</v>
+        <v>45231</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3390,10 +3386,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3405,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3414,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3426,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46230</v>
+        <v>45075</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,7 +3491,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3507,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3519,62 +3515,62 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3588,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45818</v>
+        <v>46230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,20 +3600,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3628,51 +3624,55 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59883-2021</t>
+          <t>A 70949-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44494</v>
+        <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4309,11 +4309,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 6068-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44476</v>
+        <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 34676-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4507,7 +4507,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 59883-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45090</v>
+        <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4536,8 +4536,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4580,7 +4585,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 70949-2021</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44538</v>
+        <v>44795</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4611,11 +4616,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4658,7 +4663,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4672,10 +4677,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45090</v>
+        <v>44476</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4693,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4731,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6068-2022</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4745,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44599</v>
+        <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4804,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4818,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45183</v>
+        <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4839,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4877,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34676-2022</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4891,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44795</v>
+        <v>45002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4906,13 +4911,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45243</v>
+        <v>45524</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45720</v>
+        <v>45524</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5062,8 +5062,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5106,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45394</v>
+        <v>44538</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5137,11 +5142,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5184,7 +5189,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5198,10 +5203,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45252</v>
+        <v>45160</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5213,13 +5218,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44809</v>
+        <v>45566</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5291,13 +5291,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5340,7 +5335,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5350,14 +5345,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45883</v>
+        <v>45630</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5370,7 +5365,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5413,7 +5408,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5427,10 +5422,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45231</v>
+        <v>45243</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5442,8 +5437,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>9.5</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44974</v>
+        <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44974</v>
+        <v>45166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45251</v>
+        <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,8 +5661,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5705,7 +5710,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46079</v>
+        <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,8 +5739,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5778,7 +5788,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5792,10 +5802,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45470</v>
+        <v>45019</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5807,13 +5817,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5856,7 +5861,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5866,14 +5871,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45483</v>
+        <v>45804</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5887,11 +5892,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>6.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5934,7 +5939,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5948,10 +5953,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45265</v>
+        <v>45089</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5964,7 +5969,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6007,7 +6012,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6021,10 +6026,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45824</v>
+        <v>45707</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6036,13 +6041,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6085,7 +6085,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45103</v>
+        <v>45478</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44515</v>
+        <v>45183</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6231,7 +6231,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45176</v>
+        <v>45090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6304,7 +6304,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45566</v>
+        <v>45603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45548</v>
+        <v>45103</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45899</v>
+        <v>45824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6479,8 +6479,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6540,7 +6545,7 @@
         <v>45632</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6558,7 +6563,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6601,7 +6606,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6615,10 +6620,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45252</v>
+        <v>44494</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6632,11 +6637,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6679,7 +6684,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6693,10 +6698,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44908</v>
+        <v>45548</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6709,7 +6714,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6752,7 +6757,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6766,10 +6771,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45908</v>
+        <v>45899</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,13 +6786,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6830,7 +6830,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45589</v>
+        <v>45002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6917,10 +6917,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45916</v>
+        <v>45908</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45742</v>
+        <v>45257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7068,10 +7068,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44895</v>
+        <v>45742</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7127,7 +7127,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44595</v>
+        <v>45834</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7200,7 +7200,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7210,14 +7210,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45919</v>
+        <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7229,8 +7229,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7273,7 +7278,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7283,14 +7288,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45919</v>
+        <v>45834</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7303,7 +7308,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7346,7 +7351,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7360,10 +7365,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45566</v>
+        <v>44537</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7376,7 +7381,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7419,7 +7424,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7433,10 +7438,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45565</v>
+        <v>45916</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7448,8 +7453,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7492,7 +7502,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7506,10 +7516,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45002</v>
+        <v>45575</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7522,7 +7532,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7565,7 +7575,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7579,10 +7589,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44937</v>
+        <v>45919</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7595,7 +7605,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7638,7 +7648,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7652,10 +7662,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45930</v>
+        <v>45919</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7668,7 +7678,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7711,7 +7721,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7725,10 +7735,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45566</v>
+        <v>44895</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7741,7 +7751,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7784,7 +7794,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7798,10 +7808,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45930</v>
+        <v>44974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7814,7 +7824,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7857,7 +7867,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7871,10 +7881,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46127</v>
+        <v>44974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7886,13 +7896,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7935,7 +7940,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7949,10 +7954,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45575</v>
+        <v>44944</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7964,8 +7969,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8008,7 +8018,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8022,10 +8032,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44906</v>
+        <v>45169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8037,8 +8047,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8081,7 +8096,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8095,10 +8110,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44503</v>
+        <v>45716</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8110,13 +8125,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8159,7 +8169,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8173,10 +8183,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45933</v>
+        <v>45930</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8189,7 +8199,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8232,7 +8242,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8246,10 +8256,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44664</v>
+        <v>45589</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8261,13 +8271,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8310,7 +8315,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8324,10 +8329,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45940</v>
+        <v>45394</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8339,8 +8344,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8383,7 +8393,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8397,10 +8407,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45942</v>
+        <v>45930</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8413,7 +8423,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8456,7 +8466,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8470,10 +8480,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44906</v>
+        <v>45265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8486,7 +8496,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8529,7 +8539,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8543,10 +8553,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45209</v>
+        <v>44906</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8559,7 +8569,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8602,7 +8612,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8616,10 +8626,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45933</v>
+        <v>45862</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8631,13 +8641,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>9.4</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8680,7 +8685,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8694,10 +8699,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45589</v>
+        <v>45933</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8710,7 +8715,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8753,7 +8758,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8767,10 +8772,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45524</v>
+        <v>44687</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8782,13 +8787,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44929</v>
+        <v>46045</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8860,8 +8860,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8900,35 +8905,11 @@
         <v>0</v>
       </c>
       <c r="V99" s="2" t="inlineStr"/>
-      <c r="X99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD99">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8942,10 +8923,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45755</v>
+        <v>46045</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8957,8 +8938,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>14.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9001,7 +8987,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9015,10 +9001,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45369</v>
+        <v>46045</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9030,8 +9016,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9074,7 +9065,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9088,10 +9079,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44785</v>
+        <v>45942</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9101,11 +9092,6 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -9152,7 +9138,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9166,10 +9152,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45614</v>
+        <v>45940</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9182,7 +9168,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9225,7 +9211,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9235,14 +9221,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45401</v>
+        <v>45883</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9255,7 +9241,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9298,7 +9284,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9312,10 +9298,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45489</v>
+        <v>44944</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9327,8 +9313,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9371,7 +9362,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9385,10 +9376,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45973</v>
+        <v>46052</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9401,7 +9392,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9444,7 +9435,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9458,10 +9449,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44494</v>
+        <v>46055</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9473,13 +9464,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9522,7 +9508,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9536,10 +9522,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45436</v>
+        <v>44937</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9552,7 +9538,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9595,7 +9581,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9609,10 +9595,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45980</v>
+        <v>45566</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9625,7 +9611,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9668,7 +9654,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,14 +9664,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45531</v>
+        <v>45614</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9697,13 +9683,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9746,7 +9727,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9760,10 +9741,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44939</v>
+        <v>46010</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9775,8 +9756,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9819,7 +9805,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9833,10 +9819,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45257</v>
+        <v>45524</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9848,8 +9834,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9892,7 +9883,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9906,10 +9897,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45002</v>
+        <v>45176</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9922,7 +9913,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9965,7 +9956,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9979,10 +9970,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46142</v>
+        <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9996,11 +9987,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10043,7 +10034,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10057,10 +10048,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44900</v>
+        <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10072,8 +10063,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10116,7 +10112,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10130,10 +10126,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45988</v>
+        <v>46010</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10145,8 +10141,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10189,7 +10190,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10203,10 +10204,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44755</v>
+        <v>46062</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10219,7 +10220,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10262,7 +10263,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10276,10 +10277,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45992</v>
+        <v>46069</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10293,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10335,7 +10336,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10349,10 +10350,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44727</v>
+        <v>45973</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,7 +10366,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10408,7 +10409,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10422,10 +10423,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45089</v>
+        <v>44944</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10437,8 +10438,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10481,7 +10487,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10495,10 +10501,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46143</v>
+        <v>45369</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10517,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>14.6</v>
+        <v>0.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10554,7 +10560,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10568,10 +10574,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45169</v>
+        <v>45980</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10583,13 +10589,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10632,7 +10633,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10646,10 +10647,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45090</v>
+        <v>45470</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10661,8 +10662,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10705,7 +10711,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10719,10 +10725,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45453</v>
+        <v>44795</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10734,8 +10740,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10778,7 +10789,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10792,10 +10803,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46153</v>
+        <v>45090</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10819,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10851,7 +10862,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10865,10 +10876,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46006</v>
+        <v>45988</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10880,13 +10891,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10929,7 +10935,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10943,10 +10949,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10958,13 +10964,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11007,7 +11008,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11021,10 +11022,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45229</v>
+        <v>45992</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11037,7 +11038,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11080,7 +11081,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11094,10 +11095,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45890</v>
+        <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11110,7 +11111,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11153,7 +11154,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11167,10 +11168,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44687</v>
+        <v>46006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11182,8 +11183,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11226,7 +11232,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11240,10 +11246,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46021</v>
+        <v>46006</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11255,8 +11261,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11299,7 +11310,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11313,10 +11324,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46021</v>
+        <v>44727</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11329,7 +11340,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11372,7 +11383,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11386,10 +11397,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46021</v>
+        <v>45233</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11402,7 +11413,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11445,7 +11456,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11459,10 +11470,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44906</v>
+        <v>46021</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11475,7 +11486,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11518,7 +11529,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11532,10 +11543,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45251</v>
+        <v>46021</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11548,7 +11559,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11591,7 +11602,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11605,10 +11616,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44538</v>
+        <v>46021</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11620,13 +11631,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11669,7 +11675,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11683,10 +11689,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45566</v>
+        <v>45489</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11699,7 +11705,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11742,7 +11748,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11756,10 +11762,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45089</v>
+        <v>45742</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11815,7 +11821,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11829,10 +11835,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46170</v>
+        <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11845,7 +11851,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11888,7 +11894,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24724-2026</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11902,10 +11908,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46171</v>
+        <v>45090</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11917,13 +11923,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11966,7 +11967,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11980,10 +11981,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46171</v>
+        <v>45218</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12001,7 +12002,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12044,7 +12045,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12058,10 +12059,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46045</v>
+        <v>45720</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12073,13 +12074,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12122,7 +12118,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12132,14 +12128,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46045</v>
+        <v>45631</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12153,11 +12149,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12200,7 +12196,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12214,10 +12210,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46045</v>
+        <v>45561</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12229,13 +12225,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>14.3</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12278,7 +12269,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12292,10 +12283,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44809</v>
+        <v>46127</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12313,7 +12304,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12356,7 +12347,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12370,10 +12361,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46052</v>
+        <v>45386</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12386,7 +12377,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12429,7 +12420,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12443,10 +12434,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44972</v>
+        <v>45252</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12458,8 +12449,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12502,7 +12498,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12516,10 +12512,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46055</v>
+        <v>44906</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12532,7 +12528,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12575,7 +12571,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12589,10 +12585,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44944</v>
+        <v>45209</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12604,13 +12600,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12653,7 +12644,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12667,10 +12658,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45098</v>
+        <v>45589</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12683,7 +12674,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12726,7 +12717,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12740,10 +12731,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45169</v>
+        <v>45755</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12755,13 +12746,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12804,7 +12790,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12818,10 +12804,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46181</v>
+        <v>45933</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12833,8 +12819,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12877,7 +12868,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12891,10 +12882,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45394</v>
+        <v>44972</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12906,13 +12897,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12955,7 +12941,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12969,10 +12955,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46010</v>
+        <v>44785</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12986,11 +12972,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13033,7 +13019,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13043,14 +13029,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46010</v>
+        <v>45531</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13064,11 +13050,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13111,7 +13097,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13121,14 +13107,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46062</v>
+        <v>45076</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13141,7 +13127,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13184,7 +13170,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13198,10 +13184,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45078</v>
+        <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13214,7 +13200,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13257,7 +13243,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13271,10 +13257,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44537</v>
+        <v>46143</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13287,7 +13273,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>14.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13330,7 +13316,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13344,10 +13330,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46010</v>
+        <v>46142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13361,11 +13347,11 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13408,7 +13394,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13422,10 +13408,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46010</v>
+        <v>45251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13437,13 +13423,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13486,7 +13467,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13500,10 +13481,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44944</v>
+        <v>44900</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13515,13 +13496,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13564,7 +13540,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13578,10 +13554,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46069</v>
+        <v>44809</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13593,8 +13569,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13637,7 +13618,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13647,14 +13628,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46188</v>
+        <v>45483</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13672,7 +13653,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13715,7 +13696,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13729,10 +13710,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45575</v>
+        <v>45719</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13745,7 +13726,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13788,7 +13769,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13802,10 +13783,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45166</v>
+        <v>46153</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13818,7 +13799,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13861,7 +13842,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13875,10 +13856,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45166</v>
+        <v>45229</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13891,7 +13872,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13934,7 +13915,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13944,14 +13925,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46188</v>
+        <v>44929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13963,13 +13944,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>12.6</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14008,11 +13984,35 @@
         <v>0</v>
       </c>
       <c r="V167" s="2" t="inlineStr"/>
+      <c r="X167">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y167">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA167">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB167">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC167">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD167">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14026,10 +14026,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46188</v>
+        <v>45890</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14041,13 +14041,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14090,7 +14085,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14104,10 +14099,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45394</v>
+        <v>44755</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14119,13 +14114,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14168,7 +14158,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14182,10 +14172,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44795</v>
+        <v>45243</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14246,7 +14236,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14256,14 +14246,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45632</v>
+        <v>44908</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14275,13 +14265,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14324,7 +14309,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14338,10 +14323,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45524</v>
+        <v>46170</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14353,13 +14338,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14402,7 +14382,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14412,14 +14392,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45524</v>
+        <v>45631</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14433,11 +14413,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14480,7 +14460,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 24724-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14494,10 +14474,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45524</v>
+        <v>46171</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14511,11 +14491,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.1</v>
+        <v>6.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14558,7 +14538,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14572,10 +14552,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45019</v>
+        <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14587,8 +14567,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14631,7 +14616,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14645,10 +14630,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44494</v>
+        <v>45707</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14660,13 +14645,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14709,7 +14689,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14723,10 +14703,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44494</v>
+        <v>45252</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14740,11 +14720,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14787,7 +14767,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14797,14 +14777,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44944</v>
+        <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14818,11 +14798,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14865,7 +14845,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14879,10 +14859,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45719</v>
+        <v>46181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14895,7 +14875,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14938,7 +14918,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14952,10 +14932,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44531</v>
+        <v>45394</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14967,8 +14947,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15011,7 +14996,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15021,14 +15006,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45631</v>
+        <v>46188</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15046,7 +15031,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>12.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15089,7 +15074,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15103,10 +15088,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45742</v>
+        <v>46188</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15118,8 +15103,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15162,7 +15152,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15176,10 +15166,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46206</v>
+        <v>46188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15191,8 +15181,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15235,7 +15230,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15249,10 +15244,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46160</v>
+        <v>45209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15264,13 +15259,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15313,7 +15303,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15323,14 +15313,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45076</v>
+        <v>44494</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15342,8 +15332,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15386,7 +15381,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15400,10 +15395,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46210</v>
+        <v>44906</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15415,13 +15410,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15464,7 +15454,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15478,10 +15468,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15493,13 +15483,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15542,7 +15527,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15552,14 +15537,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45630</v>
+        <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15572,7 +15557,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15615,7 +15600,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15629,10 +15614,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45561</v>
+        <v>45089</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15645,7 +15630,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15688,7 +15673,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15702,10 +15687,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45233</v>
+        <v>45524</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15717,8 +15702,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15761,7 +15751,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15775,10 +15765,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45218</v>
+        <v>46160</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15796,7 +15786,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15839,7 +15829,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15853,10 +15843,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46260</v>
+        <v>46210</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15868,8 +15858,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15912,7 +15907,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15926,10 +15921,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45209</v>
+        <v>46210</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15941,8 +15936,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15985,7 +15985,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15995,14 +15995,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45243</v>
+        <v>45401</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16014,13 +16014,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16063,7 +16058,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16077,10 +16072,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45243</v>
+        <v>44494</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16092,8 +16087,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16136,7 +16136,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16150,10 +16150,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45603</v>
+        <v>46260</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16209,7 +16209,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16223,10 +16223,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45160</v>
+        <v>45098</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16282,7 +16282,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16296,10 +16296,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45478</v>
+        <v>45231</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16355,7 +16355,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16369,10 +16369,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46230</v>
+        <v>45575</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16428,7 +16428,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45386</v>
+        <v>45078</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16501,7 +16501,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16515,10 +16515,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46191</v>
+        <v>45566</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16588,10 +16588,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45561</v>
+        <v>45251</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16661,10 +16661,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45707</v>
+        <v>44809</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16676,8 +16676,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16720,7 +16725,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16734,10 +16739,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46276</v>
+        <v>45243</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16750,7 +16755,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16793,7 +16798,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16803,14 +16808,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45631</v>
+        <v>44939</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16822,13 +16827,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44469</v>
+        <v>46230</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16944,7 +16944,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45617</v>
+        <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45786</v>
+        <v>45565</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17046,13 +17046,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>8.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17095,7 +17090,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17109,10 +17104,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45789</v>
+        <v>45169</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17124,8 +17119,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17168,7 +17168,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17182,10 +17182,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45721</v>
+        <v>45566</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17241,7 +17241,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45680</v>
+        <v>46276</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45527</v>
+        <v>44664</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17343,8 +17343,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17387,7 +17392,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17401,10 +17406,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45630</v>
+        <v>45436</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17416,13 +17421,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17465,7 +17465,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17479,10 +17479,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45804</v>
+        <v>44469</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17494,13 +17494,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17543,7 +17538,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17557,10 +17552,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45707</v>
+        <v>45617</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17573,7 +17568,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17616,7 +17611,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17630,10 +17625,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45834</v>
+        <v>45786</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17645,8 +17640,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17689,7 +17689,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17699,14 +17699,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45834</v>
+        <v>45789</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17762,7 +17762,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17772,14 +17772,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45835</v>
+        <v>45721</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17791,13 +17791,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17840,7 +17835,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17854,10 +17849,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45716</v>
+        <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17869,8 +17864,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17913,7 +17913,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17927,10 +17927,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45265</v>
+        <v>45527</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17986,7 +17986,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45862</v>
+        <v>45680</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52381-2024</t>
+          <t>A 19851-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45609</v>
+        <v>45771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,8 +1636,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1670,357 +1675,352 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52381-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45609</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 43626-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45184</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.7</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallfingersvamp</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 19851-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S 1323-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45771</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>4.9</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S 1323-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45771</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/S 1323-2025 artfynd.xlsx", "S 1323-2025")</f>
         <v/>
@@ -2074,7 +2074,7 @@
         <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45818</v>
+        <v>46127</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,11 +2196,16 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -2237,42 +2242,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2291,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46045</v>
+        <v>45824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2301,19 +2306,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2340,49 +2340,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45566</v>
+        <v>45075</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,16 +2412,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2452,42 +2452,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2505,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46127</v>
+        <v>45713</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2518,17 +2522,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2558,46 +2562,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2611,10 +2619,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45824</v>
+        <v>45566</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2627,17 +2635,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2651,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2660,49 +2668,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2716,10 +2724,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45713</v>
+        <v>44494</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2733,27 +2741,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9.5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -2761,62 +2769,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2834,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45222</v>
+        <v>45714</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,29 +2849,24 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -2875,58 +2874,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2939,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45714</v>
+        <v>46202</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,14 +2954,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2971,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2980,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2996,42 +3000,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3045,10 +3049,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44494</v>
+        <v>45222</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3062,14 +3066,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3081,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3090,10 +3094,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3102,39 +3106,39 @@
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
@@ -3158,7 +3162,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3250,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3260,10 +3264,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46202</v>
+        <v>45231</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3275,19 +3279,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3317,46 +3316,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3369,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45231</v>
+        <v>46230</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,7 +3385,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3398,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3410,58 +3409,62 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3478,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45075</v>
+        <v>46045</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,14 +3493,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3527,50 +3535,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3584,10 +3588,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46230</v>
+        <v>45818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,19 +3604,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3624,55 +3628,51 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44795</v>
+        <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4614,13 +4614,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4663,7 +4658,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4677,10 +4672,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44476</v>
+        <v>44795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4692,8 +4687,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45453</v>
+        <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44595</v>
+        <v>45090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45002</v>
+        <v>45394</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4911,8 +4911,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4960,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45524</v>
+        <v>45243</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,11 +4991,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5033,7 +5038,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5047,10 +5052,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45524</v>
+        <v>45231</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5062,13 +5067,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44538</v>
+        <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5140,13 +5140,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5189,7 +5184,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5203,10 +5198,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45160</v>
+        <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5219,7 +5214,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5262,7 +5257,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5276,10 +5271,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45566</v>
+        <v>44974</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5292,7 +5287,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5335,7 +5330,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5345,14 +5340,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45630</v>
+        <v>45470</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5364,8 +5359,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5418,14 +5418,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45243</v>
+        <v>45483</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5486,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45166</v>
+        <v>45265</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45166</v>
+        <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44503</v>
+        <v>45176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,13 +5661,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5710,7 +5705,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45394</v>
+        <v>45548</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5739,13 +5734,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5788,7 +5778,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5798,14 +5788,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45019</v>
+        <v>45632</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5817,8 +5807,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5861,7 +5856,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5875,10 +5870,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45804</v>
+        <v>44908</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5890,13 +5885,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5939,7 +5929,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5953,10 +5943,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45089</v>
+        <v>45589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5969,7 +5959,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6012,7 +6002,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6026,10 +6016,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45707</v>
+        <v>45742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6042,7 +6032,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6085,7 +6075,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6099,10 +6089,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45478</v>
+        <v>44595</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6115,7 +6105,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6158,7 +6148,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6172,10 +6162,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45183</v>
+        <v>45566</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6188,7 +6178,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6231,7 +6221,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6245,10 +6235,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45090</v>
+        <v>45565</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6261,7 +6251,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6304,7 +6294,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6318,10 +6308,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45603</v>
+        <v>45002</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6334,7 +6324,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6377,7 +6367,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6391,10 +6381,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45103</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6407,7 +6397,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6450,7 +6440,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6464,10 +6454,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45824</v>
+        <v>46069</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6479,13 +6469,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6528,7 +6513,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6538,14 +6523,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45632</v>
+        <v>45566</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6557,13 +6542,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6606,7 +6586,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6620,10 +6600,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44494</v>
+        <v>45575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,13 +6615,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6684,7 +6659,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6698,10 +6673,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45548</v>
+        <v>46079</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6714,7 +6689,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6757,7 +6732,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6771,10 +6746,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45899</v>
+        <v>45834</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6787,7 +6762,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6830,7 +6805,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6844,10 +6819,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45002</v>
+        <v>44906</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6860,7 +6835,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6903,7 +6878,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6913,14 +6888,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45908</v>
+        <v>45834</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6932,13 +6907,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6981,7 +6951,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6995,10 +6965,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45257</v>
+        <v>45209</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7011,7 +6981,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7054,7 +7024,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7064,14 +7034,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45742</v>
+        <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7083,8 +7053,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7127,7 +7102,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7141,10 +7116,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45834</v>
+        <v>45589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7157,7 +7132,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7200,7 +7175,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7210,14 +7185,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45835</v>
+        <v>45524</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7231,11 +7206,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7278,7 +7253,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7292,10 +7267,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45834</v>
+        <v>44929</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7308,7 +7283,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7347,11 +7322,35 @@
         <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr"/>
+      <c r="X78">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y78">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA78">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB78">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC78">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD78">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7365,10 +7364,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44537</v>
+        <v>45716</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7381,7 +7380,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7424,7 +7423,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7438,10 +7437,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45916</v>
+        <v>45265</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7453,13 +7452,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7502,7 +7496,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7516,10 +7510,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45575</v>
+        <v>45369</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7532,7 +7526,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7575,7 +7569,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7589,10 +7583,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45919</v>
+        <v>45862</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7605,7 +7599,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7648,7 +7642,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7662,10 +7656,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45919</v>
+        <v>45614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7678,7 +7672,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7721,7 +7715,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7735,10 +7729,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44895</v>
+        <v>45824</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7750,8 +7744,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7794,7 +7793,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7808,10 +7807,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44974</v>
+        <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7824,7 +7823,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7867,7 +7866,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7881,10 +7880,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44974</v>
+        <v>45257</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7897,7 +7896,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7940,7 +7939,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7954,10 +7953,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44944</v>
+        <v>46127</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7971,11 +7970,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8018,7 +8017,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8032,10 +8031,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45169</v>
+        <v>45002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8047,13 +8046,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8096,7 +8090,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8110,10 +8104,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45716</v>
+        <v>44900</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8126,7 +8120,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8169,7 +8163,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8183,10 +8177,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45930</v>
+        <v>45899</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8199,7 +8193,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8242,7 +8236,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8256,10 +8250,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45589</v>
+        <v>44755</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8272,7 +8266,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8315,7 +8309,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8329,10 +8323,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45394</v>
+        <v>44727</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8344,13 +8338,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8393,7 +8382,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8407,10 +8396,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45930</v>
+        <v>45169</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8422,8 +8411,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8466,7 +8460,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8480,10 +8474,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45265</v>
+        <v>45908</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8495,8 +8489,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8539,7 +8538,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8553,10 +8552,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44906</v>
+        <v>45883</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8569,7 +8568,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8612,7 +8611,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8626,10 +8625,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45862</v>
+        <v>45916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8641,8 +8640,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8685,7 +8689,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8699,10 +8703,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45933</v>
+        <v>45453</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8715,7 +8719,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8758,7 +8762,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8772,10 +8776,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44687</v>
+        <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8787,8 +8791,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8831,7 +8840,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8845,10 +8854,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46045</v>
+        <v>45919</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8860,13 +8869,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8909,7 +8913,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8923,10 +8927,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46045</v>
+        <v>45919</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8938,13 +8942,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>14.3</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8987,7 +8986,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9001,10 +9000,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46045</v>
+        <v>45229</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9016,13 +9015,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9065,7 +9059,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9079,10 +9073,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45942</v>
+        <v>45755</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9095,7 +9089,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9138,7 +9132,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9152,10 +9146,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45940</v>
+        <v>44785</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9167,8 +9161,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9211,7 +9210,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9225,10 +9224,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45883</v>
+        <v>45251</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9241,7 +9240,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9284,7 +9283,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9294,14 +9293,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44944</v>
+        <v>45531</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9315,11 +9314,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9362,7 +9361,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9376,10 +9375,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46052</v>
+        <v>44538</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9391,8 +9390,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9435,7 +9439,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9449,10 +9453,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46055</v>
+        <v>45566</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9465,7 +9469,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7.3</v>
+        <v>5.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9508,7 +9512,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9522,10 +9526,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44937</v>
+        <v>45930</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9538,7 +9542,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9581,7 +9585,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9595,10 +9599,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45566</v>
+        <v>45089</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9611,7 +9615,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9654,7 +9658,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9668,10 +9672,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45614</v>
+        <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9684,7 +9688,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9727,7 +9731,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9741,10 +9745,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46010</v>
+        <v>46142</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9758,11 +9762,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9805,7 +9809,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9819,10 +9823,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45524</v>
+        <v>46143</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9834,13 +9838,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>14.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9883,7 +9882,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9897,10 +9896,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45176</v>
+        <v>46153</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9913,7 +9912,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9956,7 +9955,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9970,10 +9969,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46010</v>
+        <v>44944</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9987,11 +9986,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10034,7 +10033,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10048,10 +10047,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46010</v>
+        <v>45098</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,13 +10062,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10112,7 +10106,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10126,10 +10120,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46010</v>
+        <v>45169</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10143,11 +10137,11 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10190,7 +10184,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10204,10 +10198,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46062</v>
+        <v>45394</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10219,8 +10213,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10263,7 +10262,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10277,10 +10276,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46069</v>
+        <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10293,7 +10292,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10336,7 +10335,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10350,10 +10349,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45973</v>
+        <v>45078</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10366,7 +10365,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10409,7 +10408,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10423,10 +10422,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44944</v>
+        <v>44537</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,13 +10437,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10487,7 +10481,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10501,10 +10495,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45369</v>
+        <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10517,7 +10511,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10560,7 +10554,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10574,10 +10568,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45980</v>
+        <v>44944</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10589,8 +10583,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10633,7 +10632,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10647,10 +10646,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45470</v>
+        <v>45940</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10662,13 +10661,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10711,7 +10705,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10725,10 +10719,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44795</v>
+        <v>45575</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10740,13 +10734,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10789,7 +10778,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10803,10 +10792,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45090</v>
+        <v>45942</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10819,7 +10808,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10862,7 +10851,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10876,10 +10865,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45988</v>
+        <v>46170</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10935,7 +10924,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10949,10 +10938,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46079</v>
+        <v>45524</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10964,8 +10953,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11008,7 +11002,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11022,10 +11016,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45992</v>
+        <v>45524</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11037,8 +11031,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11081,7 +11080,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11095,10 +11094,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45561</v>
+        <v>45524</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11110,8 +11109,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11154,7 +11158,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 24724-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11168,10 +11172,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46006</v>
+        <v>46171</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11189,7 +11193,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11232,7 +11236,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11246,10 +11250,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46006</v>
+        <v>46171</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11267,7 +11271,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11310,7 +11314,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11324,10 +11328,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44727</v>
+        <v>44494</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11339,8 +11343,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11383,7 +11392,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11397,10 +11406,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45233</v>
+        <v>44494</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11412,8 +11421,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11456,7 +11470,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11470,10 +11484,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46021</v>
+        <v>45719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11486,7 +11500,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11529,7 +11543,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11543,10 +11557,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46021</v>
+        <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11559,7 +11573,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11602,7 +11616,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11616,10 +11630,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46021</v>
+        <v>46188</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11631,8 +11645,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11675,7 +11694,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11689,10 +11708,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45489</v>
+        <v>44531</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11705,7 +11724,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11748,7 +11767,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11762,10 +11781,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45742</v>
+        <v>46188</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11777,8 +11796,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>12.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11821,7 +11845,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11835,10 +11859,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44515</v>
+        <v>46188</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11850,8 +11874,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11894,7 +11923,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11904,14 +11933,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45090</v>
+        <v>45631</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11923,8 +11952,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11967,7 +12001,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11981,10 +12015,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45218</v>
+        <v>45742</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11996,13 +12030,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12045,7 +12074,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12055,14 +12084,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45720</v>
+        <v>45076</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12075,7 +12104,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12118,7 +12147,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12128,14 +12157,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45631</v>
+        <v>45561</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12147,13 +12176,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12196,7 +12220,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12210,10 +12234,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45561</v>
+        <v>45233</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12226,7 +12250,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12269,7 +12293,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12283,10 +12307,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46127</v>
+        <v>45973</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12298,13 +12322,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12347,7 +12366,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12361,10 +12380,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45386</v>
+        <v>45218</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12376,8 +12395,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12420,7 +12444,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12434,10 +12458,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45252</v>
+        <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,13 +12473,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12498,7 +12517,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12512,10 +12531,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44906</v>
+        <v>45243</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12527,8 +12546,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12571,7 +12595,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12585,10 +12609,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45209</v>
+        <v>46206</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12601,7 +12625,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12644,7 +12668,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12658,10 +12682,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45589</v>
+        <v>46160</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12673,8 +12697,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12717,7 +12746,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12731,10 +12760,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45755</v>
+        <v>45183</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12747,7 +12776,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12790,7 +12819,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12804,10 +12833,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45933</v>
+        <v>46210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12825,7 +12854,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>9.4</v>
+        <v>3.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12868,7 +12897,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12882,10 +12911,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44972</v>
+        <v>46210</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12897,8 +12926,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12941,7 +12975,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12955,10 +12989,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44785</v>
+        <v>45988</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12970,13 +13004,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13019,7 +13048,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13029,14 +13058,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45531</v>
+        <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13048,13 +13077,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>9.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13097,7 +13121,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13107,14 +13131,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45076</v>
+        <v>45252</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,8 +13150,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13170,7 +13199,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13184,10 +13213,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45265</v>
+        <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13200,7 +13229,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13243,7 +13272,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13257,10 +13286,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46143</v>
+        <v>44809</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,8 +13301,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>14.6</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13316,7 +13350,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13330,10 +13364,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46142</v>
+        <v>46260</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,13 +13379,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13394,7 +13423,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13408,10 +13437,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45251</v>
+        <v>46006</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13423,8 +13452,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13467,7 +13501,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13481,10 +13515,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44900</v>
+        <v>46006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13496,8 +13530,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13540,7 +13579,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13554,10 +13593,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44809</v>
+        <v>45566</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13569,13 +13608,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13618,7 +13652,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13628,14 +13662,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45483</v>
+        <v>45252</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13649,11 +13683,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13696,7 +13730,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13710,10 +13744,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45719</v>
+        <v>44895</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13726,7 +13760,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13769,7 +13803,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13783,10 +13817,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46153</v>
+        <v>44906</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13799,7 +13833,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13842,7 +13876,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13856,10 +13890,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45229</v>
+        <v>46230</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13872,7 +13906,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13915,7 +13949,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13925,14 +13959,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44929</v>
+        <v>46191</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13945,7 +13979,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13984,35 +14018,11 @@
         <v>0</v>
       </c>
       <c r="V167" s="2" t="inlineStr"/>
-      <c r="X167">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y167">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA167">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB167">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC167">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD167">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14026,10 +14036,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45890</v>
+        <v>44503</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14041,8 +14051,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14085,7 +14100,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14099,10 +14114,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44755</v>
+        <v>44664</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14114,8 +14129,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14158,7 +14178,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14172,10 +14192,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45243</v>
+        <v>46021</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14187,13 +14207,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14236,7 +14251,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14250,10 +14265,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44908</v>
+        <v>46021</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14266,7 +14281,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14309,7 +14324,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14323,10 +14338,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46170</v>
+        <v>46021</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14339,7 +14354,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14382,7 +14397,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14392,14 +14407,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45631</v>
+        <v>46276</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14411,13 +14426,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14460,7 +14470,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 24724-2026</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14470,14 +14480,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46171</v>
+        <v>45401</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14489,13 +14499,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14538,7 +14543,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14552,10 +14557,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46171</v>
+        <v>45489</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14567,13 +14572,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14616,7 +14616,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45707</v>
+        <v>44494</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14645,8 +14645,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14689,7 +14694,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14703,10 +14708,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45252</v>
+        <v>45436</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14718,13 +14723,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14767,7 +14767,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14777,14 +14777,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45632</v>
+        <v>44939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14796,13 +14796,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14845,7 +14840,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14859,10 +14854,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46181</v>
+        <v>45089</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14875,7 +14870,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14918,7 +14913,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14932,10 +14927,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45394</v>
+        <v>45090</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14947,13 +14942,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14996,7 +14986,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15010,10 +15000,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46188</v>
+        <v>44687</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15025,13 +15015,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>12.6</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15074,7 +15059,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15088,10 +15073,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46188</v>
+        <v>44906</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15103,13 +15088,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15152,7 +15132,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15166,10 +15146,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46188</v>
+        <v>44809</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15187,7 +15167,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15230,7 +15210,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15244,10 +15224,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45209</v>
+        <v>44972</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15260,7 +15240,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15303,7 +15283,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15317,10 +15297,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44494</v>
+        <v>46045</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15334,11 +15314,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15381,7 +15361,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15395,10 +15375,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44906</v>
+        <v>46045</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15410,8 +15390,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15454,7 +15439,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15468,10 +15453,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46206</v>
+        <v>46045</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15483,8 +15468,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>14.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15527,7 +15517,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15541,10 +15531,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44531</v>
+        <v>45166</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15557,7 +15547,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15600,7 +15590,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15614,10 +15604,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45089</v>
+        <v>45166</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15630,7 +15620,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15673,7 +15663,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15687,10 +15677,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45524</v>
+        <v>46052</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15702,13 +15692,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15751,7 +15736,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15765,10 +15750,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46160</v>
+        <v>46055</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15780,13 +15765,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15829,7 +15809,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15843,10 +15823,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46210</v>
+        <v>45394</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15864,7 +15844,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15907,7 +15887,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15921,10 +15901,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46210</v>
+        <v>44795</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15942,7 +15922,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15985,7 +15965,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15995,14 +15975,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45401</v>
+        <v>45632</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16014,8 +15994,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16058,7 +16043,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16072,10 +16057,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44494</v>
+        <v>46010</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16093,7 +16078,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16136,7 +16121,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16150,10 +16135,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46260</v>
+        <v>46010</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16165,8 +16150,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16209,7 +16199,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16223,10 +16213,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45098</v>
+        <v>46062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16239,7 +16229,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16282,7 +16272,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16296,10 +16286,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45231</v>
+        <v>46010</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16311,8 +16301,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16355,7 +16350,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16369,10 +16364,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45575</v>
+        <v>46010</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16384,8 +16379,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16428,7 +16428,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45078</v>
+        <v>45019</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16501,7 +16501,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16515,10 +16515,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45566</v>
+        <v>44944</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16530,8 +16530,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16574,7 +16579,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16584,14 +16589,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45251</v>
+        <v>45630</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16604,7 +16609,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16647,7 +16652,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16661,10 +16666,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44809</v>
+        <v>45209</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16676,13 +16681,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
         <v>45243</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44939</v>
+        <v>45603</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46230</v>
+        <v>45160</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16944,7 +16944,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46191</v>
+        <v>45478</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45565</v>
+        <v>45386</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17104,10 +17104,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45169</v>
+        <v>45561</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17119,13 +17119,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17168,7 +17163,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17182,10 +17177,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45566</v>
+        <v>45707</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17198,7 +17193,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17241,7 +17236,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17251,14 +17246,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46276</v>
+        <v>45631</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17270,8 +17265,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44664</v>
+        <v>44469</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17343,13 +17343,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17392,7 +17387,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17406,10 +17401,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45436</v>
+        <v>45617</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17422,7 +17417,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17465,7 +17460,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17479,10 +17474,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44469</v>
+        <v>45786</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17494,8 +17489,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17538,7 +17538,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17552,10 +17552,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45617</v>
+        <v>45789</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17611,7 +17611,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17625,10 +17625,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45786</v>
+        <v>45721</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17640,13 +17640,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17689,7 +17684,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17703,10 +17698,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45789</v>
+        <v>45680</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17714,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17762,7 +17757,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17776,10 +17771,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45721</v>
+        <v>45527</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17787,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17852,7 +17847,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17913,7 +17908,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17927,10 +17922,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45527</v>
+        <v>45804</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17942,8 +17937,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17986,7 +17986,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45680</v>
+        <v>45707</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 19851-2025</t>
+          <t>A 52381-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45771</v>
+        <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,13 +1636,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1675,267 +1670,272 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 43626-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45184</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 19851-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52381-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45609</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 43626-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45184</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46127</v>
+        <v>45713</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2238,46 +2238,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2291,10 +2295,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45824</v>
+        <v>45566</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2307,17 +2311,17 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2331,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2340,49 +2344,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,10 +2400,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45075</v>
+        <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2411,8 +2415,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2445,53 +2454,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2505,10 +2510,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45713</v>
+        <v>45714</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,29 +2525,24 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2562,50 +2562,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2619,10 +2615,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45566</v>
+        <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2634,8 +2630,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2644,13 +2645,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2662,55 +2663,55 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2724,10 +2725,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44494</v>
+        <v>46045</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2741,17 +2742,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2760,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2769,58 +2770,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2834,10 +2835,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45714</v>
+        <v>45161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,10 +2851,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2865,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2874,10 +2875,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2890,35 +2891,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
@@ -2942,7 +2943,7 @@
         <v>46202</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3035,7 +3036,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3049,10 +3050,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45222</v>
+        <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3066,17 +3067,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.2</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3103,49 +3104,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3159,10 +3160,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45161</v>
+        <v>45824</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3175,7 +3176,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3208,42 +3209,42 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
@@ -3267,7 +3268,7 @@
         <v>45231</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3355,7 +3356,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3369,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46230</v>
+        <v>45075</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3385,7 +3386,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3397,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3409,62 +3410,62 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3478,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46045</v>
+        <v>46230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3493,26 +3494,21 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3523,51 +3519,55 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
         <v>45818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59883-2021</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44494</v>
+        <v>44795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4538,11 +4538,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4585,7 +4585,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 59883-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44476</v>
+        <v>44494</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4614,8 +4614,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4658,7 +4663,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4672,10 +4677,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44795</v>
+        <v>44476</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4687,13 +4692,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45090</v>
+        <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45090</v>
+        <v>45524</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4838,8 +4838,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4887,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4901,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45394</v>
+        <v>45524</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4913,11 +4918,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4960,7 +4965,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4974,10 +4979,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45243</v>
+        <v>45453</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4989,13 +4994,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45231</v>
+        <v>45160</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>9.5</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44974</v>
+        <v>44538</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5140,8 +5140,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5184,7 +5189,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5198,10 +5203,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45251</v>
+        <v>44595</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5214,7 +5219,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5257,7 +5262,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5267,14 +5272,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44974</v>
+        <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5287,7 +5292,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5330,7 +5335,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5344,10 +5349,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45470</v>
+        <v>45566</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5359,13 +5364,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.1</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5418,14 +5418,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45483</v>
+        <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5437,13 +5437,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5481,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5495,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45265</v>
+        <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5516,7 +5511,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5559,7 +5554,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44515</v>
+        <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5588,8 +5583,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45176</v>
+        <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,8 +5661,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5705,7 +5710,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45548</v>
+        <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5734,8 +5739,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5778,7 +5788,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5788,14 +5798,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45632</v>
+        <v>45019</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5807,13 +5817,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5856,7 +5861,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5870,10 +5875,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44908</v>
+        <v>45089</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5886,7 +5891,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5929,7 +5934,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5943,10 +5948,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45589</v>
+        <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6002,7 +6007,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6016,10 +6021,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45742</v>
+        <v>45090</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6032,7 +6037,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6075,7 +6080,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6089,10 +6094,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44595</v>
+        <v>45603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6105,7 +6110,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6148,7 +6153,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6162,10 +6167,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45566</v>
+        <v>45183</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6178,7 +6183,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6221,7 +6226,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6231,14 +6236,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45565</v>
+        <v>45632</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6250,8 +6255,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6294,7 +6304,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6308,10 +6318,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45002</v>
+        <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6323,8 +6333,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6367,7 +6382,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6381,10 +6396,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>45548</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6397,7 +6412,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6440,7 +6455,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6454,10 +6469,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46069</v>
+        <v>45257</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6470,7 +6485,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6513,7 +6528,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6527,10 +6542,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45566</v>
+        <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6543,7 +6558,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6586,7 +6601,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6600,10 +6615,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45575</v>
+        <v>45742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6616,7 +6631,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6659,7 +6674,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6673,10 +6688,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46079</v>
+        <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6689,7 +6704,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6732,7 +6747,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6746,10 +6761,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45834</v>
+        <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6762,7 +6777,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6805,7 +6820,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6819,10 +6834,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44906</v>
+        <v>45575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6835,7 +6850,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6878,7 +6893,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6888,14 +6903,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45834</v>
+        <v>44974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6908,7 +6923,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6951,7 +6966,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6965,10 +6980,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45209</v>
+        <v>44974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6981,7 +6996,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7024,7 +7039,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7034,14 +7049,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45835</v>
+        <v>44944</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7055,11 +7070,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7102,7 +7117,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7116,10 +7131,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45589</v>
+        <v>45169</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7131,8 +7146,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7175,7 +7195,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7189,10 +7209,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45524</v>
+        <v>45589</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7204,13 +7224,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7253,7 +7268,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7263,14 +7278,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44929</v>
+        <v>45394</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7282,8 +7297,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7322,35 +7342,11 @@
         <v>0</v>
       </c>
       <c r="V78" s="2" t="inlineStr"/>
-      <c r="X78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD78">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7364,10 +7360,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45716</v>
+        <v>44906</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7380,7 +7376,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7423,7 +7419,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7437,10 +7433,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45265</v>
+        <v>44687</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7453,7 +7449,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7496,7 +7492,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7510,10 +7506,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45369</v>
+        <v>44944</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7525,8 +7521,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7569,7 +7570,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7583,10 +7584,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45862</v>
+        <v>44937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7599,7 +7600,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7642,7 +7643,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7656,10 +7657,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45614</v>
+        <v>45176</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7672,7 +7673,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7715,7 +7716,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7729,10 +7730,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45824</v>
+        <v>45566</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7744,13 +7745,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7793,7 +7789,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7807,10 +7803,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45103</v>
+        <v>45614</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7823,7 +7819,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7866,7 +7862,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7880,10 +7876,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45257</v>
+        <v>45524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7895,8 +7891,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7939,7 +7940,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7953,10 +7954,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46127</v>
+        <v>44944</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7970,11 +7971,11 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8017,7 +8018,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8031,10 +8032,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45002</v>
+        <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8047,7 +8048,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8090,7 +8091,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8104,10 +8105,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44900</v>
+        <v>45470</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8119,8 +8120,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8163,7 +8169,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8177,10 +8183,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45899</v>
+        <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8193,7 +8199,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8236,7 +8242,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8250,10 +8256,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44755</v>
+        <v>45933</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8265,8 +8271,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8309,7 +8320,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8323,10 +8334,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44727</v>
+        <v>44795</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8336,6 +8347,11 @@
       <c r="G92" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -8382,7 +8398,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8396,10 +8412,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45169</v>
+        <v>44785</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8413,11 +8429,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8460,7 +8476,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8474,10 +8490,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45908</v>
+        <v>45090</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8489,13 +8505,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8538,7 +8549,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8548,14 +8559,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45883</v>
+        <v>45531</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8567,8 +8578,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8611,7 +8627,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8625,10 +8641,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45916</v>
+        <v>45103</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8640,13 +8656,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8689,7 +8700,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8703,10 +8714,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45453</v>
+        <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8718,8 +8729,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8762,7 +8778,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8776,10 +8792,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45933</v>
+        <v>45561</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8791,13 +8807,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8840,7 +8851,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8854,10 +8865,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45919</v>
+        <v>45899</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8870,7 +8881,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8913,7 +8924,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8927,10 +8938,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45919</v>
+        <v>45908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8942,8 +8953,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8986,7 +9002,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9000,10 +9016,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45229</v>
+        <v>44727</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9016,7 +9032,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9059,7 +9075,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9073,10 +9089,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45755</v>
+        <v>45233</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9089,7 +9105,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9132,7 +9148,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9146,10 +9162,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44785</v>
+        <v>45916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9163,11 +9179,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9210,7 +9226,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9224,10 +9240,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45251</v>
+        <v>45919</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9240,7 +9256,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9283,7 +9299,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9293,14 +9309,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45531</v>
+        <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9312,13 +9328,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>9.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9361,7 +9372,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9375,10 +9386,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44538</v>
+        <v>45489</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9390,13 +9401,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9439,7 +9445,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9453,10 +9459,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45566</v>
+        <v>45742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9469,7 +9475,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9512,7 +9518,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9526,10 +9532,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45930</v>
+        <v>44515</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9542,7 +9548,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9585,7 +9591,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9599,10 +9605,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45089</v>
+        <v>46143</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9615,7 +9621,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>14.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9658,7 +9664,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9672,10 +9678,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45930</v>
+        <v>46142</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9687,8 +9693,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9731,7 +9742,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9745,10 +9756,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46142</v>
+        <v>45930</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9760,13 +9771,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9809,7 +9815,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9823,10 +9829,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46143</v>
+        <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9839,7 +9845,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>14.6</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9882,7 +9888,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9896,10 +9902,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46153</v>
+        <v>45090</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9912,7 +9918,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9955,7 +9961,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9969,10 +9975,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44944</v>
+        <v>45218</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9986,11 +9992,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10033,7 +10039,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10047,10 +10053,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45098</v>
+        <v>45720</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,7 +10069,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10106,7 +10112,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10120,10 +10126,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45169</v>
+        <v>45933</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10133,11 +10139,6 @@
       <c r="G116" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -10184,7 +10185,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10198,10 +10199,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45394</v>
+        <v>45942</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10213,13 +10214,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10262,7 +10258,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10276,10 +10272,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45933</v>
+        <v>45940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10288,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10335,7 +10331,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10345,14 +10341,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45078</v>
+        <v>45631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10364,8 +10360,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10408,7 +10409,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10422,10 +10423,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44537</v>
+        <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10439,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10481,7 +10482,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10495,10 +10496,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45890</v>
+        <v>45386</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10512,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10554,7 +10555,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10568,10 +10569,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44944</v>
+        <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10589,7 +10590,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10632,7 +10633,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10646,10 +10647,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45940</v>
+        <v>46153</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10662,7 +10663,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10705,7 +10706,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10719,10 +10720,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45575</v>
+        <v>44906</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10736,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10778,7 +10779,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10792,10 +10793,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45942</v>
+        <v>45209</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10809,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10851,7 +10852,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10865,10 +10866,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46170</v>
+        <v>45973</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10881,7 +10882,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10924,7 +10925,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10938,10 +10939,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45524</v>
+        <v>45890</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10953,13 +10954,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11002,7 +10998,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11016,10 +11012,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45524</v>
+        <v>45589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11031,13 +11027,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11080,7 +11071,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11094,10 +11085,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45524</v>
+        <v>45980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11109,13 +11100,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11158,7 +11144,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24724-2026</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11172,10 +11158,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46171</v>
+        <v>44972</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11187,13 +11173,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11236,7 +11217,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11246,14 +11227,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46171</v>
+        <v>45076</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11265,13 +11246,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11314,7 +11290,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11328,10 +11304,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44494</v>
+        <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11343,13 +11319,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11392,7 +11363,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11406,10 +11377,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44494</v>
+        <v>45988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11421,13 +11392,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11470,7 +11436,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11484,10 +11450,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45719</v>
+        <v>45992</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11543,7 +11509,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11557,10 +11523,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46181</v>
+        <v>45251</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11573,7 +11539,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11616,7 +11582,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11630,10 +11596,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46188</v>
+        <v>44900</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11645,13 +11611,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11694,7 +11655,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11708,10 +11669,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44531</v>
+        <v>44809</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11723,8 +11684,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11767,7 +11733,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11777,14 +11743,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46188</v>
+        <v>45483</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11802,7 +11768,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>12.6</v>
+        <v>2.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11845,7 +11811,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11859,10 +11825,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46188</v>
+        <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11880,7 +11846,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11923,7 +11889,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11933,14 +11899,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45631</v>
+        <v>46006</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11958,7 +11924,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12001,7 +11967,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12015,10 +11981,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45742</v>
+        <v>45719</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12031,7 +11997,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12074,7 +12040,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12084,14 +12050,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45076</v>
+        <v>45229</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12104,7 +12070,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12147,7 +12113,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12157,14 +12123,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45561</v>
+        <v>44929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12177,7 +12143,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12216,11 +12182,35 @@
         <v>0</v>
       </c>
       <c r="V143" s="2" t="inlineStr"/>
+      <c r="X143">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y143">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA143">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB143">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC143">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD143">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12234,10 +12224,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45233</v>
+        <v>46021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12250,7 +12240,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12293,7 +12283,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12307,10 +12297,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45973</v>
+        <v>46021</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12323,7 +12313,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12366,7 +12356,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12380,10 +12370,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45218</v>
+        <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12395,13 +12385,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12444,7 +12429,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12458,10 +12443,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45980</v>
+        <v>44755</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12474,7 +12459,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12517,7 +12502,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12531,10 +12516,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45243</v>
+        <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12546,13 +12531,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12595,7 +12575,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12609,10 +12589,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46206</v>
+        <v>45243</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12624,8 +12604,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12668,7 +12653,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 24724-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12682,10 +12667,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12703,7 +12688,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12746,7 +12731,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12760,10 +12745,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45183</v>
+        <v>46171</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12775,8 +12760,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12819,7 +12809,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12833,10 +12823,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46210</v>
+        <v>46045</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12850,11 +12840,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12897,7 +12887,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12911,10 +12901,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46210</v>
+        <v>46045</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12928,11 +12918,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>14.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12975,7 +12965,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12989,10 +12979,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45988</v>
+        <v>46045</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13004,8 +12994,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13048,7 +13043,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13062,10 +13057,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45720</v>
+        <v>44908</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13078,7 +13073,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13121,7 +13116,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13135,10 +13130,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45252</v>
+        <v>46052</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13150,13 +13145,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13199,7 +13189,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13213,10 +13203,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45992</v>
+        <v>46055</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13229,7 +13219,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13272,7 +13262,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13282,14 +13272,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44809</v>
+        <v>45631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13307,7 +13297,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13350,7 +13340,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13364,10 +13354,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46260</v>
+        <v>45707</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13380,7 +13370,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13423,7 +13413,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13437,10 +13427,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13454,11 +13444,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13501,7 +13491,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13515,10 +13505,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13532,11 +13522,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13579,7 +13569,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13593,10 +13583,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45566</v>
+        <v>46010</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13608,8 +13598,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13652,7 +13647,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13666,10 +13661,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45252</v>
+        <v>46010</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13683,11 +13678,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13730,7 +13725,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13744,10 +13739,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44895</v>
+        <v>46062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13760,7 +13755,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13803,7 +13798,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13817,10 +13812,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44906</v>
+        <v>46069</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13833,7 +13828,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13876,7 +13871,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13890,10 +13885,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46230</v>
+        <v>45252</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13905,8 +13900,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13949,7 +13949,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46191</v>
+        <v>46181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14022,7 +14022,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14032,14 +14032,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44503</v>
+        <v>45632</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14100,7 +14100,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14114,10 +14114,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44664</v>
+        <v>46079</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14129,13 +14129,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14178,7 +14173,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14192,10 +14187,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46021</v>
+        <v>46188</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14207,8 +14202,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>2.2</v>
+        <v>12.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14251,7 +14251,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14265,10 +14265,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46021</v>
+        <v>46188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14280,8 +14280,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14324,7 +14329,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14338,10 +14343,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46021</v>
+        <v>45394</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14353,8 +14358,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14397,7 +14407,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14411,10 +14421,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46276</v>
+        <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14426,8 +14436,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14470,7 +14485,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14480,14 +14495,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45401</v>
+        <v>45209</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14500,7 +14515,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14543,7 +14558,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14557,10 +14572,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45489</v>
+        <v>44494</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14572,8 +14587,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14616,7 +14636,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14630,10 +14650,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44494</v>
+        <v>44906</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14645,13 +14665,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14694,7 +14709,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14708,10 +14723,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45436</v>
+        <v>44531</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14724,7 +14739,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14767,7 +14782,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14781,10 +14796,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44939</v>
+        <v>46127</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14796,8 +14811,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14857,7 +14877,7 @@
         <v>45089</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14913,7 +14933,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14927,10 +14947,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45090</v>
+        <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14942,8 +14962,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14986,7 +15011,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14996,14 +15021,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44687</v>
+        <v>45401</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15016,7 +15041,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15059,7 +15084,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15073,10 +15098,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44906</v>
+        <v>44494</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15088,8 +15113,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15132,7 +15162,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15146,10 +15176,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44809</v>
+        <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15161,13 +15191,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15210,7 +15235,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15224,10 +15249,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44972</v>
+        <v>45098</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15240,7 +15265,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15283,7 +15308,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15297,10 +15322,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46045</v>
+        <v>45231</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15312,13 +15337,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15361,7 +15381,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15375,10 +15395,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46045</v>
+        <v>45575</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15390,13 +15410,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15439,7 +15454,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15453,10 +15468,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46045</v>
+        <v>46160</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15470,11 +15485,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>14.3</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15517,7 +15532,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15531,10 +15546,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45166</v>
+        <v>46210</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15546,8 +15561,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15590,7 +15610,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15604,10 +15624,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45166</v>
+        <v>46210</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15619,8 +15639,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15663,7 +15688,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15677,10 +15702,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46052</v>
+        <v>45078</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15693,7 +15718,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15736,7 +15761,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15750,10 +15775,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46055</v>
+        <v>45566</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15766,7 +15791,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15809,7 +15834,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15823,10 +15848,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45394</v>
+        <v>45251</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15838,13 +15863,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15887,7 +15907,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15901,10 +15921,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44795</v>
+        <v>44809</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15922,7 +15942,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15965,7 +15985,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15975,14 +15995,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45632</v>
+        <v>45243</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15994,13 +16014,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16043,7 +16058,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16057,10 +16072,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46010</v>
+        <v>46260</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16072,13 +16087,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16121,7 +16131,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16135,10 +16145,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46010</v>
+        <v>44939</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16150,13 +16160,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16199,7 +16204,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16213,10 +16218,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46062</v>
+        <v>45565</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16229,7 +16234,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16272,7 +16277,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16286,10 +16291,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46010</v>
+        <v>45169</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16303,11 +16308,11 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16350,7 +16355,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16364,10 +16369,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46010</v>
+        <v>45566</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16379,13 +16384,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16428,7 +16428,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16442,10 +16442,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45019</v>
+        <v>44664</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16457,8 +16457,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16501,7 +16506,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16515,10 +16520,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44944</v>
+        <v>45436</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16530,13 +16535,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16579,7 +16579,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16589,14 +16589,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45630</v>
+        <v>46230</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16666,10 +16666,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45209</v>
+        <v>46191</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16739,10 +16739,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45243</v>
+        <v>44469</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45603</v>
+        <v>45617</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16871,7 +16871,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16885,10 +16885,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45160</v>
+        <v>45786</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16900,8 +16900,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16944,7 +16949,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16958,10 +16963,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45478</v>
+        <v>46276</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16974,7 +16979,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +17022,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17036,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45386</v>
+        <v>45789</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17047,7 +17052,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17090,7 +17095,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17104,10 +17109,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45561</v>
+        <v>45721</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17120,7 +17125,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17163,7 +17168,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17177,10 +17182,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45707</v>
+        <v>45630</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17192,8 +17197,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17236,7 +17246,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17246,14 +17256,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45631</v>
+        <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17265,13 +17275,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17319,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17333,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44469</v>
+        <v>45680</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17344,7 +17349,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17387,7 +17392,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17401,10 +17406,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45617</v>
+        <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17416,8 +17421,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17460,7 +17470,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17474,10 +17484,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45786</v>
+        <v>45707</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17489,13 +17499,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17538,7 +17543,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17552,10 +17557,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45789</v>
+        <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17568,7 +17573,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17611,7 +17616,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17621,14 +17626,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45721</v>
+        <v>45835</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17640,8 +17645,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17684,7 +17694,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17694,14 +17704,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45680</v>
+        <v>45834</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17714,7 +17724,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17757,7 +17767,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17771,10 +17781,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45527</v>
+        <v>45716</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17787,7 +17797,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17830,7 +17840,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17844,10 +17854,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45630</v>
+        <v>45265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17859,13 +17869,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17908,7 +17913,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17922,10 +17927,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45804</v>
+        <v>45862</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17937,13 +17942,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17986,7 +17986,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45707</v>
+        <v>45883</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45771</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45713</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>45566</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45714</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44494</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>46045</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>45161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>46202</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45824</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45231</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45075</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46230</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>45818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44584</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44494</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44476</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45524</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45524</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45453</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45160</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44538</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>44595</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45566</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45243</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>45019</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>45089</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45090</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>45183</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45632</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45548</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45257</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>45742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44944</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45169</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45589</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45394</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44906</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44687</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44944</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45176</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45566</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45614</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44944</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>45369</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>45470</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45933</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>44795</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44785</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45090</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45531</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>45103</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45561</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>45899</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>44727</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45233</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45919</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45489</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45742</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44515</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>46143</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>46142</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>45930</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45090</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45218</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45720</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45933</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45942</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45940</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45386</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>46153</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>44906</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45209</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45973</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45890</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44972</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45076</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45992</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45251</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44900</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44809</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45483</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>46006</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45719</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45229</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46021</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44755</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45243</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>46171</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>46171</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>46045</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46045</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>46045</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44908</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>46052</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>46055</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45707</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>46010</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>46010</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>46010</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>46010</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>46062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>46069</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45252</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>46181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45632</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46079</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46188</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>46188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45394</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>46188</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45209</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44494</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44906</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44531</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>46127</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45089</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45401</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44494</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45098</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45231</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45575</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>46160</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>46210</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>46210</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45078</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45566</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45251</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>44809</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45243</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>46260</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44939</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>45565</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45169</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45566</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>44664</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45436</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>46230</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>46191</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>44469</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45617</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45786</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>46276</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45789</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45721</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45630</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45680</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45707</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45835</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45834</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45716</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45862</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45883</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE223"/>
+  <dimension ref="A1:AE222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45771</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45713</v>
+        <v>45824</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,13 +2196,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2235,53 +2230,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2295,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45566</v>
+        <v>45713</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2310,17 +2301,22 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2335,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2351,42 +2347,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>45566</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2415,23 +2415,18 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2445,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2454,49 +2449,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2510,10 +2505,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45714</v>
+        <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2525,11 +2520,16 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2550,58 +2550,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44494</v>
+        <v>46045</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2632,17 +2632,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2660,58 +2660,58 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46045</v>
+        <v>45714</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2740,40 +2740,35 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2786,42 +2781,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2835,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45161</v>
+        <v>46202</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,14 +2845,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2891,42 +2891,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46202</v>
+        <v>44494</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2961,75 +2961,75 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
         <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45824</v>
+        <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3209,49 +3209,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45231</v>
+        <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3305,58 +3305,62 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3374,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45075</v>
+        <v>45231</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,7 +3390,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3426,46 +3430,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46230</v>
+        <v>45075</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3519,55 +3519,55 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
         <v>45818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3290-2022</t>
+          <t>A 66556-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44584</v>
+        <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3752,7 +3752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 66556-2021</t>
+          <t>A 3290-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44519</v>
+        <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 59883-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44795</v>
+        <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4538,11 +4538,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4585,7 +4585,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59883-2021</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44494</v>
+        <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4614,13 +4614,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4663,7 +4658,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4677,10 +4672,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44476</v>
+        <v>44795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4692,8 +4687,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45002</v>
+        <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45524</v>
+        <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4836,11 +4836,6 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4887,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45524</v>
+        <v>45002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4916,13 +4911,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4965,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4979,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45453</v>
+        <v>45524</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4994,8 +4984,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5038,7 +5033,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5052,10 +5047,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45160</v>
+        <v>45524</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5067,8 +5062,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44538</v>
+        <v>45160</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5140,13 +5140,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5189,7 +5184,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5203,10 +5198,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44595</v>
+        <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5218,8 +5213,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
         <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45566</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45166</v>
+        <v>45243</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5437,8 +5437,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5481,7 +5486,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5498,7 +5503,7 @@
         <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5511,7 +5516,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5554,7 +5559,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45243</v>
+        <v>45166</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5583,13 +5588,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         <v>44503</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5802,10 +5802,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45019</v>
+        <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5875,10 +5875,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45089</v>
+        <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5951,7 +5951,7 @@
         <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45090</v>
+        <v>45183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6080,7 +6080,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45603</v>
+        <v>45090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6153,7 +6153,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45183</v>
+        <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>45632</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45548</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45257</v>
+        <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6542,10 +6542,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45002</v>
+        <v>45257</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>45742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44944</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45169</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45589</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45394</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44906</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44687</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44944</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7657,10 +7657,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45176</v>
+        <v>45883</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7733,7 +7733,7 @@
         <v>45566</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45614</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44944</v>
+        <v>45176</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7969,13 +7969,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8018,7 +8013,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8032,10 +8027,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45369</v>
+        <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8048,7 +8043,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8091,7 +8086,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8105,10 +8100,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45470</v>
+        <v>45824</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8126,7 +8121,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8186,7 +8181,7 @@
         <v>45755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8242,7 +8237,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8256,10 +8251,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45933</v>
+        <v>45899</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8271,13 +8266,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8320,7 +8310,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8334,10 +8324,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44795</v>
+        <v>45933</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8355,7 +8345,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8415,7 +8405,7 @@
         <v>44785</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8476,7 +8466,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8486,14 +8476,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45090</v>
+        <v>45531</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8505,8 +8495,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8549,7 +8544,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8559,14 +8554,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45531</v>
+        <v>44944</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8580,11 +8575,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8627,7 +8622,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8641,10 +8636,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45103</v>
+        <v>45908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8656,8 +8651,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45824</v>
+        <v>45369</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8729,13 +8729,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8778,7 +8773,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8792,10 +8787,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45561</v>
+        <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,8 +8802,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45899</v>
+        <v>45919</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45908</v>
+        <v>45919</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8953,13 +8953,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9002,7 +8997,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9016,10 +9011,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44727</v>
+        <v>45470</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,8 +9026,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45233</v>
+        <v>44795</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9104,8 +9104,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9148,7 +9153,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9162,10 +9167,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45916</v>
+        <v>45090</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9177,13 +9182,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45919</v>
+        <v>45930</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45919</v>
+        <v>45561</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45489</v>
+        <v>45930</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45742</v>
+        <v>45933</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44515</v>
+        <v>46143</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>14.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46143</v>
+        <v>46142</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9620,8 +9620,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>14.6</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9664,7 +9669,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,10 +9683,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9693,13 +9698,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9742,7 +9742,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45930</v>
+        <v>44727</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9829,10 +9829,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45930</v>
+        <v>45942</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9888,7 +9888,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45090</v>
+        <v>45233</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9961,7 +9961,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9975,10 +9975,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45218</v>
+        <v>45940</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9990,13 +9990,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10039,7 +10034,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10053,10 +10048,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45720</v>
+        <v>45890</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10069,7 +10064,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10112,7 +10107,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10126,10 +10121,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45933</v>
+        <v>45489</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10142,7 +10137,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10185,7 +10180,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10199,10 +10194,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45942</v>
+        <v>45742</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10215,7 +10210,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10258,7 +10253,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10272,10 +10267,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45940</v>
+        <v>44515</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10288,7 +10283,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10331,7 +10326,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10341,14 +10336,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45631</v>
+        <v>45090</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,13 +10355,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10409,7 +10399,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10423,10 +10413,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45561</v>
+        <v>45218</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,8 +10428,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10482,7 +10477,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10496,10 +10491,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45386</v>
+        <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10512,7 +10507,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10555,7 +10550,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10569,10 +10564,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45252</v>
+        <v>45973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10584,13 +10579,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10633,7 +10623,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10647,10 +10637,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46153</v>
+        <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10663,7 +10653,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10706,7 +10696,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10716,14 +10706,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44906</v>
+        <v>45631</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,8 +10725,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10779,7 +10774,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10793,10 +10788,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45209</v>
+        <v>45561</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10809,7 +10804,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10852,7 +10847,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10866,10 +10861,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45973</v>
+        <v>46170</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10882,7 +10877,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10925,7 +10920,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10939,10 +10934,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45890</v>
+        <v>45988</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10955,7 +10950,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10998,7 +10993,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45589</v>
+        <v>45386</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11028,7 +11023,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11071,7 +11066,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11085,10 +11080,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45980</v>
+        <v>45252</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11100,8 +11095,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11144,7 +11144,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44972</v>
+        <v>45992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11217,7 +11217,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11227,14 +11227,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45076</v>
+        <v>46171</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,8 +11246,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11290,7 +11295,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11304,10 +11309,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45265</v>
+        <v>44906</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11320,7 +11325,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11363,7 +11368,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11377,10 +11382,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45988</v>
+        <v>45209</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11393,7 +11398,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11436,7 +11441,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11450,10 +11455,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11465,8 +11470,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11509,7 +11519,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11523,10 +11533,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45251</v>
+        <v>46006</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11538,8 +11548,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11582,7 +11597,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11596,10 +11611,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44900</v>
+        <v>45589</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11612,7 +11627,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11655,7 +11670,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11669,10 +11684,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44809</v>
+        <v>46021</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11684,13 +11699,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11733,7 +11743,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11743,14 +11753,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45483</v>
+        <v>46021</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11762,13 +11772,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11811,7 +11816,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11825,10 +11830,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46006</v>
+        <v>46021</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11840,13 +11845,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11889,7 +11889,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11903,10 +11903,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46006</v>
+        <v>44972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11918,13 +11918,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11967,7 +11962,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11977,14 +11972,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45719</v>
+        <v>45076</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11997,7 +11992,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12040,7 +12035,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12054,10 +12049,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45229</v>
+        <v>46181</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12070,7 +12065,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12113,7 +12108,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12123,14 +12118,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44929</v>
+        <v>45265</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12143,7 +12138,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12182,35 +12177,11 @@
         <v>0</v>
       </c>
       <c r="V143" s="2" t="inlineStr"/>
-      <c r="X143">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y143">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA143">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB143">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC143">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD143">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12224,10 +12195,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46021</v>
+        <v>46188</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12239,8 +12210,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>12.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12283,7 +12259,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12297,10 +12273,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46021</v>
+        <v>46188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12312,8 +12288,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12356,7 +12337,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12370,10 +12351,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46021</v>
+        <v>46188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12385,8 +12366,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12429,7 +12415,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12443,10 +12429,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44755</v>
+        <v>46045</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12458,8 +12444,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12502,7 +12493,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12516,10 +12507,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46170</v>
+        <v>46045</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12531,8 +12522,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>14.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12575,7 +12571,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12589,10 +12585,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45243</v>
+        <v>46045</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12606,11 +12602,11 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12653,7 +12649,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24724-2026</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12667,10 +12663,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46171</v>
+        <v>46052</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12682,13 +12678,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12731,7 +12722,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12745,10 +12736,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46171</v>
+        <v>46055</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12760,13 +12751,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12809,7 +12795,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12823,10 +12809,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46045</v>
+        <v>45251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12838,13 +12824,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12887,7 +12868,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12901,10 +12882,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46045</v>
+        <v>46010</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12918,11 +12899,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>14.3</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12965,7 +12946,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12979,10 +12960,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46045</v>
+        <v>44900</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12994,13 +12975,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13043,7 +13019,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13057,10 +13033,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44908</v>
+        <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13072,8 +13048,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13116,7 +13097,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13130,10 +13111,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46052</v>
+        <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13145,8 +13126,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13189,7 +13175,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13203,10 +13189,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46055</v>
+        <v>46010</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13218,8 +13204,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13262,7 +13253,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13272,14 +13263,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45631</v>
+        <v>46062</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13291,13 +13282,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13340,7 +13326,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13354,10 +13340,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45707</v>
+        <v>46069</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13370,7 +13356,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13413,7 +13399,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13427,10 +13413,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46010</v>
+        <v>44809</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13444,11 +13430,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13491,7 +13477,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13501,14 +13487,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46010</v>
+        <v>45483</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13522,11 +13508,11 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13569,7 +13555,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13583,10 +13569,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46010</v>
+        <v>45719</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13598,13 +13584,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13647,7 +13628,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13661,10 +13642,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46010</v>
+        <v>46079</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13676,13 +13657,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13725,7 +13701,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13739,10 +13715,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46062</v>
+        <v>45229</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13755,7 +13731,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13798,7 +13774,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13808,14 +13784,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46069</v>
+        <v>44929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13828,7 +13804,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13867,11 +13843,35 @@
         <v>0</v>
       </c>
       <c r="V165" s="2" t="inlineStr"/>
+      <c r="X165">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y165">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA165">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB165">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC165">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD165">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13885,10 +13885,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45252</v>
+        <v>44755</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13900,13 +13900,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13949,7 +13944,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13963,10 +13958,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46181</v>
+        <v>45243</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13976,6 +13971,11 @@
       <c r="G167" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -14022,7 +14022,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14032,14 +14032,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45632</v>
+        <v>44908</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14051,13 +14051,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14100,7 +14095,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14110,14 +14105,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46079</v>
+        <v>45631</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14127,6 +14122,11 @@
       <c r="G169" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -14173,7 +14173,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14187,10 +14187,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46188</v>
+        <v>45707</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14202,13 +14202,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>12.6</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14251,7 +14246,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14265,10 +14260,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46188</v>
+        <v>46206</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14280,13 +14275,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14329,7 +14319,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14343,10 +14333,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45394</v>
+        <v>46127</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14364,7 +14354,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14407,7 +14397,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14421,10 +14411,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46188</v>
+        <v>45252</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14438,11 +14428,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14485,7 +14475,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14495,14 +14485,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45209</v>
+        <v>45632</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14514,8 +14504,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14558,7 +14553,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14572,10 +14567,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44494</v>
+        <v>46160</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14589,11 +14584,11 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14636,7 +14631,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14650,10 +14645,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44906</v>
+        <v>46210</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14665,8 +14660,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14709,7 +14709,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44531</v>
+        <v>46210</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14738,8 +14738,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14782,7 +14787,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14796,10 +14801,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46127</v>
+        <v>45394</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14817,7 +14822,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14860,7 +14865,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14874,10 +14879,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45089</v>
+        <v>45209</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14890,7 +14895,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14933,7 +14938,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14947,10 +14952,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45524</v>
+        <v>46260</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14962,13 +14967,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.1</v>
+        <v>7.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15011,7 +15011,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15021,14 +15021,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45401</v>
+        <v>44494</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15040,8 +15040,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15084,7 +15089,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15098,10 +15103,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44494</v>
+        <v>44906</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15113,13 +15118,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15162,7 +15162,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15176,10 +15176,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46206</v>
+        <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15235,7 +15235,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15249,10 +15249,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45098</v>
+        <v>45089</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15308,7 +15308,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15322,10 +15322,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45231</v>
+        <v>45524</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15337,8 +15337,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>9.5</v>
+        <v>0.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15381,7 +15386,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15391,14 +15396,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45575</v>
+        <v>45401</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15411,7 +15416,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15454,7 +15459,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15468,10 +15473,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46160</v>
+        <v>46230</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15483,13 +15488,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15532,7 +15532,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15546,10 +15546,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46210</v>
+        <v>46191</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15561,13 +15561,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15610,7 +15605,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15624,10 +15619,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46210</v>
+        <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15641,11 +15636,11 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15688,7 +15683,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15702,10 +15697,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45078</v>
+        <v>45098</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15718,7 +15713,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15761,7 +15756,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15775,10 +15770,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45566</v>
+        <v>46276</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15791,7 +15786,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15834,7 +15829,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15848,10 +15843,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45251</v>
+        <v>45231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15864,7 +15859,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15907,7 +15902,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15921,10 +15916,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44809</v>
+        <v>45575</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15936,13 +15931,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15985,7 +15975,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15999,10 +15989,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45243</v>
+        <v>45078</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16015,7 +16005,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16058,7 +16048,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16072,10 +16062,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46260</v>
+        <v>45566</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16088,7 +16078,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16131,7 +16121,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16145,10 +16135,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44939</v>
+        <v>45251</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16161,7 +16151,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16204,7 +16194,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16218,10 +16208,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45565</v>
+        <v>44809</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16233,8 +16223,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>8.9</v>
+        <v>0.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16277,7 +16272,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16291,10 +16286,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45169</v>
+        <v>45243</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16306,13 +16301,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16355,7 +16345,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16369,10 +16359,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45566</v>
+        <v>44939</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16385,7 +16375,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16428,7 +16418,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16442,10 +16432,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44664</v>
+        <v>45565</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16457,13 +16447,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>3.4</v>
+        <v>8.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16506,7 +16491,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16520,10 +16505,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45436</v>
+        <v>45169</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16535,8 +16520,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16579,7 +16569,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16593,10 +16583,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46230</v>
+        <v>45566</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16609,7 +16599,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16652,7 +16642,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16666,10 +16656,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46191</v>
+        <v>44664</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16681,8 +16671,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16725,7 +16720,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16739,10 +16734,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44469</v>
+        <v>45436</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16755,7 +16750,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16798,7 +16793,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16812,10 +16807,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45617</v>
+        <v>44469</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16828,7 +16823,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16871,7 +16866,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16885,10 +16880,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45786</v>
+        <v>45617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16900,13 +16895,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16949,7 +16939,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16963,10 +16953,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46276</v>
+        <v>45786</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16978,8 +16968,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17039,7 +17034,7 @@
         <v>45789</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17112,7 +17107,7 @@
         <v>45721</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17185,7 +17180,7 @@
         <v>45630</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17263,7 +17258,7 @@
         <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17336,7 +17331,7 @@
         <v>45680</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17409,7 +17404,7 @@
         <v>45804</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17487,7 +17482,7 @@
         <v>45707</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17560,7 +17555,7 @@
         <v>45834</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17633,7 +17628,7 @@
         <v>45835</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17711,7 +17706,7 @@
         <v>45834</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17784,7 +17779,7 @@
         <v>45716</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17857,7 +17852,7 @@
         <v>45265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17930,7 +17925,7 @@
         <v>45862</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17986,24 +17981,24 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>S 2395-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45883</v>
+        <v>45468</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18015,8 +18010,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18056,10 +18056,10 @@
       </c>
       <c r="V221" s="2" t="inlineStr"/>
     </row>
-    <row r="222" ht="15" customHeight="1">
+    <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>S 2395-2024</t>
+          <t>S 343-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18069,14 +18069,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45468</v>
+        <v>46059</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18088,13 +18088,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>0.1</v>
+        <v>25.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18133,79 +18128,6 @@
         <v>0</v>
       </c>
       <c r="V222" s="2" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>S 343-2026</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D223" s="1" t="n">
-        <v>46059</v>
-      </c>
-      <c r="E223" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I223" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J223" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0</v>
-      </c>
-      <c r="L223" t="n">
-        <v>0</v>
-      </c>
-      <c r="M223" t="n">
-        <v>0</v>
-      </c>
-      <c r="N223" t="n">
-        <v>0</v>
-      </c>
-      <c r="O223" t="n">
-        <v>0</v>
-      </c>
-      <c r="P223" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0</v>
-      </c>
-      <c r="S223" t="n">
-        <v>0</v>
-      </c>
-      <c r="T223" t="n">
-        <v>0</v>
-      </c>
-      <c r="U223" t="n">
-        <v>0</v>
-      </c>
-      <c r="V223" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE222"/>
+  <dimension ref="A1:AE223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 13365-2024</t>
+          <t>A 38204-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1387,14 +1387,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45387</v>
+        <v>45545</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1408,619 +1408,619 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38204-2024 artfynd.xlsx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38204-2024 karta.png", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38204-2024 georefererad karta.tif", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 38204-2024 karta knärot.png", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38204-2024 FSC-klagomål.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38204-2024 FSC-klagomål mail.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38204-2024 tillsynsbegäran.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38204-2024 tillsynsbegäran mail.docx", "A 38204-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 13365-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45387</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>15</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>15</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 13365-2024 artfynd.xlsx", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 13365-2024 karta.png", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 13365-2024 georefererad karta.tif", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 13365-2024 FSC-klagomål.docx", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 13365-2024 FSC-klagomål mail.docx", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 13365-2024 tillsynsbegäran.docx", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 13365-2024 tillsynsbegäran mail.docx", "A 13365-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 13365-2024 prioriterade fågelarter.docx", "A 13365-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 38204-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 19851-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>45545</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="D11" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="U10" t="n">
-        <v>6</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38204-2024 artfynd.xlsx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38204-2024 karta.png", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38204-2024 georefererad karta.tif", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 38204-2024 karta knärot.png", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38204-2024 FSC-klagomål.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38204-2024 FSC-klagomål mail.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38204-2024 tillsynsbegäran.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38204-2024 tillsynsbegäran mail.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 52381-2024</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>45609</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>1.4</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 43626-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45184</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.7</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallfingersvamp</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 19851-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S 1323-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45771</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>4.9</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S 1323-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45771</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/S 1323-2025 artfynd.xlsx", "S 1323-2025")</f>
         <v/>
@@ -2057,7 +2057,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23268-2022</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44720</v>
+        <v>45075</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2086,13 +2086,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2132,42 +2127,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2180,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45824</v>
+        <v>45566</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2197,17 +2196,17 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2230,49 +2229,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2285,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45713</v>
+        <v>44494</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2303,27 +2302,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9.5</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2331,62 +2330,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 23268-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45566</v>
+        <v>44720</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2415,17 +2410,22 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2456,42 +2456,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45222</v>
+        <v>45714</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,29 +2520,24 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>11.2</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -2550,58 +2545,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2615,10 +2610,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46045</v>
+        <v>45818</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,13 +2625,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2676,42 +2666,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2725,10 +2715,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45714</v>
+        <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2740,11 +2730,16 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2756,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2765,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46202</v>
+        <v>45161</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,19 +2840,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2891,42 +2881,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44494</v>
+        <v>45231</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,16 +2945,11 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2976,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2985,58 +2970,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3050,10 +3035,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46127</v>
+        <v>46045</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3067,14 +3052,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -3111,42 +3096,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3160,10 +3145,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45161</v>
+        <v>46127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3175,14 +3160,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3216,42 +3206,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3255,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46230</v>
+        <v>45824</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3281,7 +3271,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3293,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3305,62 +3295,58 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3374,10 +3360,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45231</v>
+        <v>45713</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3389,8 +3375,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3430,42 +3421,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3474,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45075</v>
+        <v>46202</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3494,14 +3489,19 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3531,50 +3531,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3588,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45818</v>
+        <v>46230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,20 +3600,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3628,51 +3624,55 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6068-2022</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44599</v>
+        <v>45617</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34676-2022</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44795</v>
+        <v>44755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4458,13 +4458,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4507,7 +4502,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59883-2021</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4521,10 +4516,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44494</v>
+        <v>44727</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4536,13 +4531,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4585,7 +4575,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4599,10 +4589,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44476</v>
+        <v>45786</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4614,8 +4604,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4658,7 +4653,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 6068-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4672,10 +4667,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44795</v>
+        <v>44599</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4687,13 +4682,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4736,7 +4726,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4740,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45453</v>
+        <v>45169</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4765,8 +4755,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4804,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 34676-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4818,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44595</v>
+        <v>44795</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4838,8 +4833,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45002</v>
+        <v>45453</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 59883-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45524</v>
+        <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45524</v>
+        <v>44476</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5062,13 +5062,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5106,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45160</v>
+        <v>44795</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5140,8 +5135,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5184,7 +5184,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44538</v>
+        <v>45229</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5213,13 +5213,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5262,7 +5257,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5272,14 +5267,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45630</v>
+        <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5292,7 +5287,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5335,7 +5330,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5349,10 +5344,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45566</v>
+        <v>45090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5365,7 +5360,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5408,7 +5403,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5422,10 +5417,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45243</v>
+        <v>45090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5437,13 +5432,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5476,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5490,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45166</v>
+        <v>45883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5516,7 +5506,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5559,7 +5549,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5573,10 +5563,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45166</v>
+        <v>45721</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5589,7 +5579,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5632,7 +5622,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5646,10 +5636,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44503</v>
+        <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5661,13 +5651,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5710,7 +5695,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5724,10 +5709,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45394</v>
+        <v>45680</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5739,13 +5724,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5788,7 +5768,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5802,10 +5782,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45089</v>
+        <v>44538</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5817,8 +5797,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5861,7 +5846,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5875,10 +5860,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45019</v>
+        <v>45566</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5891,7 +5876,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5934,7 +5919,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5948,10 +5933,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45478</v>
+        <v>45243</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5963,8 +5948,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6007,7 +5997,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6021,10 +6011,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45183</v>
+        <v>45527</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6037,7 +6027,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6080,7 +6070,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6094,10 +6084,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45090</v>
+        <v>45089</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6110,7 +6100,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6153,7 +6143,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6167,10 +6157,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45603</v>
+        <v>45394</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6182,8 +6172,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6226,7 +6221,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6236,14 +6231,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6257,11 +6252,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6304,7 +6299,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6318,10 +6313,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44494</v>
+        <v>45231</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6333,13 +6328,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6382,7 +6372,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6396,10 +6386,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45548</v>
+        <v>44944</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6411,8 +6401,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6455,7 +6450,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45002</v>
+        <v>45098</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6485,7 +6480,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6528,7 +6523,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6542,10 +6537,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45257</v>
+        <v>45169</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6557,8 +6552,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45742</v>
+        <v>44974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44537</v>
+        <v>45394</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6703,8 +6703,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6747,7 +6752,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6761,10 +6766,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>45824</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6776,8 +6781,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6820,7 +6830,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6834,10 +6844,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45575</v>
+        <v>44974</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6850,7 +6860,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6893,7 +6903,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6907,10 +6917,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44974</v>
+        <v>45251</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6923,7 +6933,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6966,7 +6976,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6980,10 +6990,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44974</v>
+        <v>45103</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6996,7 +7006,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7039,7 +7049,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7053,10 +7063,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44944</v>
+        <v>45078</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7068,13 +7078,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7117,7 +7122,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7131,10 +7136,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45169</v>
+        <v>44537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,13 +7151,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45589</v>
+        <v>45470</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7224,8 +7224,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7268,7 +7273,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7282,10 +7287,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45394</v>
+        <v>44944</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7299,11 +7304,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7346,7 +7351,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7360,10 +7365,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44906</v>
+        <v>45899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7376,7 +7381,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7419,7 +7424,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7429,14 +7434,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44687</v>
+        <v>45483</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7448,8 +7453,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7492,7 +7502,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7506,10 +7516,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44944</v>
+        <v>45908</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7523,11 +7533,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7570,7 +7580,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7584,10 +7594,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44937</v>
+        <v>45265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7600,7 +7610,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7643,7 +7653,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7657,10 +7667,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45883</v>
+        <v>45575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7673,7 +7683,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7716,7 +7726,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7730,10 +7740,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45566</v>
+        <v>44515</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7746,7 +7756,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7789,7 +7799,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7803,10 +7813,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45614</v>
+        <v>45176</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7819,7 +7829,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7862,7 +7872,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7876,10 +7886,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45524</v>
+        <v>45916</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7893,11 +7903,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7940,7 +7950,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7954,10 +7964,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45176</v>
+        <v>45548</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7970,7 +7980,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.3</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8013,7 +8023,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8023,14 +8033,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45103</v>
+        <v>45632</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8042,8 +8052,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8086,7 +8101,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8100,10 +8115,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45824</v>
+        <v>45919</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8115,13 +8130,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8164,7 +8174,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8178,10 +8188,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45755</v>
+        <v>45919</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8194,7 +8204,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8237,7 +8247,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8251,10 +8261,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45899</v>
+        <v>45524</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8266,8 +8276,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8310,7 +8325,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8324,10 +8339,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45933</v>
+        <v>45524</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8341,11 +8356,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8388,7 +8403,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8402,10 +8417,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44785</v>
+        <v>45524</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8419,11 +8434,11 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8466,7 +8481,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8476,14 +8491,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45531</v>
+        <v>44908</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8495,13 +8510,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8544,7 +8554,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8558,10 +8568,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44944</v>
+        <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8579,7 +8589,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8622,7 +8632,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8636,10 +8646,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45908</v>
+        <v>45589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8651,13 +8661,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8700,7 +8705,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45369</v>
+        <v>44494</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8729,8 +8734,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8773,7 +8783,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8787,10 +8797,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45916</v>
+        <v>44494</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8804,11 +8814,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8851,7 +8861,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8865,10 +8875,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45919</v>
+        <v>45719</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8881,7 +8891,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8924,7 +8934,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8938,10 +8948,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45919</v>
+        <v>45930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8954,7 +8964,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8997,7 +9007,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9011,10 +9021,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45470</v>
+        <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9026,13 +9036,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9075,7 +9080,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44795</v>
+        <v>45707</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9104,13 +9109,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45090</v>
+        <v>45742</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45930</v>
+        <v>45933</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45561</v>
+        <v>44595</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45933</v>
+        <v>45566</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46143</v>
+        <v>45565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>14.6</v>
+        <v>8.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46142</v>
+        <v>45002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9620,13 +9620,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9669,7 +9664,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9683,10 +9678,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46153</v>
+        <v>44531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9699,7 +9694,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9742,7 +9737,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9756,10 +9751,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44727</v>
+        <v>45942</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9772,7 +9767,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9815,7 +9810,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9829,10 +9824,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45942</v>
+        <v>44937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9845,7 +9840,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9888,7 +9883,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9902,10 +9897,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45233</v>
+        <v>45566</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9918,7 +9913,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9961,7 +9956,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9975,10 +9970,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45940</v>
+        <v>45575</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9991,7 +9986,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10034,7 +10029,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10044,14 +10039,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45890</v>
+        <v>45631</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,8 +10058,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45489</v>
+        <v>45742</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45742</v>
+        <v>44906</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10253,7 +10253,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10263,14 +10263,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44515</v>
+        <v>45076</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45090</v>
+        <v>45209</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10399,7 +10399,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10413,10 +10413,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45218</v>
+        <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10428,13 +10428,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10477,7 +10472,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10491,10 +10486,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45720</v>
+        <v>45589</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10507,7 +10502,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10550,7 +10545,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10564,10 +10559,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45973</v>
+        <v>45524</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,8 +10574,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45980</v>
+        <v>45233</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10696,7 +10696,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10706,14 +10706,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45631</v>
+        <v>45218</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10774,7 +10774,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10784,14 +10784,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45561</v>
+        <v>44929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10843,11 +10843,35 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
+      <c r="X125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD125">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10861,10 +10885,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46170</v>
+        <v>45973</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10877,7 +10901,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10920,7 +10944,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10934,10 +10958,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45988</v>
+        <v>45369</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10950,7 +10974,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10993,7 +11017,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11007,10 +11031,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45386</v>
+        <v>45614</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11023,7 +11047,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11066,7 +11090,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11080,10 +11104,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45252</v>
+        <v>45980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11095,13 +11119,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11144,7 +11163,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11158,10 +11177,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45992</v>
+        <v>45243</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,8 +11192,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11217,7 +11241,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11231,10 +11255,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46171</v>
+        <v>45183</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,13 +11270,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11295,7 +11314,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11309,10 +11328,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44906</v>
+        <v>45988</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11325,7 +11344,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11368,7 +11387,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11382,10 +11401,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45209</v>
+        <v>45257</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11398,7 +11417,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11441,7 +11460,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11455,10 +11474,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11470,13 +11489,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11519,7 +11533,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11533,10 +11547,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46006</v>
+        <v>45002</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11548,13 +11562,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11597,7 +11606,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11611,10 +11620,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45589</v>
+        <v>45720</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11627,7 +11636,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11670,7 +11679,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11684,10 +11693,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46021</v>
+        <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11700,7 +11709,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11743,7 +11752,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11757,10 +11766,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46021</v>
+        <v>45252</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11772,8 +11781,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11816,7 +11830,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11830,10 +11844,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46021</v>
+        <v>45834</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11846,7 +11860,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11889,7 +11903,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11899,14 +11913,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44972</v>
+        <v>45834</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11919,7 +11933,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11962,7 +11976,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11972,14 +11986,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45076</v>
+        <v>44809</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11991,8 +12005,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12035,7 +12054,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12049,10 +12068,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46181</v>
+        <v>46006</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12064,8 +12083,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12108,7 +12132,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12122,10 +12146,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45265</v>
+        <v>46006</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12137,8 +12161,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12181,7 +12210,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12191,14 +12220,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46188</v>
+        <v>45835</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12216,7 +12245,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>12.6</v>
+        <v>3.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12259,7 +12288,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12273,10 +12302,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46188</v>
+        <v>46045</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12290,11 +12319,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12337,7 +12366,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12351,10 +12380,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46188</v>
+        <v>46045</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12368,11 +12397,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12415,7 +12444,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12432,7 +12461,7 @@
         <v>46045</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12450,7 +12479,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>14.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12493,7 +12522,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12507,10 +12536,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,13 +12551,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>14.3</v>
+        <v>0.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12571,7 +12595,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12585,10 +12609,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46045</v>
+        <v>46021</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12600,13 +12624,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12649,7 +12668,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12663,10 +12682,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46052</v>
+        <v>46021</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12679,7 +12698,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12722,7 +12741,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12736,10 +12755,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46055</v>
+        <v>46021</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12752,7 +12771,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.3</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12795,7 +12814,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12809,10 +12828,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45251</v>
+        <v>45566</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12825,7 +12844,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12868,7 +12887,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12882,10 +12901,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46010</v>
+        <v>46055</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12897,13 +12916,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12946,7 +12960,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12960,10 +12974,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44900</v>
+        <v>45252</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12975,8 +12989,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13019,7 +13038,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13033,10 +13052,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46010</v>
+        <v>44895</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13048,13 +13067,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13097,7 +13111,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13114,7 +13128,7 @@
         <v>46010</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13132,7 +13146,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13192,7 +13206,7 @@
         <v>46010</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13270,7 +13284,7 @@
         <v>46062</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13326,7 +13340,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13340,10 +13354,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46069</v>
+        <v>46010</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13355,8 +13369,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13399,7 +13418,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13413,10 +13432,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44809</v>
+        <v>46010</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13430,11 +13449,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13477,7 +13496,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13487,14 +13506,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45483</v>
+        <v>44906</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13506,13 +13525,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13555,7 +13569,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13569,10 +13583,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45719</v>
+        <v>44503</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13582,6 +13596,11 @@
       <c r="G162" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -13628,7 +13647,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13642,10 +13661,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46079</v>
+        <v>46069</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13658,7 +13677,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13701,7 +13720,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13715,10 +13734,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45229</v>
+        <v>44664</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13730,8 +13749,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13774,7 +13798,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 39394-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13784,14 +13808,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44929</v>
+        <v>46288</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13804,7 +13828,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13843,35 +13867,11 @@
         <v>0</v>
       </c>
       <c r="V165" s="2" t="inlineStr"/>
-      <c r="X165">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y165">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA165">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB165">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC165">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD165">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13881,14 +13881,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44755</v>
+        <v>45401</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13944,7 +13944,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13958,10 +13958,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45243</v>
+        <v>45489</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13973,13 +13973,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14022,7 +14017,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14036,10 +14031,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44908</v>
+        <v>46079</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14052,7 +14047,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14095,7 +14090,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14105,14 +14100,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45631</v>
+        <v>44494</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14126,11 +14121,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14173,7 +14168,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14187,10 +14182,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45707</v>
+        <v>45436</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14203,7 +14198,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14246,7 +14241,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14260,10 +14255,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46206</v>
+        <v>44939</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14276,7 +14271,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14319,7 +14314,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14333,10 +14328,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46127</v>
+        <v>45089</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14348,13 +14343,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14397,7 +14387,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14411,10 +14401,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45252</v>
+        <v>45090</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14426,13 +14416,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14475,7 +14460,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14485,14 +14470,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45632</v>
+        <v>45716</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14504,13 +14489,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14553,7 +14533,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14567,10 +14547,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46160</v>
+        <v>44687</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14582,13 +14562,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14631,7 +14606,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14645,10 +14620,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46210</v>
+        <v>44906</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14660,13 +14635,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14709,7 +14679,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14723,10 +14693,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46210</v>
+        <v>45265</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14738,13 +14708,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14787,7 +14752,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14801,10 +14766,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45394</v>
+        <v>45862</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14814,11 +14779,6 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -14865,7 +14825,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14879,10 +14839,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45209</v>
+        <v>44809</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14894,8 +14854,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14938,7 +14903,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14952,10 +14917,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46260</v>
+        <v>44972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14968,7 +14933,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15011,7 +14976,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15025,10 +14990,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44494</v>
+        <v>45166</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15040,13 +15005,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15089,7 +15049,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15103,10 +15063,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44906</v>
+        <v>45166</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15119,7 +15079,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15162,7 +15122,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15176,10 +15136,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44531</v>
+        <v>45394</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15191,8 +15151,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15235,7 +15200,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15249,10 +15214,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45089</v>
+        <v>44795</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15264,8 +15229,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15308,7 +15278,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15322,10 +15292,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45524</v>
+        <v>46127</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15339,11 +15309,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15386,7 +15356,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15396,14 +15366,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45401</v>
+        <v>45632</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15415,8 +15385,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15459,7 +15434,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15473,10 +15448,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46230</v>
+        <v>45019</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15489,7 +15464,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15532,7 +15507,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15546,10 +15521,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46191</v>
+        <v>44944</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15561,8 +15536,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15605,7 +15585,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15619,10 +15599,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44494</v>
+        <v>45933</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15636,11 +15616,11 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15683,7 +15663,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15693,14 +15673,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45098</v>
+        <v>45630</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15713,7 +15693,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15756,7 +15736,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15770,10 +15750,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46276</v>
+        <v>45209</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15786,7 +15766,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15829,7 +15809,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15843,10 +15823,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45231</v>
+        <v>45755</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15859,7 +15839,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15902,7 +15882,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15916,10 +15896,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45575</v>
+        <v>44785</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15931,8 +15911,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15975,7 +15960,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15989,10 +15974,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45078</v>
+        <v>45243</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16005,7 +15990,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16048,7 +16033,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16062,10 +16047,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45566</v>
+        <v>45603</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16078,7 +16063,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16121,7 +16106,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16135,10 +16120,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45251</v>
+        <v>45160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16151,7 +16136,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16194,7 +16179,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16204,14 +16189,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44809</v>
+        <v>45531</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16229,7 +16214,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16272,7 +16257,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16286,10 +16271,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45243</v>
+        <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16302,7 +16287,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16345,7 +16330,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16359,10 +16344,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44939</v>
+        <v>46142</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16374,8 +16359,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16418,7 +16408,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16432,10 +16422,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45565</v>
+        <v>45386</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16448,7 +16438,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16491,7 +16481,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16505,10 +16495,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45169</v>
+        <v>45561</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,13 +16510,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16569,7 +16554,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16583,10 +16568,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45566</v>
+        <v>45707</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16599,7 +16584,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16642,7 +16627,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16656,10 +16641,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44664</v>
+        <v>46143</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16671,13 +16656,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>3.4</v>
+        <v>14.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16720,7 +16700,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16730,14 +16710,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45436</v>
+        <v>45631</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16749,8 +16729,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16793,7 +16778,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16807,10 +16792,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44469</v>
+        <v>46153</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16823,7 +16808,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16866,7 +16851,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16880,10 +16865,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45617</v>
+        <v>44469</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16896,7 +16881,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16939,7 +16924,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16953,10 +16938,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45786</v>
+        <v>45890</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16968,13 +16953,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +16997,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17011,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45789</v>
+        <v>46170</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17047,7 +17027,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17090,7 +17070,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17104,10 +17084,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45721</v>
+        <v>46171</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17119,8 +17099,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17163,7 +17148,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17177,10 +17162,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45630</v>
+        <v>46181</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17192,13 +17177,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17241,7 +17221,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17255,10 +17235,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45527</v>
+        <v>46188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17270,8 +17250,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17299,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17313,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45680</v>
+        <v>46188</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17343,8 +17328,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>2.3</v>
+        <v>12.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17387,7 +17377,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17401,10 +17391,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45804</v>
+        <v>46188</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17418,11 +17408,11 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17465,7 +17455,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17479,10 +17469,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45707</v>
+        <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17495,7 +17485,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17538,7 +17528,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17552,10 +17542,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45834</v>
+        <v>46160</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17567,8 +17557,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17611,7 +17606,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17621,14 +17616,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45835</v>
+        <v>46210</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17646,7 +17641,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17689,7 +17684,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17699,14 +17694,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45834</v>
+        <v>46210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17718,8 +17713,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17762,7 +17762,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17776,10 +17776,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45716</v>
+        <v>46260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17849,10 +17849,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45265</v>
+        <v>46230</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17908,7 +17908,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17922,10 +17922,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45862</v>
+        <v>46191</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17981,153 +17981,226 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
+          <t>A 37622-2026</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222" ht="15" customHeight="1">
+      <c r="A222" t="inlineStr">
+        <is>
           <t>S 2395-2024</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D221" s="1" t="n">
+      <c r="D222" s="1" t="n">
         <v>45468</v>
       </c>
-      <c r="E221" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
+      <c r="E222" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I221" t="n">
+      <c r="I222" t="n">
         <v>0.1</v>
       </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>0</v>
-      </c>
-      <c r="O221" t="n">
-        <v>0</v>
-      </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
-      <c r="S221" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" t="n">
-        <v>0</v>
-      </c>
-      <c r="U221" t="n">
-        <v>0</v>
-      </c>
-      <c r="V221" s="2" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>S 343-2026</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D222" s="1" t="n">
+      <c r="D223" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="E222" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I222" t="n">
+      <c r="E223" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
         <v>25.7</v>
       </c>
-      <c r="J222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>0</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" s="2" t="inlineStr"/>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="n">
+        <v>0</v>
+      </c>
+      <c r="T223" t="n">
+        <v>0</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0</v>
+      </c>
+      <c r="V223" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38204-2024</t>
+          <t>A 13365-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1387,14 +1387,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45545</v>
+        <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1436,178 +1436,178 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
       </c>
       <c r="T9" t="n">
+        <v>15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 13365-2024 artfynd.xlsx", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 13365-2024 karta.png", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 13365-2024 georefererad karta.tif", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 13365-2024 FSC-klagomål.docx", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 13365-2024 FSC-klagomål mail.docx", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 13365-2024 tillsynsbegäran.docx", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 13365-2024 tillsynsbegäran mail.docx", "A 13365-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 13365-2024 prioriterade fågelarter.docx", "A 13365-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 38204-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45545</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>6</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>6</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38204-2024 artfynd.xlsx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38204-2024 karta.png", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38204-2024 georefererad karta.tif", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 38204-2024 karta knärot.png", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38204-2024 FSC-klagomål.docx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38204-2024 FSC-klagomål mail.docx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38204-2024 tillsynsbegäran.docx", "A 38204-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38204-2024 tillsynsbegäran mail.docx", "A 38204-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 13365-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45387</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 13365-2024 artfynd.xlsx", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 13365-2024 karta.png", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 13365-2024 georefererad karta.tif", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 13365-2024 FSC-klagomål.docx", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 13365-2024 FSC-klagomål mail.docx", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 13365-2024 tillsynsbegäran.docx", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 13365-2024 tillsynsbegäran mail.docx", "A 13365-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 13365-2024 prioriterade fågelarter.docx", "A 13365-2024")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 19851-2025</t>
+          <t>A 52381-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45771</v>
+        <v>45609</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,13 +1636,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1675,267 +1670,272 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 43626-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45184</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 19851-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45771</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52381-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45609</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 43626-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45184</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 23268-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45075</v>
+        <v>44720</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2086,8 +2086,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2127,46 +2132,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2180,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45566</v>
+        <v>45824</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,16 +2197,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2220,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2229,49 +2230,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2285,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44494</v>
+        <v>45713</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2302,14 +2303,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2321,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2330,58 +2331,62 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23268-2022</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2395,10 +2400,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44720</v>
+        <v>45566</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2410,23 +2415,18 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2456,42 +2456,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45714</v>
+        <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,11 +2520,16 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>11.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2536,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2545,58 +2550,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2610,10 +2615,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45818</v>
+        <v>45714</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2626,23 +2631,23 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -2650,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,42 +2671,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2715,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45222</v>
+        <v>46045</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2732,17 +2737,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2769,49 +2774,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2830,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45161</v>
+        <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2840,24 +2845,29 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -2865,58 +2875,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2940,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45231</v>
+        <v>45161</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2956,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2982,46 +2992,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3035,10 +3045,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46045</v>
+        <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3052,14 +3062,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J24" t="n">
         <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -3096,42 +3106,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 29156-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3145,10 +3155,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46127</v>
+        <v>46202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3166,7 +3176,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3210,38 +3220,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3255,10 +3265,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45824</v>
+        <v>46230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3271,7 +3281,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3283,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3295,58 +3305,62 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3360,10 +3374,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45713</v>
+        <v>45231</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3375,13 +3389,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>9.5</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3421,46 +3430,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 29156-2026</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3474,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46202</v>
+        <v>45075</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3489,19 +3494,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3531,46 +3531,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29156-2026 artfynd.xlsx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29156-2026 karta.png", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29156-2026 georefererad karta.tif", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29156-2026 FSC-klagomål.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29156-2026 FSC-klagomål mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29156-2026 tillsynsbegäran.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29156-2026 tillsynsbegäran mail.docx", "A 29156-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3584,10 +3588,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46230</v>
+        <v>45818</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,19 +3604,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3624,55 +3628,51 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 6068-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45617</v>
+        <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 34676-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44755</v>
+        <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4458,8 +4458,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4502,7 +4507,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 59883-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4516,10 +4521,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44727</v>
+        <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4531,8 +4536,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4575,7 +4585,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 55831-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4589,10 +4599,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45786</v>
+        <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4604,13 +4614,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4653,7 +4658,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6068-2022</t>
+          <t>A 34673-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4667,10 +4672,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44599</v>
+        <v>44795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4682,8 +4687,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4726,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4740,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45169</v>
+        <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4755,13 +4765,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4804,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34676-2022</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4818,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44795</v>
+        <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4833,13 +4838,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45453</v>
+        <v>45002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.300000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59883-2021</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44494</v>
+        <v>45524</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,11 +4986,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55831-2021</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44476</v>
+        <v>45524</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5062,8 +5062,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5106,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34673-2022</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44795</v>
+        <v>45160</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5135,13 +5140,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5184,7 +5184,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45229</v>
+        <v>44538</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5213,8 +5213,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5257,7 +5262,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5267,14 +5272,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45789</v>
+        <v>45630</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5287,7 +5292,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5330,7 +5335,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5344,10 +5349,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45090</v>
+        <v>45243</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5359,8 +5364,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5403,7 +5413,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5417,10 +5427,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45090</v>
+        <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5476,7 +5486,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5490,10 +5500,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45883</v>
+        <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5506,7 +5516,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5549,7 +5559,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5563,10 +5573,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45721</v>
+        <v>44503</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5578,8 +5588,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5622,7 +5637,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5636,10 +5651,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45251</v>
+        <v>45394</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5651,8 +5666,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5695,7 +5715,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5709,10 +5729,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45680</v>
+        <v>45019</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5725,7 +5745,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5768,7 +5788,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5782,10 +5802,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44538</v>
+        <v>45089</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5797,13 +5817,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5846,7 +5861,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5860,10 +5875,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45566</v>
+        <v>45478</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5876,7 +5891,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5919,7 +5934,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5933,10 +5948,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45243</v>
+        <v>45566</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5948,13 +5963,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5997,7 +6007,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6011,10 +6021,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45527</v>
+        <v>45183</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6027,7 +6037,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6070,7 +6080,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6084,10 +6094,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45089</v>
+        <v>45090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6100,7 +6110,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6143,7 +6153,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6157,10 +6167,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45394</v>
+        <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6172,13 +6182,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6221,7 +6226,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6231,14 +6236,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45630</v>
+        <v>45632</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6252,11 +6257,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6299,7 +6304,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6313,10 +6318,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45231</v>
+        <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6328,8 +6333,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>9.5</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6372,7 +6382,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6386,10 +6396,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44944</v>
+        <v>45548</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6401,13 +6411,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6450,7 +6455,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6464,10 +6469,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45098</v>
+        <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6480,7 +6485,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6537,10 +6542,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45169</v>
+        <v>45257</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6552,13 +6557,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44974</v>
+        <v>45742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45394</v>
+        <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6703,13 +6703,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6752,7 +6747,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6766,10 +6761,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45824</v>
+        <v>44895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,13 +6776,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6830,7 +6820,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6844,10 +6834,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44974</v>
+        <v>44944</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6859,8 +6849,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6903,7 +6898,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6917,10 +6912,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45251</v>
+        <v>45575</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6933,7 +6928,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6976,7 +6971,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6990,10 +6985,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45103</v>
+        <v>45169</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7005,8 +7000,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7063,10 +7063,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45078</v>
+        <v>45589</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7122,7 +7122,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7136,10 +7136,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44537</v>
+        <v>45394</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7151,8 +7151,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7195,7 +7200,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7209,10 +7214,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45470</v>
+        <v>44906</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7224,13 +7229,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44944</v>
+        <v>44687</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7302,13 +7302,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7351,7 +7346,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7365,10 +7360,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45899</v>
+        <v>44974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7381,7 +7376,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7424,7 +7419,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7434,14 +7429,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45483</v>
+        <v>44974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7453,13 +7448,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7502,7 +7492,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7516,10 +7506,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45908</v>
+        <v>44944</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7533,11 +7523,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7580,7 +7570,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7594,10 +7584,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45265</v>
+        <v>44937</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7610,7 +7600,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7653,7 +7643,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7667,10 +7657,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45575</v>
+        <v>45566</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7683,7 +7673,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7726,7 +7716,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7740,10 +7730,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44515</v>
+        <v>45883</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7756,7 +7746,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7799,7 +7789,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7813,10 +7803,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45176</v>
+        <v>45614</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7829,7 +7819,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7872,7 +7862,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7886,10 +7876,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45916</v>
+        <v>45524</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7903,11 +7893,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7950,7 +7940,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7964,10 +7954,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45548</v>
+        <v>45103</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7980,7 +7970,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8023,7 +8013,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8033,14 +8023,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45632</v>
+        <v>45824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8054,11 +8044,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8101,7 +8091,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8115,10 +8105,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45919</v>
+        <v>45176</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8131,7 +8121,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>7.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8174,7 +8164,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8188,10 +8178,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45919</v>
+        <v>45899</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8204,7 +8194,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8247,7 +8237,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8261,10 +8251,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45524</v>
+        <v>44944</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8282,7 +8272,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8325,7 +8315,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8339,10 +8329,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45524</v>
+        <v>45908</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8356,11 +8346,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8403,7 +8393,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8417,10 +8407,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45524</v>
+        <v>45369</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8432,13 +8422,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8481,7 +8466,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8495,10 +8480,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44908</v>
+        <v>45470</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8510,8 +8495,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8554,7 +8544,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8568,10 +8558,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45804</v>
+        <v>45916</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8585,11 +8575,11 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8632,7 +8622,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8646,10 +8636,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45589</v>
+        <v>44795</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,8 +8651,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8705,7 +8700,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44494</v>
+        <v>45919</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,13 +8729,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8783,7 +8773,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8797,10 +8787,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44494</v>
+        <v>45919</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8812,13 +8802,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8861,7 +8846,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8875,10 +8860,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45719</v>
+        <v>45090</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8891,7 +8876,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8934,7 +8919,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8948,10 +8933,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45930</v>
+        <v>45561</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8964,7 +8949,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9007,7 +8992,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9021,10 +9006,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45930</v>
+        <v>45755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9037,7 +9022,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9080,7 +9065,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9094,10 +9079,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45707</v>
+        <v>45930</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9110,7 +9095,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9153,7 +9138,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9167,10 +9152,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45742</v>
+        <v>45933</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9182,8 +9167,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9226,7 +9216,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9240,10 +9230,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45933</v>
+        <v>45930</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9256,7 +9246,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9299,7 +9289,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9313,10 +9303,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44595</v>
+        <v>44785</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9328,8 +9318,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45940</v>
+        <v>45933</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9402,7 +9397,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9445,7 +9440,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9455,14 +9450,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45566</v>
+        <v>45531</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9474,8 +9469,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45565</v>
+        <v>44727</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45002</v>
+        <v>45233</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44531</v>
+        <v>45942</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45942</v>
+        <v>45940</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44937</v>
+        <v>45489</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9897,10 +9897,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45566</v>
+        <v>45742</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45575</v>
+        <v>44515</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10039,14 +10039,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45631</v>
+        <v>45090</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10058,13 +10058,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10107,7 +10102,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10121,10 +10116,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45742</v>
+        <v>45218</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10136,8 +10131,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44906</v>
+        <v>45720</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10253,7 +10253,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10263,14 +10263,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45076</v>
+        <v>45973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10336,14 +10336,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45209</v>
+        <v>45631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10353,6 +10353,11 @@
       <c r="G119" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -10399,7 +10404,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10413,10 +10418,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45561</v>
+        <v>45980</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10429,7 +10434,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10472,7 +10477,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10486,10 +10491,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45589</v>
+        <v>45561</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10502,7 +10507,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10545,7 +10550,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10559,10 +10564,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45524</v>
+        <v>45386</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10574,13 +10579,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10623,7 +10623,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45233</v>
+        <v>45252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10652,8 +10652,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10696,7 +10701,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10710,10 +10715,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45218</v>
+        <v>46143</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10725,13 +10730,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>14.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10774,7 +10774,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10784,14 +10784,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44929</v>
+        <v>46142</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,8 +10803,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10843,35 +10848,11 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
-      <c r="X125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD125">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10885,10 +10866,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45973</v>
+        <v>45988</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10901,7 +10882,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10944,7 +10925,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10958,10 +10939,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45369</v>
+        <v>45992</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10974,7 +10955,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11017,7 +10998,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11031,10 +11012,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45614</v>
+        <v>46153</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11047,7 +11028,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11090,7 +11071,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11104,10 +11085,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45980</v>
+        <v>44906</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11120,7 +11101,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11163,7 +11144,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11177,10 +11158,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45243</v>
+        <v>45209</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11192,13 +11173,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11241,7 +11217,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11255,10 +11231,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45183</v>
+        <v>45890</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11271,7 +11247,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11314,7 +11290,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11328,10 +11304,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45988</v>
+        <v>46006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11343,8 +11319,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11387,7 +11368,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11401,10 +11382,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45257</v>
+        <v>46006</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11416,8 +11397,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11460,7 +11446,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11474,10 +11460,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45992</v>
+        <v>45589</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11490,7 +11476,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11533,7 +11519,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11547,10 +11533,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45002</v>
+        <v>44972</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11563,7 +11549,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11606,7 +11592,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11616,14 +11602,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45720</v>
+        <v>45076</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11636,7 +11622,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11679,7 +11665,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11693,10 +11679,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44900</v>
+        <v>46021</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11709,7 +11695,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11752,7 +11738,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11766,10 +11752,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45252</v>
+        <v>45265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11781,13 +11767,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11830,7 +11811,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11844,10 +11825,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45834</v>
+        <v>46021</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11903,7 +11884,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11913,14 +11894,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45834</v>
+        <v>46021</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11933,7 +11914,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11976,7 +11957,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11990,10 +11971,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44809</v>
+        <v>46045</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12007,11 +11988,11 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12054,7 +12035,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12068,10 +12049,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46006</v>
+        <v>46045</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12085,11 +12066,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.6</v>
+        <v>14.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12132,7 +12113,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12146,10 +12127,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46006</v>
+        <v>46045</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12163,11 +12144,11 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12210,7 +12191,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12220,14 +12201,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45835</v>
+        <v>45251</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12239,13 +12220,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12288,7 +12264,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12302,10 +12278,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46045</v>
+        <v>44900</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12317,13 +12293,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12366,7 +12337,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12380,10 +12351,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46045</v>
+        <v>44809</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12397,11 +12368,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12444,7 +12415,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12454,14 +12425,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46045</v>
+        <v>45483</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12475,11 +12446,11 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>14.3</v>
+        <v>2.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12539,7 +12510,7 @@
         <v>46052</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12595,7 +12566,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12609,10 +12580,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46021</v>
+        <v>46055</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12625,7 +12596,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>7.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12668,7 +12639,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12682,10 +12653,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46021</v>
+        <v>45719</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12698,7 +12669,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12741,7 +12712,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12755,10 +12726,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12770,8 +12741,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12814,7 +12790,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12828,10 +12804,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45566</v>
+        <v>46010</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12843,8 +12819,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12887,7 +12868,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12901,10 +12882,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46055</v>
+        <v>46010</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12916,8 +12897,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12960,7 +12946,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12974,10 +12960,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45252</v>
+        <v>46010</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12991,11 +12977,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13038,7 +13024,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13052,10 +13038,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44895</v>
+        <v>46062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13068,7 +13054,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13111,7 +13097,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13125,10 +13111,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46010</v>
+        <v>45229</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13140,13 +13126,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13189,7 +13170,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13199,14 +13180,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46010</v>
+        <v>44929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13218,13 +13199,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13263,11 +13239,35 @@
         <v>0</v>
       </c>
       <c r="V157" s="2" t="inlineStr"/>
+      <c r="X157">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y157">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA157">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB157">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC157">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD157">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13281,10 +13281,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13340,7 +13340,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13354,10 +13354,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46010</v>
+        <v>46170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13369,13 +13369,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13418,7 +13413,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13432,10 +13427,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46010</v>
+        <v>44755</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13447,13 +13442,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13496,7 +13486,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13510,10 +13500,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44906</v>
+        <v>46079</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13526,7 +13516,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13569,7 +13559,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13583,10 +13573,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44503</v>
+        <v>46171</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13604,7 +13594,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13647,7 +13637,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13661,10 +13651,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46069</v>
+        <v>45243</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13676,8 +13666,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13720,7 +13715,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13734,10 +13729,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44664</v>
+        <v>44908</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13749,13 +13744,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3.4</v>
+        <v>8.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13798,7 +13788,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39394-2026</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13812,10 +13802,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46288</v>
+        <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13828,7 +13818,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13871,7 +13861,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13881,14 +13871,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45401</v>
+        <v>46188</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13900,8 +13890,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>12.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13944,7 +13939,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13958,10 +13953,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45489</v>
+        <v>46188</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13973,8 +13968,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14017,7 +14017,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14031,10 +14031,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46079</v>
+        <v>46188</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14046,8 +14046,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14090,7 +14095,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14100,14 +14105,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44494</v>
+        <v>45631</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14121,11 +14126,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14168,7 +14173,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14182,10 +14187,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45436</v>
+        <v>45707</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14198,7 +14203,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14241,7 +14246,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14255,10 +14260,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44939</v>
+        <v>45252</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14270,8 +14275,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14314,7 +14324,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14324,14 +14334,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45089</v>
+        <v>45632</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14343,8 +14353,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14387,7 +14402,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14401,10 +14416,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45090</v>
+        <v>46127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14416,8 +14431,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14460,7 +14480,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14474,10 +14494,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45716</v>
+        <v>45394</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14487,6 +14507,11 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -14533,7 +14558,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14547,10 +14572,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44687</v>
+        <v>45209</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14563,7 +14588,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14606,7 +14631,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14620,10 +14645,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44906</v>
+        <v>46206</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14636,7 +14661,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14679,7 +14704,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14693,10 +14718,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45265</v>
+        <v>44494</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14708,8 +14733,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14752,7 +14782,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14766,10 +14796,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45862</v>
+        <v>44906</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14782,7 +14812,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14825,7 +14855,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14839,10 +14869,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44809</v>
+        <v>46160</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14860,7 +14890,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14903,7 +14933,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14917,10 +14947,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44972</v>
+        <v>46210</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14932,8 +14962,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14976,7 +15011,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14990,10 +15025,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45166</v>
+        <v>46210</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15005,8 +15040,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15049,7 +15089,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15063,10 +15103,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45166</v>
+        <v>44531</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15079,7 +15119,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15122,7 +15162,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15136,10 +15176,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45394</v>
+        <v>45089</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15151,13 +15191,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15200,7 +15235,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15214,10 +15249,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44795</v>
+        <v>45524</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15231,11 +15266,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15278,7 +15313,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15288,14 +15323,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46127</v>
+        <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15307,13 +15342,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15356,7 +15386,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15366,14 +15396,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45632</v>
+        <v>46260</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15385,13 +15415,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15434,7 +15459,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15448,10 +15473,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45019</v>
+        <v>44494</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15463,8 +15488,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15507,7 +15537,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15521,10 +15551,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44944</v>
+        <v>45098</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15536,13 +15566,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15585,7 +15610,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15599,10 +15624,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45933</v>
+        <v>45231</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15614,13 +15639,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15663,7 +15683,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15673,14 +15693,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45630</v>
+        <v>45575</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15693,7 +15713,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15736,7 +15756,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15750,10 +15770,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45209</v>
+        <v>45078</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15766,7 +15786,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15809,7 +15829,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15823,10 +15843,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45755</v>
+        <v>45566</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15839,7 +15859,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15882,7 +15902,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15896,10 +15916,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44785</v>
+        <v>46230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15911,13 +15931,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15960,7 +15975,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15974,10 +15989,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45243</v>
+        <v>45251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15990,7 +16005,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16033,7 +16048,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16047,10 +16062,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45603</v>
+        <v>44809</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16062,8 +16077,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16106,7 +16126,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16120,10 +16140,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45160</v>
+        <v>45243</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16136,7 +16156,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16179,7 +16199,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16189,14 +16209,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45531</v>
+        <v>46191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16208,13 +16228,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16257,7 +16272,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16271,10 +16286,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45478</v>
+        <v>44939</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16287,7 +16302,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16330,7 +16345,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16344,10 +16359,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46142</v>
+        <v>46276</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16359,13 +16374,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16408,7 +16418,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16422,10 +16432,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45386</v>
+        <v>45565</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16438,7 +16448,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16481,7 +16491,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16495,10 +16505,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45561</v>
+        <v>45169</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16510,8 +16520,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16554,7 +16569,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16568,10 +16583,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45707</v>
+        <v>45566</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16584,7 +16599,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16627,7 +16642,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16641,10 +16656,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46143</v>
+        <v>44664</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16656,8 +16671,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>14.6</v>
+        <v>3.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16700,7 +16720,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16710,14 +16730,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45631</v>
+        <v>45436</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16729,13 +16749,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16778,7 +16793,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16792,10 +16807,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46153</v>
+        <v>44469</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16808,7 +16823,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16851,7 +16866,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16865,10 +16880,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44469</v>
+        <v>45617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16881,7 +16896,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16924,7 +16939,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16938,10 +16953,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45890</v>
+        <v>45786</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16953,8 +16968,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16997,7 +17017,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17011,10 +17031,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46170</v>
+        <v>45789</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17027,7 +17047,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17070,7 +17090,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17084,10 +17104,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46171</v>
+        <v>45721</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17099,13 +17119,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17148,7 +17163,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17162,10 +17177,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46181</v>
+        <v>45630</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17177,8 +17192,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17221,7 +17241,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17235,10 +17255,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46188</v>
+        <v>45527</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17250,13 +17270,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17299,7 +17314,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 39394-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17313,10 +17328,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46188</v>
+        <v>46288</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17328,13 +17343,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>12.6</v>
+        <v>7.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17377,7 +17387,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17391,10 +17401,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46188</v>
+        <v>45680</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17406,13 +17416,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17455,7 +17460,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17469,10 +17474,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46206</v>
+        <v>45804</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17484,8 +17489,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17528,7 +17538,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17542,10 +17552,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46160</v>
+        <v>45707</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17557,13 +17567,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17606,7 +17611,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17620,10 +17625,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46210</v>
+        <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17635,13 +17640,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17684,7 +17684,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17694,14 +17694,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46210</v>
+        <v>45835</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17762,7 +17762,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17772,14 +17772,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46260</v>
+        <v>45834</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17835,7 +17835,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17849,10 +17849,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46230</v>
+        <v>45716</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17908,7 +17908,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17922,10 +17922,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46191</v>
+        <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17981,7 +17981,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17995,10 +17995,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46276</v>
+        <v>45862</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18071,7 +18071,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52381-2024</t>
+          <t>A 19851-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45609</v>
+        <v>45771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1636,8 +1636,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1670,357 +1675,352 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52381-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45609</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 52381-2024 artfynd.xlsx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 52381-2024 karta.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 52381-2024 georefererad karta.tif", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="Z11">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 52381-2024 karta knärot.png", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 52381-2024 FSC-klagomål.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 52381-2024 FSC-klagomål mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 52381-2024 tillsynsbegäran.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 52381-2024 tillsynsbegäran mail.docx", "A 52381-2024")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 52381-2024 prioriterade fågelarter.docx", "A 52381-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 43626-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45184</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.7</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>2</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallfingersvamp</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 43626-2023 artfynd.xlsx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 43626-2023 karta.png", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 43626-2023 georefererad karta.tif", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 43626-2023 FSC-klagomål.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 43626-2023 FSC-klagomål mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 43626-2023 tillsynsbegäran.docx", "A 43626-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 43626-2023 tillsynsbegäran mail.docx", "A 43626-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 19851-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S 1323-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>45771</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSBORG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>4.9</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>6</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 19851-2025 artfynd.xlsx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 19851-2025 karta.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 19851-2025 georefererad karta.tif", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 19851-2025 karta knärot.png", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 19851-2025 FSC-klagomål.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 19851-2025 FSC-klagomål mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 19851-2025 tillsynsbegäran.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 19851-2025 tillsynsbegäran mail.docx", "A 19851-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S 1323-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45771</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Kungsfågel</t>
-        </is>
-      </c>
       <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/S 1323-2025 artfynd.xlsx", "S 1323-2025")</f>
         <v/>
@@ -2057,7 +2057,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23268-2022</t>
+          <t>A 4448-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44720</v>
+        <v>46045</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,17 +2088,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2128,46 +2128,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29484-2025</t>
+          <t>A 23268-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45824</v>
+        <v>44720</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2196,8 +2196,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2230,49 +2235,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23268-2022 artfynd.xlsx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23268-2022 karta.png", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23268-2022 georefererad karta.tif", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23268-2022 FSC-klagomål.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23268-2022 FSC-klagomål mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23268-2022 tillsynsbegäran.docx", "A 23268-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23268-2022 tillsynsbegäran mail.docx", "A 23268-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 8984-2025</t>
+          <t>A 18567-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2291,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45713</v>
+        <v>46127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2303,17 +2308,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9.5</v>
+        <v>2.6</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2343,50 +2348,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42778-2024</t>
+          <t>A 29484-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2400,10 +2401,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45566</v>
+        <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2416,16 +2417,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2440,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2449,49 +2450,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 29484-2025 artfynd.xlsx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 29484-2025 karta.png", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 29484-2025 georefererad karta.tif", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 29484-2025 FSC-klagomål.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 29484-2025 FSC-klagomål mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 29484-2025 tillsynsbegäran.docx", "A 29484-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 29484-2025 tillsynsbegäran mail.docx", "A 29484-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51531-2023</t>
+          <t>A 28315-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2505,10 +2506,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45222</v>
+        <v>45818</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2520,19 +2521,14 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>11.2</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2559,49 +2555,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 9337-2025</t>
+          <t>A 23973-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2615,10 +2611,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45714</v>
+        <v>45075</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2631,10 +2627,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2646,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2655,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2667,46 +2663,50 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4448-2026</t>
+          <t>A 8984-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46045</v>
+        <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2741,13 +2741,13 @@
         </is>
       </c>
       <c r="I21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2777,46 +2777,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 4448-2026 artfynd.xlsx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 8984-2025 artfynd.xlsx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 4448-2026 karta.png", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 8984-2025 karta.png", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 4448-2026 georefererad karta.tif", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 8984-2025 georefererad karta.tif", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 4448-2026 FSC-klagomål.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 8984-2025 FSC-klagomål.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 4448-2026 FSC-klagomål mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 8984-2025 FSC-klagomål mail.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 4448-2026 tillsynsbegäran.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 8984-2025 tillsynsbegäran.docx", "A 8984-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 4448-2026 tillsynsbegäran mail.docx", "A 4448-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 8984-2025 tillsynsbegäran mail.docx", "A 8984-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 8984-2025 prioriterade fågelarter.docx", "A 8984-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59712-2021</t>
+          <t>A 42778-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2830,10 +2834,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44494</v>
+        <v>45566</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,13 +2849,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2860,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2878,55 +2877,55 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 42778-2024 artfynd.xlsx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 42778-2024 karta.png", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 42778-2024 georefererad karta.tif", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 42778-2024 FSC-klagomål.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 42778-2024 FSC-klagomål mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 42778-2024 tillsynsbegäran.docx", "A 42778-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 42778-2024 tillsynsbegäran mail.docx", "A 42778-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38103-2023</t>
+          <t>A 59712-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2940,10 +2939,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45161</v>
+        <v>44494</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,24 +2954,29 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
@@ -2980,58 +2984,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 59712-2021 artfynd.xlsx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 59712-2021 karta.png", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 59712-2021 georefererad karta.tif", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 59712-2021 FSC-klagomål.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 59712-2021 FSC-klagomål mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 59712-2021 tillsynsbegäran.docx", "A 59712-2021")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 59712-2021 tillsynsbegäran mail.docx", "A 59712-2021")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18567-2026</t>
+          <t>A 9337-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3045,10 +3049,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46127</v>
+        <v>45714</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,40 +3064,35 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3106,35 +3105,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 18567-2026 artfynd.xlsx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 9337-2025 artfynd.xlsx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 18567-2026 karta.png", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 9337-2025 karta.png", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 18567-2026 georefererad karta.tif", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 9337-2025 georefererad karta.tif", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 18567-2026 FSC-klagomål.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 9337-2025 FSC-klagomål.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 18567-2026 FSC-klagomål mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 9337-2025 FSC-klagomål mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 18567-2026 tillsynsbegäran.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 9337-2025 tillsynsbegäran.docx", "A 9337-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 18567-2026 tillsynsbegäran mail.docx", "A 18567-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 9337-2025 tillsynsbegäran mail.docx", "A 9337-2025")</f>
         <v/>
       </c>
     </row>
@@ -3158,7 +3157,7 @@
         <v>46202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3250,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31801-2026</t>
+          <t>A 51531-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3265,10 +3264,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46230</v>
+        <v>45222</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3280,8 +3279,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>11.2</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3293,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3305,62 +3309,58 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 51531-2023 artfynd.xlsx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 51531-2023 karta.png", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
-        <v/>
-      </c>
-      <c r="Z26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 51531-2023 georefererad karta.tif", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 51531-2023 FSC-klagomål.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 51531-2023 FSC-klagomål mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 51531-2023 tillsynsbegäran.docx", "A 51531-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 51531-2023 tillsynsbegäran mail.docx", "A 51531-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 53909-2023</t>
+          <t>A 38103-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45231</v>
+        <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3426,46 +3426,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 38103-2023 artfynd.xlsx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 38103-2023 karta.png", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 38103-2023 georefererad karta.tif", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 38103-2023 FSC-klagomål.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 38103-2023 FSC-klagomål mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 38103-2023 tillsynsbegäran.docx", "A 38103-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 38103-2023 tillsynsbegäran mail.docx", "A 38103-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 23973-2023</t>
+          <t>A 53909-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45075</v>
+        <v>45231</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3535,46 +3535,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 23973-2023 artfynd.xlsx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 53909-2023 artfynd.xlsx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 23973-2023 karta.png", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 53909-2023 karta.png", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 23973-2023 georefererad karta.tif", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 53909-2023 georefererad karta.tif", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 23973-2023 FSC-klagomål.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 53909-2023 FSC-klagomål.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 23973-2023 FSC-klagomål mail.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 53909-2023 FSC-klagomål mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 23973-2023 tillsynsbegäran.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 53909-2023 tillsynsbegäran.docx", "A 53909-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 23973-2023 tillsynsbegäran mail.docx", "A 23973-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/fåglar/A 23973-2023 prioriterade fågelarter.docx", "A 23973-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 53909-2023 tillsynsbegäran mail.docx", "A 53909-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28315-2025</t>
+          <t>A 31801-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3588,10 +3584,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45818</v>
+        <v>46230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3604,20 +3600,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3628,51 +3624,55 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 28315-2025 artfynd.xlsx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/artfynd/A 31801-2026 artfynd.xlsx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 28315-2025 karta.png", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 31801-2026 karta.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 28315-2025 georefererad karta.tif", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 31801-2026 georefererad karta.tif", "A 31801-2026")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/knärot/A 31801-2026 karta knärot.png", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 28315-2025 FSC-klagomål.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 31801-2026 FSC-klagomål.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 28315-2025 FSC-klagomål mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 31801-2026 FSC-klagomål mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 28315-2025 tillsynsbegäran.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 31801-2026 tillsynsbegäran.docx", "A 31801-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 28315-2025 tillsynsbegäran mail.docx", "A 28315-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 31801-2026 tillsynsbegäran mail.docx", "A 31801-2026")</f>
         <v/>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>44795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23469-2024</t>
+          <t>A 25999-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45453</v>
+        <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5439-2022</t>
+          <t>A 26016-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44595</v>
+        <v>45090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13076-2023</t>
+          <t>A 14522-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45002</v>
+        <v>45394</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4911,8 +4911,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4955,7 +4960,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34120-2024</t>
+          <t>A 56541-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45524</v>
+        <v>45243</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4986,11 +4991,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5033,7 +5038,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34123-2024</t>
+          <t>A 53898-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5047,10 +5052,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45524</v>
+        <v>45231</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5062,13 +5067,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38073-2023</t>
+          <t>A 8052-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45160</v>
+        <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5184,7 +5184,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 70945-2021</t>
+          <t>A 58533-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44538</v>
+        <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5213,13 +5213,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5262,7 +5257,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57454-2024</t>
+          <t>A 8053-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5272,14 +5267,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45630</v>
+        <v>44974</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5292,7 +5287,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5335,7 +5330,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56541-2023</t>
+          <t>A 3575-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5349,10 +5344,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45243</v>
+        <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5364,13 +5359,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5413,7 +5403,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39285-2023</t>
+          <t>A 38290-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5427,10 +5417,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45166</v>
+        <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5443,7 +5433,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5486,7 +5476,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39287-2023</t>
+          <t>A 26914-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5500,10 +5490,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45166</v>
+        <v>45470</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5515,8 +5505,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5559,7 +5554,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62304-2021</t>
+          <t>A 64011-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44503</v>
+        <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5588,13 +5583,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5637,7 +5627,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14514-2024</t>
+          <t>A 64012-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5651,10 +5641,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45394</v>
+        <v>46021</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5666,13 +5656,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5715,7 +5700,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15220-2023</t>
+          <t>A 64025-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5729,10 +5714,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45019</v>
+        <v>46021</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5745,7 +5730,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5788,7 +5773,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25696-2023</t>
+          <t>A 35040-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5802,10 +5787,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45089</v>
+        <v>45527</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5818,7 +5803,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5861,7 +5846,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28528-2024</t>
+          <t>A 29357-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5871,14 +5856,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45478</v>
+        <v>45483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5890,8 +5875,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5934,7 +5924,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 42757-2024</t>
+          <t>A 57727-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5948,10 +5938,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45566</v>
+        <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5963,8 +5953,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6007,7 +6002,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44577-2023</t>
+          <t>A 61542-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6021,10 +6016,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45183</v>
+        <v>45265</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6037,7 +6032,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6080,7 +6075,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26016-2023</t>
+          <t>A 65313-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6094,10 +6089,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45090</v>
+        <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6110,7 +6105,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6153,7 +6148,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51111-2024</t>
+          <t>A 41684-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6167,10 +6162,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45603</v>
+        <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6183,7 +6178,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6226,7 +6221,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58127-2024</t>
+          <t>A 38995-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6236,14 +6231,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45632</v>
+        <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6255,13 +6250,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6304,7 +6294,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59887-2021</t>
+          <t>A 29490-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6318,10 +6308,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44494</v>
+        <v>45824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6335,11 +6325,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6382,7 +6372,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38995-2024</t>
+          <t>A 28460-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6396,10 +6386,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45548</v>
+        <v>45103</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6412,7 +6402,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6455,7 +6445,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13077-2023</t>
+          <t>A 58129-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6465,14 +6455,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45002</v>
+        <v>45632</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6484,8 +6474,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6528,7 +6523,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59845-2023</t>
+          <t>A 61211-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6542,10 +6537,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45257</v>
+        <v>44908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6558,7 +6553,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>8.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6601,7 +6596,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14703-2025</t>
+          <t>A 4430-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6615,10 +6610,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45742</v>
+        <v>46045</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6630,8 +6625,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 70783-2021</t>
+          <t>A 4454-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44537</v>
+        <v>46045</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6703,8 +6703,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6747,7 +6752,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 57235-2022</t>
+          <t>A 4439-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6761,10 +6766,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44895</v>
+        <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6776,8 +6781,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>14.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6820,7 +6830,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2796-2023</t>
+          <t>A 41350-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6834,10 +6844,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44944</v>
+        <v>45899</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6849,13 +6859,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6898,7 +6903,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44985-2024</t>
+          <t>A 48175-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6912,10 +6917,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45575</v>
+        <v>45589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6971,7 +6976,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40129-2023</t>
+          <t>A 42757-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6985,10 +6990,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45169</v>
+        <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7002,11 +7007,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7049,7 +7054,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 48175-2024</t>
+          <t>A 6035-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7063,10 +7068,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45589</v>
+        <v>46052</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7079,7 +7084,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7122,7 +7127,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14525-2024</t>
+          <t>A 6408-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7136,10 +7141,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45394</v>
+        <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7151,13 +7156,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7200,7 +7200,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59401-2022</t>
+          <t>A 14703-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7214,10 +7214,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44906</v>
+        <v>45742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18623-2022</t>
+          <t>A 44366-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44687</v>
+        <v>45916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7302,8 +7302,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7346,7 +7351,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8052-2023</t>
+          <t>A 63732-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7360,10 +7365,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44974</v>
+        <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7375,8 +7380,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7419,7 +7429,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8053-2023</t>
+          <t>A 63733-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7433,10 +7443,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44974</v>
+        <v>46010</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7448,8 +7458,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7492,7 +7507,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2784-2023</t>
+          <t>A 7644-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7506,10 +7521,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44944</v>
+        <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7521,13 +7536,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7570,7 +7580,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1454-2023</t>
+          <t>A 63731-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7584,10 +7594,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44937</v>
+        <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7599,8 +7609,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7643,7 +7658,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42710-2024</t>
+          <t>A 63734-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7657,10 +7672,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45566</v>
+        <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7672,8 +7687,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7716,7 +7736,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38290-2025</t>
+          <t>A 5439-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7730,10 +7750,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45883</v>
+        <v>44595</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7789,7 +7809,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53251-2024</t>
+          <t>A 45247-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7803,10 +7823,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45614</v>
+        <v>45919</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7819,7 +7839,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7862,7 +7882,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34314-2024</t>
+          <t>A 45256-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7876,10 +7896,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45524</v>
+        <v>45919</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7891,13 +7911,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7940,7 +7955,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28460-2023</t>
+          <t>A 25982-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7954,10 +7969,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45103</v>
+        <v>45804</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7969,8 +7984,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8013,7 +8033,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29490-2025</t>
+          <t>A 9130-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8027,10 +8047,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45824</v>
+        <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8042,13 +8062,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8091,7 +8106,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41684-2023</t>
+          <t>A 42757-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8105,10 +8120,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45176</v>
+        <v>45566</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8121,7 +8136,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.3</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8164,7 +8179,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41350-2025</t>
+          <t>A 42598-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8178,10 +8193,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45899</v>
+        <v>45565</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8194,7 +8209,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>8.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8237,7 +8252,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 2791-2023</t>
+          <t>A 13076-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8251,10 +8266,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44944</v>
+        <v>45002</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8266,13 +8281,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8315,7 +8325,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42757-2025</t>
+          <t>A 47265-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8329,10 +8339,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45908</v>
+        <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8344,13 +8354,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8393,7 +8398,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10828-2024</t>
+          <t>A 10907-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8407,10 +8412,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45369</v>
+        <v>46079</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8423,7 +8428,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8466,7 +8471,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26914-2024</t>
+          <t>A 47262-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8480,10 +8485,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45470</v>
+        <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8495,13 +8500,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8544,7 +8544,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 44366-2025</t>
+          <t>A 1454-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45916</v>
+        <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8573,13 +8573,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8622,7 +8617,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34670-2022</t>
+          <t>A 42724-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8636,10 +8631,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44795</v>
+        <v>45566</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8651,13 +8646,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8700,7 +8690,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 45247-2025</t>
+          <t>A 44985-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8714,10 +8704,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45919</v>
+        <v>45575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8730,7 +8720,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8773,7 +8763,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 45256-2025</t>
+          <t>A 48129-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8787,10 +8777,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8803,7 +8793,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8846,7 +8836,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25999-2023</t>
+          <t>A 7978-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8860,10 +8850,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45090</v>
+        <v>45707</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8876,7 +8866,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8919,7 +8909,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41937-2024</t>
+          <t>A 59401-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8933,10 +8923,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45561</v>
+        <v>44906</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8949,7 +8939,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8992,7 +8982,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17002-2025</t>
+          <t>A 48888-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9006,10 +8996,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45755</v>
+        <v>45209</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9022,7 +9012,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9065,7 +9055,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47265-2025</t>
+          <t>A 49866-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9079,10 +9069,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9095,7 +9085,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9138,7 +9128,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48385-2025</t>
+          <t>A 49985-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9152,10 +9142,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45933</v>
+        <v>45942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9167,13 +9157,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>9.4</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9216,7 +9201,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 47262-2025</t>
+          <t>A 48174-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9230,10 +9215,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45930</v>
+        <v>45589</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9246,7 +9231,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9289,7 +9274,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33122-2022</t>
+          <t>A 34314-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9303,10 +9288,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44785</v>
+        <v>45524</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9320,11 +9305,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9367,7 +9352,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48129-2025</t>
+          <t>A 412-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9377,14 +9362,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45933</v>
+        <v>44929</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9397,7 +9382,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9436,11 +9421,35 @@
         <v>0</v>
       </c>
       <c r="V106" s="2" t="inlineStr"/>
+      <c r="X106">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="Y106">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AA106">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AB106">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AC106">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
+        <v/>
+      </c>
+      <c r="AD106">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 35441-2024</t>
+          <t>A 10828-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9450,14 +9459,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45531</v>
+        <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9469,13 +9478,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>9.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9518,7 +9522,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 24594-2022</t>
+          <t>A 53251-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9532,10 +9536,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44727</v>
+        <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9548,7 +9552,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9591,7 +9595,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 54444-2023</t>
+          <t>A 18564-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9605,10 +9609,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45233</v>
+        <v>46127</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9620,8 +9624,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9664,7 +9673,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 49985-2025</t>
+          <t>A 56110-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9678,10 +9687,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45942</v>
+        <v>45973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9694,7 +9703,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9737,7 +9746,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 49866-2025</t>
+          <t>A 57581-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9751,10 +9760,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45940</v>
+        <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9767,7 +9776,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9810,7 +9819,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 30136-2024</t>
+          <t>A 59845-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9824,10 +9833,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45489</v>
+        <v>45257</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9840,7 +9849,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9883,7 +9892,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14738-2025</t>
+          <t>A 13077-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9897,10 +9906,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45742</v>
+        <v>45002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9913,7 +9922,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9956,7 +9965,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 65313-2021</t>
+          <t>A 58152-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9970,10 +9979,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44515</v>
+        <v>44900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9986,7 +9995,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10029,7 +10038,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26017-2023</t>
+          <t>A 29685-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10043,10 +10052,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45090</v>
+        <v>44755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10059,7 +10068,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10102,7 +10111,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50985-2023</t>
+          <t>A 59111-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10116,10 +10125,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45218</v>
+        <v>45988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10131,13 +10140,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10180,7 +10184,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10415-2025</t>
+          <t>A 24594-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10194,10 +10198,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45720</v>
+        <v>44727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10210,7 +10214,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10253,7 +10257,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 56110-2025</t>
+          <t>A 59697-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10267,10 +10271,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45973</v>
+        <v>45992</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10283,7 +10287,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10326,7 +10330,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57915-2024</t>
+          <t>A 48385-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10336,14 +10340,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45631</v>
+        <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10361,7 +10365,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.2</v>
+        <v>9.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10404,7 +10408,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57581-2025</t>
+          <t>A 40128-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10418,10 +10422,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45980</v>
+        <v>45169</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,8 +10437,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10477,7 +10486,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41943-2024</t>
+          <t>A 23469-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10491,10 +10500,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45561</v>
+        <v>45453</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10507,7 +10516,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10550,7 +10559,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13252-2024</t>
+          <t>A 62068-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10564,10 +10573,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45386</v>
+        <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,8 +10588,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10623,7 +10637,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 59045-2023</t>
+          <t>A 62072-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10637,10 +10651,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45252</v>
+        <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10654,11 +10668,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10701,7 +10715,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21014-2026</t>
+          <t>A 17002-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10715,10 +10729,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46143</v>
+        <v>45755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10731,7 +10745,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>14.6</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10774,7 +10788,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20940-2026</t>
+          <t>A 53247-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10788,10 +10802,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46142</v>
+        <v>45229</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,13 +10817,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10852,7 +10861,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 59111-2025</t>
+          <t>A 33122-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10866,10 +10875,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45988</v>
+        <v>44785</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10881,8 +10890,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10925,7 +10939,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 59697-2025</t>
+          <t>A 35441-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10935,14 +10949,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45992</v>
+        <v>45531</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10954,8 +10968,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10998,7 +11017,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21988-2026</t>
+          <t>A 20940-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11012,10 +11031,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11027,8 +11046,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11071,7 +11095,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59399-2022</t>
+          <t>A 58573-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11085,10 +11109,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44906</v>
+        <v>45251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11101,7 +11125,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11144,7 +11168,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48888-2023</t>
+          <t>A 70945-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11158,10 +11182,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45209</v>
+        <v>44538</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,8 +11197,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11217,7 +11246,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 39699-2025</t>
+          <t>A 21014-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11231,10 +11260,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45890</v>
+        <v>46143</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11247,7 +11276,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>14.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11290,7 +11319,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62068-2025</t>
+          <t>A 42710-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11304,10 +11333,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46006</v>
+        <v>45566</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,13 +11348,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11368,7 +11392,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62072-2025</t>
+          <t>A 25696-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11382,10 +11406,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46006</v>
+        <v>45089</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11395,11 +11419,6 @@
       <c r="G133" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -11446,7 +11465,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 48174-2024</t>
+          <t>A 21988-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11460,10 +11479,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45589</v>
+        <v>46153</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11476,7 +11495,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11519,7 +11538,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 7652-2023</t>
+          <t>A 31770-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11533,10 +11552,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44972</v>
+        <v>45834</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11549,7 +11568,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11592,7 +11611,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23500-2023</t>
+          <t>A 31701-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11606,10 +11625,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45076</v>
+        <v>45834</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11622,7 +11641,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11665,7 +11684,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 64011-2025</t>
+          <t>A 39699-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11679,10 +11698,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46021</v>
+        <v>45890</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11695,7 +11714,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11738,7 +11757,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 61542-2023</t>
+          <t>A 2784-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11752,10 +11771,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45265</v>
+        <v>44944</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11767,8 +11786,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11811,7 +11835,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 64012-2025</t>
+          <t>A 32128-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11821,14 +11845,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46021</v>
+        <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11840,8 +11864,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11884,7 +11913,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64025-2025</t>
+          <t>A 27823-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11898,10 +11927,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46021</v>
+        <v>45098</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11914,7 +11943,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11957,7 +11986,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4430-2026</t>
+          <t>A 40129-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11971,10 +12000,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46045</v>
+        <v>45169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11992,7 +12021,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12035,7 +12064,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4439-2026</t>
+          <t>A 14525-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12049,10 +12078,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46045</v>
+        <v>45394</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12066,11 +12095,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>14.3</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12113,7 +12142,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4454-2026</t>
+          <t>A 24008-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12127,10 +12156,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46045</v>
+        <v>45078</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12142,13 +12171,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12191,7 +12215,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58533-2023</t>
+          <t>A 70783-2021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12205,10 +12229,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45251</v>
+        <v>44537</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12221,7 +12245,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12264,7 +12288,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 58152-2022</t>
+          <t>A 2791-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12278,10 +12302,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44900</v>
+        <v>44944</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12293,8 +12317,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12337,7 +12366,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 37363-2022</t>
+          <t>A 9788-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12351,10 +12380,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44809</v>
+        <v>45716</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12366,13 +12395,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12415,7 +12439,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 29357-2024</t>
+          <t>A 61559-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12425,14 +12449,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45483</v>
+        <v>45265</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12444,13 +12468,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12493,7 +12512,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6035-2026</t>
+          <t>A 24541-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12507,10 +12526,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46052</v>
+        <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12523,7 +12542,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12566,7 +12585,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 6408-2026</t>
+          <t>A 45019-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12580,10 +12599,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46055</v>
+        <v>45575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12596,7 +12615,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12639,7 +12658,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10007-2025</t>
+          <t>A 35930-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12653,10 +12672,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45719</v>
+        <v>45862</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12669,7 +12688,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12712,7 +12731,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 63732-2025</t>
+          <t>A 34120-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12726,10 +12745,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46010</v>
+        <v>45524</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12743,11 +12762,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12790,7 +12809,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 63731-2025</t>
+          <t>A 34123-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12804,10 +12823,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46010</v>
+        <v>45524</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12821,11 +12840,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12868,7 +12887,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 63734-2025</t>
+          <t>A 34125-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12882,10 +12901,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46010</v>
+        <v>45524</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12899,11 +12918,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12946,7 +12965,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 63733-2025</t>
+          <t>A 25977-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12960,10 +12979,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46010</v>
+        <v>46181</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12975,13 +12994,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13024,7 +13038,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 7644-2026</t>
+          <t>A 59887-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13038,10 +13052,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46062</v>
+        <v>44494</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,8 +13067,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13097,7 +13116,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 53247-2023</t>
+          <t>A 59890-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13111,10 +13130,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45229</v>
+        <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,8 +13145,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13170,7 +13194,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 412-2023</t>
+          <t>A 10007-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13180,14 +13204,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44929</v>
+        <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13200,7 +13224,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13239,35 +13263,11 @@
         <v>0</v>
       </c>
       <c r="V157" s="2" t="inlineStr"/>
-      <c r="X157">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor/A 412-2023 karta.png", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="Y157">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/kartor_geotiff/A 412-2023 georefererad karta.tif", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AA157">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomål/A 412-2023 FSC-klagomål.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AB157">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/klagomålsmail/A 412-2023 FSC-klagomål mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AC157">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsyn/A 412-2023 tillsynsbegäran.docx", "A 412-2023")</f>
-        <v/>
-      </c>
-      <c r="AD157">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1446/tillsynsmail/A 412-2023 tillsynsbegäran mail.docx", "A 412-2023")</f>
-        <v/>
-      </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 9130-2026</t>
+          <t>A 27333-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13281,10 +13281,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46069</v>
+        <v>46188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13296,8 +13296,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13340,7 +13345,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24541-2026</t>
+          <t>A 27332-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13354,10 +13359,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13369,8 +13374,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>12.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13413,7 +13423,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 29685-2022</t>
+          <t>A 27349-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13427,10 +13437,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44755</v>
+        <v>46188</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13442,8 +13452,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13486,7 +13501,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 10907-2026</t>
+          <t>A 69341-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13500,10 +13515,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46079</v>
+        <v>44531</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13516,7 +13531,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13559,7 +13574,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24725-2026</t>
+          <t>A 57913-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13569,14 +13584,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46171</v>
+        <v>45631</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13594,7 +13609,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13637,7 +13652,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56545-2023</t>
+          <t>A 14738-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13651,10 +13666,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45243</v>
+        <v>45742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13664,11 +13679,6 @@
       <c r="G163" t="inlineStr">
         <is>
           <t>KARLSBORG</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -13715,7 +13725,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61211-2022</t>
+          <t>A 23500-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13725,14 +13735,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44908</v>
+        <v>45076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13745,7 +13755,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13788,7 +13798,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 25977-2026</t>
+          <t>A 41937-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13802,10 +13812,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46181</v>
+        <v>45561</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13861,7 +13871,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 27332-2026</t>
+          <t>A 54444-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13875,10 +13885,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46188</v>
+        <v>45233</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13890,13 +13900,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>12.6</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13939,7 +13944,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27349-2026</t>
+          <t>A 50985-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13953,10 +13958,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46188</v>
+        <v>45218</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13974,7 +13979,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14017,7 +14022,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27333-2026</t>
+          <t>A 30262-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14031,10 +14036,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46188</v>
+        <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14046,13 +14051,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14095,7 +14095,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57913-2024</t>
+          <t>A 22890-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14105,14 +14105,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45631</v>
+        <v>46160</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14173,7 +14173,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7977-2025</t>
+          <t>A 30610-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14187,10 +14187,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45707</v>
+        <v>46210</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14202,8 +14202,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14246,7 +14251,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 59047-2023</t>
+          <t>A 30609-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14260,10 +14265,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45252</v>
+        <v>46210</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14277,11 +14282,11 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14324,7 +14329,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 58129-2024</t>
+          <t>A 35151-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14334,14 +14339,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45632</v>
+        <v>46260</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14353,13 +14358,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14402,7 +14402,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 18564-2026</t>
+          <t>A 56545-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14416,10 +14416,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46127</v>
+        <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14480,7 +14480,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 14522-2024</t>
+          <t>A 44577-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14494,10 +14494,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45394</v>
+        <v>45183</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14509,13 +14509,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14558,7 +14553,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 48884-2023</t>
+          <t>A 10415-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14572,10 +14567,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45209</v>
+        <v>45720</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14588,7 +14583,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14631,7 +14626,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 30262-2026</t>
+          <t>A 59047-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14645,10 +14640,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46206</v>
+        <v>45252</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14660,8 +14655,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14704,7 +14704,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59890-2021</t>
+          <t>A 37383-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14718,10 +14718,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44494</v>
+        <v>44809</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14735,11 +14735,11 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 59404-2022</t>
+          <t>A 31798-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14796,10 +14796,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44906</v>
+        <v>46230</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14855,7 +14855,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22890-2026</t>
+          <t>A 27906-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46160</v>
+        <v>46191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14884,13 +14884,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14933,7 +14928,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 30610-2026</t>
+          <t>A 42825-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14947,10 +14942,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46210</v>
+        <v>45566</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14962,13 +14957,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15011,7 +15001,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 30609-2026</t>
+          <t>A 37622-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15025,10 +15015,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46210</v>
+        <v>46276</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15040,13 +15030,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15089,7 +15074,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 69341-2021</t>
+          <t>A 59045-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15103,10 +15088,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44531</v>
+        <v>45252</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15118,8 +15103,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15162,7 +15152,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 25697-2023</t>
+          <t>A 57235-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15176,10 +15166,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45089</v>
+        <v>44895</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15192,7 +15182,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15235,7 +15225,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34125-2024</t>
+          <t>A 59404-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15249,10 +15239,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45524</v>
+        <v>44906</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15264,13 +15254,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15313,7 +15298,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 15396-2024</t>
+          <t>A 62304-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15323,14 +15308,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45401</v>
+        <v>44503</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15342,8 +15327,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15386,7 +15376,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35151-2026</t>
+          <t>A 15958-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15400,10 +15390,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46260</v>
+        <v>44664</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15415,8 +15405,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15459,7 +15454,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 59877-2021</t>
+          <t>A 15396-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15469,14 +15464,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44494</v>
+        <v>45401</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15488,13 +15483,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15537,7 +15527,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27823-2023</t>
+          <t>A 30136-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15551,10 +15541,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45098</v>
+        <v>45489</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15567,7 +15557,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15610,7 +15600,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 53898-2023</t>
+          <t>A 59877-2021</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15624,10 +15614,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45231</v>
+        <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15639,8 +15629,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15683,7 +15678,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 45019-2024</t>
+          <t>A 39394-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15697,10 +15692,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45575</v>
+        <v>46288</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15713,7 +15708,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15756,7 +15751,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24008-2023</t>
+          <t>A 20564-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15770,10 +15765,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45078</v>
+        <v>45436</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15786,7 +15781,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15829,7 +15824,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 42825-2024</t>
+          <t>A 2100-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15843,10 +15838,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45566</v>
+        <v>44939</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15859,7 +15854,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15902,7 +15897,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31798-2026</t>
+          <t>A 24725-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15916,10 +15911,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46230</v>
+        <v>46171</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15931,8 +15926,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15975,7 +15975,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 58573-2023</t>
+          <t>A 25697-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15989,10 +15989,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45251</v>
+        <v>45089</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16048,7 +16048,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 37383-2022</t>
+          <t>A 26017-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16062,10 +16062,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44809</v>
+        <v>45090</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16077,13 +16077,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16126,7 +16121,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 56495-2023</t>
+          <t>A 18623-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16140,10 +16135,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45243</v>
+        <v>44687</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16156,7 +16151,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16199,7 +16194,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 27906-2026</t>
+          <t>A 59399-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16213,10 +16208,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46191</v>
+        <v>44906</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16229,7 +16224,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16272,7 +16267,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 2100-2023</t>
+          <t>A 37363-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16286,10 +16281,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44939</v>
+        <v>44809</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16301,8 +16296,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16345,7 +16345,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 37622-2026</t>
+          <t>A 7652-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16359,10 +16359,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46276</v>
+        <v>44972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16418,7 +16418,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 42598-2024</t>
+          <t>A 39285-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16432,10 +16432,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45565</v>
+        <v>45166</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>8.9</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16491,7 +16491,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 40128-2023</t>
+          <t>A 39287-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16505,10 +16505,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45169</v>
+        <v>45166</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,13 +16520,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16569,7 +16564,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 42724-2024</t>
+          <t>A 14514-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16583,10 +16578,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45566</v>
+        <v>45394</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16598,8 +16593,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15958-2022</t>
+          <t>A 34670-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16656,10 +16656,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44664</v>
+        <v>44795</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16673,11 +16673,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16720,7 +16720,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 20564-2024</t>
+          <t>A 58127-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16730,14 +16730,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45436</v>
+        <v>45632</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16749,8 +16749,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16793,7 +16798,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 53898-2021</t>
+          <t>A 15220-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16807,10 +16812,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44469</v>
+        <v>45019</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16823,7 +16828,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16866,7 +16871,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 54416-2024</t>
+          <t>A 2796-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16880,10 +16885,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45617</v>
+        <v>44944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16895,8 +16900,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16939,7 +16949,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 22435-2025</t>
+          <t>A 57454-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16949,14 +16959,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45786</v>
+        <v>45630</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16968,13 +16978,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17017,7 +17022,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22761-2025</t>
+          <t>A 48884-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17031,10 +17036,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45789</v>
+        <v>45209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17047,7 +17052,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17090,7 +17095,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10667-2025</t>
+          <t>A 56495-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17104,10 +17109,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45721</v>
+        <v>45243</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17120,7 +17125,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17163,7 +17168,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 57727-2024</t>
+          <t>A 51111-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17177,10 +17182,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45630</v>
+        <v>45603</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17192,13 +17197,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17241,7 +17241,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35040-2024</t>
+          <t>A 38073-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45527</v>
+        <v>45160</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 39394-2026</t>
+          <t>A 28528-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17328,10 +17328,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46288</v>
+        <v>45478</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17387,7 +17387,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 3575-2025</t>
+          <t>A 13252-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17401,10 +17401,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45680</v>
+        <v>45386</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17460,7 +17460,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 25982-2025</t>
+          <t>A 41943-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17474,10 +17474,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45804</v>
+        <v>45561</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17489,13 +17489,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17538,7 +17533,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 7978-2025</t>
+          <t>A 7977-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17555,7 +17550,7 @@
         <v>45707</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17568,7 +17563,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17611,7 +17606,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31770-2025</t>
+          <t>A 57915-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17621,14 +17616,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45834</v>
+        <v>45631</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17640,8 +17635,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17684,7 +17684,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 32128-2025</t>
+          <t>A 53898-2021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17694,14 +17694,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45835</v>
+        <v>44469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17713,13 +17713,8 @@
           <t>KARLSBORG</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17762,7 +17757,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31701-2025</t>
+          <t>A 54416-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17772,14 +17767,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45834</v>
+        <v>45617</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17787,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17835,7 +17830,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9788-2025</t>
+          <t>A 22435-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17849,10 +17844,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45716</v>
+        <v>45786</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17864,8 +17859,13 @@
           <t>KARLSBORG</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17908,7 +17908,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61559-2023</t>
+          <t>A 22761-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17922,10 +17922,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45265</v>
+        <v>45789</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17981,7 +17981,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 35930-2025</t>
+          <t>A 10667-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17995,10 +17995,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45862</v>
+        <v>45721</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18071,7 +18071,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45609</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45184</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46045</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44720</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>46127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45818</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45075</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45566</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44494</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45714</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>46202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45222</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>45231</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>44795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45394</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45243</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45231</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44974</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45470</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>46021</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>46021</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45527</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>45265</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45103</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45632</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>46045</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>46045</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45899</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46052</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46010</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44595</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>45919</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45919</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45804</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45566</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>45565</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45002</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>46079</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45566</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45707</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44906</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45209</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45940</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45589</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45524</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44929</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46127</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45257</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>45002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45992</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45169</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45453</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45229</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44785</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45531</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>46142</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>44538</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>46143</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>45566</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45089</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>46153</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45834</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45834</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45890</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44944</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45098</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45394</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45078</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44537</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44944</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45716</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45265</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45862</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45524</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45524</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45524</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>46181</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44494</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>46188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>46188</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>46188</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>44531</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45631</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45561</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45233</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45218</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46160</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46210</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>46210</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>46260</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45183</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45720</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45252</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>44809</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>46230</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>46191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>45566</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>46276</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>45252</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>44895</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44906</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44503</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44664</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45401</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45489</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>46288</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45436</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44939</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>46171</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45089</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45090</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>44687</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44906</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>44809</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>44972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45166</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45166</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45394</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44795</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45632</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>45019</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45630</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45209</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45243</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45603</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45160</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45478</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45386</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45561</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45707</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45631</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44469</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45617</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45786</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45789</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45721</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45468</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>46059</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>

--- a/Översikt KARLSBORG.xlsx
+++ b/Översikt KARLSBORG.xlsx
@@ -601,7 +601,7 @@
         <v>46176</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>44929</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>45741</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>45098</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>45387</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45775</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45696</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>45387</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45545</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45771</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45609</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>45184</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45771</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>46045</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44720</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>46127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>45824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>45818</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45075</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45566</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44494</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45714</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>46202</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45222</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>45231</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46230</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>44584</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44538</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44496</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44785</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44469</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>44538</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44795</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>44795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45090</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45394</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>45243</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45231</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44974</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45680</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45470</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>46021</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>46021</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>46021</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45527</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>45265</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45103</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45632</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>46045</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>46045</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>46045</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45899</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46052</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>46010</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>46010</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>46010</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44595</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>45919</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45919</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45804</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>46069</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>45566</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>45565</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45002</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45930</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>46079</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45930</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44937</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45566</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45575</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45707</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44906</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45209</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45940</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45589</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45524</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44929</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45369</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46127</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45257</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>45002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>44900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>44755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45988</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44727</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45992</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45169</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45453</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>46006</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45229</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44785</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45531</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>46142</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>44538</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>46143</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>45566</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45089</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>46153</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45834</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45834</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45890</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>44944</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45098</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45394</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45078</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44537</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44944</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45716</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45265</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45575</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45862</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45524</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>45524</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45524</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>46181</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44494</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44494</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>46188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>46188</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>46188</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>44531</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45631</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v